--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -681,6 +681,20 @@
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>- 몰큘 01·02, 낫 어 퍼퓸은 단일 성분 향수라 노트가 탑 한 칸뿐입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>■ 분위기 칩 추가 (D-26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>- 새 분위기 칩 '사랑스러운(lovely)', '관능적인(sensual)'을 추가하고, 어울리는 향수 40개의 moods에 붙였습니다 (AI 판단이므로 맡아본 느낌에 맞게 고쳐도 됩니다).</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1435,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, fresh</t>
+          <t>soft, elegant, fresh, lovely</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr"/>
@@ -1541,7 +1555,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>soft, sweet, elegant</t>
+          <t>soft, sweet, elegant, lovely</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr"/>
@@ -1661,7 +1675,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>sweet, cozy, warm</t>
+          <t>sweet, cozy, warm, lovely</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -1805,7 +1819,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>soft, sweet, zesty</t>
+          <t>soft, sweet, zesty, lovely</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr"/>
@@ -3129,7 +3143,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>elegant, sweet, warm</t>
+          <t>elegant, sweet, warm, lovely</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -3253,7 +3267,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, fresh</t>
+          <t>elegant, soft, fresh, lovely</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr"/>
@@ -3373,7 +3387,7 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, warm</t>
+          <t>elegant, soft, warm, lovely</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr"/>
@@ -3613,7 +3627,7 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>elegant, sweet, soft</t>
+          <t>elegant, sweet, soft, lovely</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr"/>
@@ -3733,7 +3747,7 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft</t>
+          <t>elegant, soft, lovely</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -4349,7 +4363,7 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, calm</t>
+          <t>soft, elegant, calm, lovely</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -5353,7 +5367,7 @@
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>deep, calm, warm</t>
+          <t>deep, calm, warm, sensual</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -5617,7 +5631,7 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant</t>
+          <t>deep, warm, elegant, sensual</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
@@ -5881,7 +5895,7 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, sweet</t>
+          <t>warm, elegant, sweet, sensual</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
@@ -6005,7 +6019,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, elegant</t>
+          <t>warm, deep, elegant, sensual</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
@@ -6249,7 +6263,7 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>sweet, deep, warm</t>
+          <t>sweet, deep, warm, sensual</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
@@ -6373,7 +6387,7 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>sweet, cozy, elegant</t>
+          <t>sweet, cozy, elegant, lovely</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -6497,7 +6511,7 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep</t>
+          <t>warm, cozy, deep, sensual</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
@@ -6621,7 +6635,7 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>sweet, deep, warm</t>
+          <t>sweet, deep, warm, sensual</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
@@ -6889,7 +6903,7 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>deep, cozy, warm</t>
+          <t>deep, cozy, warm, sensual</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
@@ -7013,7 +7027,7 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, cozy</t>
+          <t>deep, warm, cozy, sensual</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
@@ -7277,7 +7291,7 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant</t>
+          <t>deep, warm, elegant, sensual</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
@@ -7825,7 +7839,7 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>deep, sweet, warm</t>
+          <t>deep, sweet, warm, sensual</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
@@ -8429,7 +8443,7 @@
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>elegant, deep, warm</t>
+          <t>elegant, deep, warm, sensual</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr">
@@ -8553,7 +8567,7 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep</t>
+          <t>warm, cozy, deep, sensual</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr">
@@ -8677,7 +8691,7 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm</t>
+          <t>elegant, warm, sensual</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
@@ -8925,7 +8939,7 @@
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, sweet</t>
+          <t>soft, elegant, sweet, lovely</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
@@ -9169,7 +9183,7 @@
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>sweet, soft, fresh</t>
+          <t>sweet, soft, fresh, lovely</t>
         </is>
       </c>
       <c r="N68" s="5" t="n"/>
@@ -9569,7 +9583,7 @@
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>elegant, sweet, soft</t>
+          <t>elegant, sweet, soft, lovely</t>
         </is>
       </c>
       <c r="N71" s="5" t="n"/>
@@ -9933,7 +9947,7 @@
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>deep, elegant, warm</t>
+          <t>deep, elegant, warm, sensual</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
@@ -10057,7 +10071,7 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, cozy</t>
+          <t>warm, deep, cozy, sensual</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
@@ -10301,7 +10315,7 @@
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant</t>
+          <t>deep, warm, elegant, sensual</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
@@ -11345,7 +11359,7 @@
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, elegant</t>
+          <t>sweet, warm, elegant, sensual</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr">
@@ -11469,7 +11483,7 @@
       </c>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, elegant</t>
+          <t>warm, sweet, elegant, sensual</t>
         </is>
       </c>
       <c r="N86" s="5" t="n"/>
@@ -11589,7 +11603,7 @@
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant</t>
+          <t>deep, warm, elegant, sensual</t>
         </is>
       </c>
       <c r="N87" s="5" t="inlineStr">
@@ -11713,7 +11727,7 @@
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>deep, elegant, warm</t>
+          <t>deep, elegant, warm, sensual</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
@@ -11837,7 +11851,7 @@
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>deep, warm</t>
+          <t>deep, warm, sensual</t>
         </is>
       </c>
       <c r="N89" s="5" t="inlineStr">
@@ -12441,7 +12455,7 @@
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, deep</t>
+          <t>warm, sweet, deep, sensual</t>
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr">
@@ -12901,7 +12915,7 @@
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>sweet, elegant, soft</t>
+          <t>sweet, elegant, soft, lovely</t>
         </is>
       </c>
       <c r="N98" s="5" t="n"/>
@@ -13021,7 +13035,7 @@
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep</t>
+          <t>warm, cozy, deep, sensual</t>
         </is>
       </c>
       <c r="N99" s="5" t="inlineStr">
@@ -13145,7 +13159,7 @@
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep</t>
+          <t>warm, cozy, deep, sensual</t>
         </is>
       </c>
       <c r="N100" s="5" t="inlineStr">
@@ -17053,6 +17067,20 @@
         <f>COUNTIF(perfumes!$K$2:$K$200,A13)</f>
         <v/>
       </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>lovely</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>사랑스러운</t>
+        </is>
+      </c>
+      <c r="I13" s="2">
+        <f>COUNTIF(perfumes!$M$2:$M$200,"*"&amp;G13&amp;"*")</f>
+        <v/>
+      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
           <t>strong</t>
@@ -17085,6 +17113,20 @@
       </c>
       <c r="E14" s="8">
         <f>COUNTIF(perfumes!$K$2:$K$200,A14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>sensual</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>관능적인</t>
+        </is>
+      </c>
+      <c r="I14" s="2">
+        <f>COUNTIF(perfumes!$M$2:$M$200,"*"&amp;G14&amp;"*")</f>
         <v/>
       </c>
     </row>

--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -663,6 +663,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
@@ -684,6 +685,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
@@ -694,7 +696,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>- 새 분위기 칩 '사랑스러운(lovely)', '관능적인(sensual)'을 추가하고, 어울리는 향수 40개의 moods에 붙였습니다 (AI 판단이므로 맡아본 느낌에 맞게 고쳐도 됩니다).</t>
+          <t>- 새 분위기 칩 '사랑스러운(lovely)', '매혹적인(sensual)'을 추가하고, 어울리는 향수 40개의 moods에 붙였습니다 (AI 판단이므로 맡아본 느낌에 맞게 고쳐도 됩니다).</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1005,11 @@
           <t>[확인 필요]</t>
         </is>
       </c>
-      <c r="AA2" s="6" t="n"/>
+      <c r="AA2" s="6" t="inlineStr">
+        <is>
+          <t>acqua-di-parma-colonia.jpeg</t>
+        </is>
+      </c>
       <c r="AB2" s="6" t="n"/>
       <c r="AC2" s="4" t="inlineStr">
         <is>
@@ -17122,7 +17128,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>관능적인</t>
+          <t>매혹적인</t>
         </is>
       </c>
       <c r="I14" s="2">

--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -663,7 +663,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
@@ -685,7 +684,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
@@ -1010,7 +1008,11 @@
           <t>acqua-di-parma-colonia.jpeg</t>
         </is>
       </c>
-      <c r="AB2" s="6" t="n"/>
+      <c r="AB2" s="6" t="inlineStr">
+        <is>
+          <t>https://kream.co.kr/products/226125</t>
+        </is>
+      </c>
       <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>AI 초안 (공식 확인 전)</t>

--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -11,10 +11,11 @@
     <sheet name="perfumes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="notes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="options" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="channels" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'perfumes'!$A$1:$AD$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'notes'!$A$1:$E$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'perfumes'!$A$1:$AD$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'notes'!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -488,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -695,6 +696,55 @@
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>- 새 분위기 칩 '사랑스러운(lovely)', '매혹적인(sensual)'을 추가하고, 어울리는 향수 40개의 moods에 붙였습니다 (AI 판단이므로 맡아본 느낌에 맞게 고쳐도 됩니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>■ 접근성 좋은 향수 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>- 백화점·올리브영 등에서 시향하기 쉬운 대중 브랜드 향수 15개를 추가했습니다 (총 114개). 같은 방식의 AI 초안이며 공식 확인 전입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>- polarizing(호불호) 기준: low=가벼움~보통 강도에 거부감 적은 계열, mid=개성 있지만 대중적, high=강한 구르망·레더·오우드·진한 꽃·향신료 위주. 판매순위는 기준으로 쓰지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>■ 시향 가능 채널(channels) 조사</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>- 브랜드 기준으로 웹 검색해 근거를 찾았습니다. 공식 사이트 대부분이 접속을 막아 근거가 검색 결과 요약 수준인 경우가 많습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>- channels_status가 '높음/보통'인 브랜드만 앱에 보여줍니다. '낮음/미확인'은 후보로만 남겼으니 직접 확인한 뒤 '높음 (앱에 표시)'로 바꾸면 앱에 나옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>- 향수별 재고가 아니라 브랜드 기준입니다. 근거는 channels 시트에 모아 두었습니다.</t>
         </is>
       </c>
     </row>
@@ -709,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD100"/>
+  <dimension ref="A1:AE115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -742,6 +792,7 @@
     <col width="28" customWidth="1" min="28" max="28"/>
     <col width="24" customWidth="1" min="29" max="29"/>
     <col width="36" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -893,6 +944,11 @@
       <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>todo</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>channels_status</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1056,7 @@
       </c>
       <c r="Z2" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA2" s="6" t="inlineStr">
@@ -1021,6 +1077,11 @@
       <c r="AD2" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE2" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1189,7 @@
       </c>
       <c r="Z3" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA3" s="6" t="n"/>
@@ -1141,6 +1202,11 @@
       <c r="AD3" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE3" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1314,7 @@
       </c>
       <c r="Z4" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA4" s="6" t="n"/>
@@ -1261,6 +1327,11 @@
       <c r="AD4" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE4" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -1383,6 +1454,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE5" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1488,7 +1564,7 @@
       </c>
       <c r="Z6" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 브랜드 매장</t>
         </is>
       </c>
       <c r="AA6" s="6" t="n"/>
@@ -1501,6 +1577,11 @@
       <c r="AD6" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE6" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1689,7 @@
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA7" s="6" t="n"/>
@@ -1623,6 +1704,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE7" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1765,6 +1851,11 @@
       <c r="AD8" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE8" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1963,7 @@
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA9" s="6" t="n"/>
@@ -1885,6 +1976,11 @@
       <c r="AD9" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE9" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -1992,7 +2088,7 @@
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA10" s="6" t="n"/>
@@ -2005,6 +2101,11 @@
       <c r="AD10" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE10" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -2127,6 +2228,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE11" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2232,7 +2338,7 @@
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 브랜드 매장</t>
         </is>
       </c>
       <c r="AA12" s="6" t="n"/>
@@ -2245,6 +2351,11 @@
       <c r="AD12" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE12" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2463,7 @@
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA13" s="6" t="n"/>
@@ -2365,6 +2476,11 @@
       <c r="AD13" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE13" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2588,7 @@
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA14" s="6" t="n"/>
@@ -2485,6 +2601,11 @@
       <c r="AD14" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE14" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2713,7 @@
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA15" s="6" t="n"/>
@@ -2605,6 +2726,11 @@
       <c r="AD15" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE15" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2838,7 @@
       </c>
       <c r="Z16" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA16" s="6" t="n"/>
@@ -2725,6 +2851,11 @@
       <c r="AD16" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE16" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2963,7 @@
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA17" s="6" t="n"/>
@@ -2845,6 +2976,11 @@
       <c r="AD17" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE17" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -2952,7 +3088,7 @@
       </c>
       <c r="Z18" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA18" s="6" t="n"/>
@@ -2965,6 +3101,11 @@
       <c r="AD18" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE18" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3217,7 @@
       </c>
       <c r="Z19" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA19" s="6" t="n"/>
@@ -3089,6 +3230,11 @@
       <c r="AD19" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE19" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3346,7 @@
       </c>
       <c r="Z20" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA20" s="6" t="n"/>
@@ -3213,6 +3359,11 @@
       <c r="AD20" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE20" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3471,7 @@
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA21" s="6" t="n"/>
@@ -3333,6 +3484,11 @@
       <c r="AD21" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE21" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3596,7 @@
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 브랜드 매장</t>
         </is>
       </c>
       <c r="AA22" s="6" t="n"/>
@@ -3453,6 +3609,11 @@
       <c r="AD22" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE22" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3721,7 @@
       </c>
       <c r="Z23" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA23" s="6" t="n"/>
@@ -3573,6 +3734,11 @@
       <c r="AD23" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE23" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3846,7 @@
       </c>
       <c r="Z24" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA24" s="6" t="n"/>
@@ -3693,6 +3859,11 @@
       <c r="AD24" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE24" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3975,7 @@
       </c>
       <c r="Z25" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA25" s="6" t="n"/>
@@ -3817,6 +3988,11 @@
       <c r="AD25" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE25" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -3924,7 +4100,7 @@
       </c>
       <c r="Z26" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA26" s="6" t="n"/>
@@ -3937,6 +4113,11 @@
       <c r="AD26" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE26" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4229,7 @@
       </c>
       <c r="Z27" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA27" s="6" t="n"/>
@@ -4061,6 +4242,11 @@
       <c r="AD27" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE27" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4358,7 @@
       </c>
       <c r="Z28" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA28" s="6" t="n"/>
@@ -4185,6 +4371,11 @@
       <c r="AD28" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE28" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4487,7 @@
       </c>
       <c r="Z29" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA29" s="6" t="n"/>
@@ -4309,6 +4500,11 @@
       <c r="AD29" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE29" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -4435,6 +4631,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE30" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -4575,6 +4776,11 @@
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
         </is>
       </c>
+      <c r="AE31" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4692,7 +4898,7 @@
       </c>
       <c r="Z32" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA32" s="6" t="inlineStr">
@@ -4713,6 +4919,11 @@
       <c r="AD32" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE32" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -4820,7 +5031,7 @@
       </c>
       <c r="Z33" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA33" s="6" t="n"/>
@@ -4833,6 +5044,11 @@
       <c r="AD33" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE33" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -4940,7 +5156,7 @@
       </c>
       <c r="Z34" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA34" s="6" t="n"/>
@@ -4953,6 +5169,11 @@
       <c r="AD34" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE34" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5281,7 @@
       </c>
       <c r="Z35" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA35" s="6" t="n"/>
@@ -5073,6 +5294,11 @@
       <c r="AD35" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE35" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5406,7 @@
       </c>
       <c r="Z36" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA36" s="6" t="n"/>
@@ -5193,6 +5419,11 @@
       <c r="AD36" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE36" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5531,7 @@
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA37" s="6" t="n"/>
@@ -5315,6 +5546,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE37" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -5436,7 +5672,7 @@
       </c>
       <c r="Z38" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA38" s="6" t="inlineStr">
@@ -5457,6 +5693,11 @@
       <c r="AD38" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE38" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5805,7 @@
       </c>
       <c r="Z39" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA39" s="6" t="n"/>
@@ -5577,6 +5818,11 @@
       <c r="AD39" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE39" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5934,7 @@
       </c>
       <c r="Z40" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA40" s="6" t="n"/>
@@ -5703,6 +5949,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE40" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -5841,6 +6092,11 @@
       <c r="AD41" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE41" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
         </is>
       </c>
     </row>
@@ -5952,7 +6208,7 @@
       </c>
       <c r="Z42" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA42" s="6" t="n"/>
@@ -5965,6 +6221,11 @@
       <c r="AD42" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE42" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6337,7 @@
       </c>
       <c r="Z43" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA43" s="6" t="n"/>
@@ -6089,6 +6350,11 @@
       <c r="AD43" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE43" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6462,7 @@
       </c>
       <c r="Z44" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA44" s="6" t="n"/>
@@ -6209,6 +6475,11 @@
       <c r="AD44" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE44" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6591,7 @@
       </c>
       <c r="Z45" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA45" s="6" t="n"/>
@@ -6333,6 +6604,11 @@
       <c r="AD45" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE45" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6720,7 @@
       </c>
       <c r="Z46" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA46" s="6" t="n"/>
@@ -6457,6 +6733,11 @@
       <c r="AD46" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE46" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6849,7 @@
       </c>
       <c r="Z47" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA47" s="6" t="n"/>
@@ -6581,6 +6862,11 @@
       <c r="AD47" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE47" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -6707,6 +6993,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE48" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -6828,7 +7119,7 @@
       </c>
       <c r="Z49" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA49" s="6" t="inlineStr">
@@ -6849,6 +7140,11 @@
       <c r="AD49" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE49" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -6960,7 +7256,7 @@
       </c>
       <c r="Z50" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA50" s="6" t="n"/>
@@ -6973,6 +7269,11 @@
       <c r="AD50" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE50" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7385,7 @@
       </c>
       <c r="Z51" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA51" s="6" t="n"/>
@@ -7099,6 +7400,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE51" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -7216,7 +7522,7 @@
       </c>
       <c r="Z52" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA52" s="6" t="inlineStr">
@@ -7237,6 +7543,11 @@
       <c r="AD52" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE52" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7671,7 @@
       </c>
       <c r="Z53" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA53" s="6" t="inlineStr">
@@ -7381,6 +7692,11 @@
       <c r="AD53" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE53" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7816,7 @@
       </c>
       <c r="Z54" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA54" s="6" t="inlineStr">
@@ -7521,6 +7837,11 @@
       <c r="AD54" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE54" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7961,7 @@
       </c>
       <c r="Z55" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA55" s="6" t="inlineStr">
@@ -7661,6 +7982,11 @@
       <c r="AD55" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE55" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -7772,7 +8098,7 @@
       </c>
       <c r="Z56" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA56" s="6" t="n"/>
@@ -7785,6 +8111,11 @@
       <c r="AD56" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE56" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -7896,7 +8227,7 @@
       </c>
       <c r="Z57" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA57" s="6" t="n"/>
@@ -7909,6 +8240,11 @@
       <c r="AD57" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE57" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8352,7 @@
       </c>
       <c r="Z58" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA58" s="6" t="n"/>
@@ -8029,6 +8365,11 @@
       <c r="AD58" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE58" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8477,7 @@
       </c>
       <c r="Z59" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA59" s="6" t="n"/>
@@ -8149,6 +8490,11 @@
       <c r="AD59" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE59" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8602,7 @@
       </c>
       <c r="Z60" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA60" s="6" t="n"/>
@@ -8269,6 +8615,11 @@
       <c r="AD60" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE60" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8727,7 @@
       </c>
       <c r="Z61" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA61" s="6" t="n"/>
@@ -8389,6 +8740,11 @@
       <c r="AD61" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE61" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8856,7 @@
       </c>
       <c r="Z62" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA62" s="6" t="n"/>
@@ -8513,6 +8869,11 @@
       <c r="AD62" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE62" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8985,7 @@
       </c>
       <c r="Z63" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA63" s="6" t="n"/>
@@ -8637,6 +8998,11 @@
       <c r="AD63" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE63" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8748,7 +9114,7 @@
       </c>
       <c r="Z64" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA64" s="6" t="n"/>
@@ -8761,6 +9127,11 @@
       <c r="AD64" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE64" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8872,7 +9243,7 @@
       </c>
       <c r="Z65" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA65" s="6" t="n"/>
@@ -8885,6 +9256,11 @@
       <c r="AD65" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE65" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -8996,7 +9372,7 @@
       </c>
       <c r="Z66" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA66" s="6" t="n"/>
@@ -9009,6 +9385,11 @@
       <c r="AD66" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE66" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9497,7 @@
       </c>
       <c r="Z67" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA67" s="6" t="n"/>
@@ -9129,6 +9510,11 @@
       <c r="AD67" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE67" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9622,7 @@
       </c>
       <c r="Z68" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA68" s="6" t="n"/>
@@ -9251,6 +9637,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE68" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -9368,7 +9759,7 @@
       </c>
       <c r="Z69" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA69" s="6" t="inlineStr">
@@ -9389,6 +9780,11 @@
       <c r="AD69" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 / 공식몰 한국 상품명: 사일런틀리, 휠 (Silently, Hwyl) (사용자 확인: 같은 제품)</t>
+        </is>
+      </c>
+      <c r="AE69" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9904,7 @@
       </c>
       <c r="Z70" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA70" s="6" t="inlineStr">
@@ -9529,6 +9925,11 @@
       <c r="AD70" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 / 공식몰 한국 상품명: 테싯 트루스 (Tacit Truths) (사용자 확인: 같은 제품)</t>
+        </is>
+      </c>
+      <c r="AE70" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -9651,6 +10052,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE71" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -9775,6 +10181,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE72" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -9880,7 +10291,7 @@
       </c>
       <c r="Z73" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA73" s="6" t="n"/>
@@ -9893,6 +10304,11 @@
       <c r="AD73" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE73" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10420,7 @@
       </c>
       <c r="Z74" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA74" s="6" t="n"/>
@@ -10017,6 +10433,11 @@
       <c r="AD74" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE74" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10549,7 @@
       </c>
       <c r="Z75" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA75" s="6" t="n"/>
@@ -10141,6 +10562,11 @@
       <c r="AD75" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE75" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10674,7 @@
       </c>
       <c r="Z76" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA76" s="6" t="n"/>
@@ -10261,6 +10687,11 @@
       <c r="AD76" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE76" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -10387,6 +10818,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE77" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -10507,6 +10943,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE78" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -10647,6 +11088,11 @@
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
         </is>
       </c>
+      <c r="AE79" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -10787,6 +11233,11 @@
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
         </is>
       </c>
+      <c r="AE80" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -10927,6 +11378,11 @@
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
         </is>
       </c>
+      <c r="AE81" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -11065,6 +11521,11 @@
       <c r="AD82" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 시향 가능 채널 (가격·이미지는 공식 페이지에서 반영됨)</t>
+        </is>
+      </c>
+      <c r="AE82" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11633,7 @@
       </c>
       <c r="Z83" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA83" s="6" t="n"/>
@@ -11185,6 +11646,11 @@
       <c r="AD83" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE83" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11758,7 @@
       </c>
       <c r="Z84" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA84" s="6" t="n"/>
@@ -11305,6 +11771,11 @@
       <c r="AD84" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE84" s="6" t="inlineStr">
+        <is>
+          <t>높음 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11887,7 @@
       </c>
       <c r="Z85" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA85" s="6" t="n"/>
@@ -11429,6 +11900,11 @@
       <c r="AD85" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE85" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11536,7 +12012,7 @@
       </c>
       <c r="Z86" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA86" s="6" t="n"/>
@@ -11549,6 +12025,11 @@
       <c r="AD86" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE86" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11660,7 +12141,7 @@
       </c>
       <c r="Z87" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA87" s="6" t="n"/>
@@ -11673,6 +12154,11 @@
       <c r="AD87" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE87" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11784,7 +12270,7 @@
       </c>
       <c r="Z88" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA88" s="6" t="n"/>
@@ -11797,6 +12283,11 @@
       <c r="AD88" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE88" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11908,7 +12399,7 @@
       </c>
       <c r="Z89" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA89" s="6" t="n"/>
@@ -11921,6 +12412,11 @@
       <c r="AD89" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE89" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12524,7 @@
       </c>
       <c r="Z90" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA90" s="6" t="n"/>
@@ -12041,6 +12537,11 @@
       <c r="AD90" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE90" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12649,7 @@
       </c>
       <c r="Z91" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA91" s="6" t="n"/>
@@ -12161,6 +12662,11 @@
       <c r="AD91" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE91" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12774,7 @@
       </c>
       <c r="Z92" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA92" s="6" t="n"/>
@@ -12281,6 +12787,11 @@
       <c r="AD92" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE92" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -12403,6 +12914,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE93" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -12512,7 +13028,7 @@
       </c>
       <c r="Z94" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA94" s="6" t="n"/>
@@ -12525,6 +13041,11 @@
       <c r="AD94" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE94" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -12624,7 +13145,7 @@
       </c>
       <c r="Z95" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA95" s="6" t="n"/>
@@ -12637,6 +13158,11 @@
       <c r="AD95" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE95" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -12736,7 +13262,7 @@
       </c>
       <c r="Z96" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA96" s="6" t="n"/>
@@ -12749,6 +13275,11 @@
       <c r="AD96" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE96" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -12848,7 +13379,7 @@
       </c>
       <c r="Z97" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>편집숍</t>
         </is>
       </c>
       <c r="AA97" s="6" t="n"/>
@@ -12861,6 +13392,11 @@
       <c r="AD97" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE97" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -12968,7 +13504,7 @@
       </c>
       <c r="Z98" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>면세점</t>
         </is>
       </c>
       <c r="AA98" s="6" t="n"/>
@@ -12981,6 +13517,11 @@
       <c r="AD98" s="4" t="inlineStr">
         <is>
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE98" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
     </row>
@@ -13107,6 +13648,11 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE99" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -13216,7 +13762,7 @@
       </c>
       <c r="Z100" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA100" s="6" t="n"/>
@@ -13231,9 +13777,1917 @@
           <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
         </is>
       </c>
+      <c r="AE100" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>versace-bright-crystal</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Versace</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>베르사체</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Bright Crystal</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>브라이트 크리스탈</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Yuzu, Pomegranate</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Magnolia, Peony, Lotus</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Musk, Amber, Woody Notes</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="n"/>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>fruity, musk</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>lovely, fresh, soft</t>
+        </is>
+      </c>
+      <c r="N101" s="5" t="n"/>
+      <c r="O101" s="5" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="P101" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q101" s="5" t="inlineStr">
+        <is>
+          <t>봄·여름 · 데일리</t>
+        </is>
+      </c>
+      <c r="R101" s="5" t="inlineStr">
+        <is>
+          <t>유자와 석류의 상큼함 뒤로 맑은 꽃이 이어지는 가벼운 향</t>
+        </is>
+      </c>
+      <c r="S101" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 부드러운 머스크가 가볍게 남아요</t>
+        </is>
+      </c>
+      <c r="T101" s="5" t="inlineStr">
+        <is>
+          <t>상큼한 첫 향이 꽃 향으로 바뀌는지 맡아보세요</t>
+        </is>
+      </c>
+      <c r="U101" s="6" t="n"/>
+      <c r="V101" s="6" t="n"/>
+      <c r="W101" s="6" t="n"/>
+      <c r="X101" s="6" t="n"/>
+      <c r="Y101" s="4" t="inlineStr">
+        <is>
+          <t>베르사체 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z101" s="6" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="AA101" s="6" t="n"/>
+      <c r="AB101" s="6" t="n"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD101" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE101" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>versace-eros</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Versace</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>베르사체</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Eros</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>에로스</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Mint, Apple, Lemon</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Tonka Bean, Geranium, Ambroxan</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Vanilla, Vetiver, Oakmoss, Cedar</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="n"/>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>aromatic</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>gourmand, woody</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>fresh, sweet, warm</t>
+        </is>
+      </c>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>tooSweet</t>
+        </is>
+      </c>
+      <c r="O102" s="5" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="P102" s="5" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="Q102" s="5" t="inlineStr">
+        <is>
+          <t>사계절 · 데이트</t>
+        </is>
+      </c>
+      <c r="R102" s="5" t="inlineStr">
+        <is>
+          <t>민트와 사과의 시원함에 바닐라가 더해진 달콤하고 강한 향</t>
+        </is>
+      </c>
+      <c r="S102" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 바닐라와 나무 향이 남아요</t>
+        </is>
+      </c>
+      <c r="T102" s="5" t="inlineStr">
+        <is>
+          <t>시원한 첫 향 뒤에 바닐라가 얼마나 달게 오는지 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U102" s="6" t="n"/>
+      <c r="V102" s="6" t="n"/>
+      <c r="W102" s="6" t="n"/>
+      <c r="X102" s="6" t="n"/>
+      <c r="Y102" s="4" t="inlineStr">
+        <is>
+          <t>베르사체 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z102" s="6" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="AA102" s="6" t="n"/>
+      <c r="AB102" s="6" t="n"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD102" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE102" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>paco-rabanne-1-million</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Paco Rabanne</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>파코 라반</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>1 Million</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>원 밀리언</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Grapefruit, Mint, Orange</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Cinnamon, Rose, Spices</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Amber, Leather, Patchouli, Woody Notes</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="n"/>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>amber</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>leather, spicy</t>
+        </is>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>warm, deep, sensual</t>
+        </is>
+      </c>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>tooSweet, tooStrong</t>
+        </is>
+      </c>
+      <c r="O103" s="5" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="P103" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q103" s="5" t="inlineStr">
+        <is>
+          <t>가을·겨울 · 저녁</t>
+        </is>
+      </c>
+      <c r="R103" s="5" t="inlineStr">
+        <is>
+          <t>계피와 가죽, 앰버가 어우러진 강하고 달콤한 향</t>
+        </is>
+      </c>
+      <c r="S103" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나도 달콤한 앰버와 가죽이 오래 남아요</t>
+        </is>
+      </c>
+      <c r="T103" s="5" t="inlineStr">
+        <is>
+          <t>가죽과 계피의 달콤함이 부담스럽지 않은지 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U103" s="6" t="n"/>
+      <c r="V103" s="6" t="n"/>
+      <c r="W103" s="6" t="n"/>
+      <c r="X103" s="6" t="n"/>
+      <c r="Y103" s="4" t="inlineStr">
+        <is>
+          <t>파코 라반 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z103" s="6" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="AA103" s="6" t="n"/>
+      <c r="AB103" s="6" t="n"/>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD103" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE103" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>paco-rabanne-lady-million</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Paco Rabanne</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>파코 라반</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Lady Million</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>레이디 밀리언</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Raspberry, Orange Blossom, Neroli</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>Jasmine, Honey, Gardenia</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Patchouli, Amber</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="n"/>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="inlineStr">
+        <is>
+          <t>whiteFloral, fruity</t>
+        </is>
+      </c>
+      <c r="M104" s="5" t="inlineStr">
+        <is>
+          <t>sweet, lovely, elegant</t>
+        </is>
+      </c>
+      <c r="N104" s="5" t="inlineStr">
+        <is>
+          <t>tooSweet</t>
+        </is>
+      </c>
+      <c r="O104" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P104" s="5" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="Q104" s="5" t="inlineStr">
+        <is>
+          <t>가을·겨울 · 저녁</t>
+        </is>
+      </c>
+      <c r="R104" s="5" t="inlineStr">
+        <is>
+          <t>라즈베리와 꿀, 하얀 꽃이 어우러진 화려하고 달콤한 향</t>
+        </is>
+      </c>
+      <c r="S104" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 달콤한 앰버와 패출리가 남아요</t>
+        </is>
+      </c>
+      <c r="T104" s="5" t="inlineStr">
+        <is>
+          <t>첫 향의 베리와 꿀의 달콤함을 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U104" s="6" t="n"/>
+      <c r="V104" s="6" t="n"/>
+      <c r="W104" s="6" t="n"/>
+      <c r="X104" s="6" t="n"/>
+      <c r="Y104" s="4" t="inlineStr">
+        <is>
+          <t>파코 라반 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z104" s="6" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="AA104" s="6" t="n"/>
+      <c r="AB104" s="6" t="n"/>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD104" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE104" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>hugo-boss-bottled</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Hugo Boss</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>휴고 보스</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Boss Bottled</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>보스 보틀드</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Apple, Bergamot, Lemon</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>Cinnamon, Geranium, Woody Notes</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Vanilla, Sandalwood, Vetiver, Cedar</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="n"/>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>woody</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>aromatic, spicy</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>calm, warm, fresh</t>
+        </is>
+      </c>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P105" s="5" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="Q105" s="5" t="inlineStr">
+        <is>
+          <t>사계절 · 출근</t>
+        </is>
+      </c>
+      <c r="R105" s="5" t="inlineStr">
+        <is>
+          <t>사과와 계피가 우디한 향으로 이어지는 단정한 클래식 향</t>
+        </is>
+      </c>
+      <c r="S105" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 부드러운 바닐라와 나무 향이 남아요</t>
+        </is>
+      </c>
+      <c r="T105" s="5" t="inlineStr">
+        <is>
+          <t>사과 향이 우디하게 바뀌는 흐름을 맡아보세요</t>
+        </is>
+      </c>
+      <c r="U105" s="6" t="n"/>
+      <c r="V105" s="6" t="n"/>
+      <c r="W105" s="6" t="n"/>
+      <c r="X105" s="6" t="n"/>
+      <c r="Y105" s="4" t="inlineStr">
+        <is>
+          <t>휴고 보스 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z105" s="6" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="AA105" s="6" t="n"/>
+      <c r="AB105" s="6" t="n"/>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD105" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE105" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>calvin-klein-eternity</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Calvin Klein</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>캘빈 클라인</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Eternity</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>이터니티</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Mandarin, Freesia, Sage</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>Lily of the Valley, Jasmine, Rose</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Sandalwood, Musk, Amber</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="n"/>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>musk</t>
+        </is>
+      </c>
+      <c r="M106" s="5" t="inlineStr">
+        <is>
+          <t>soft, elegant, clean</t>
+        </is>
+      </c>
+      <c r="N106" s="5" t="n"/>
+      <c r="O106" s="5" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="P106" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q106" s="5" t="inlineStr">
+        <is>
+          <t>봄 · 데일리</t>
+        </is>
+      </c>
+      <c r="R106" s="5" t="inlineStr">
+        <is>
+          <t>맑은 흰 꽃을 부드러운 머스크가 감싸는 깨끗한 향</t>
+        </is>
+      </c>
+      <c r="S106" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 부드러운 머스크와 샌달우드가 남아요</t>
+        </is>
+      </c>
+      <c r="T106" s="5" t="inlineStr">
+        <is>
+          <t>꽃 향이 은은하게 퍼지는지 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U106" s="6" t="n"/>
+      <c r="V106" s="6" t="n"/>
+      <c r="W106" s="6" t="n"/>
+      <c r="X106" s="6" t="n"/>
+      <c r="Y106" s="4" t="inlineStr">
+        <is>
+          <t>캘빈클라인 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z106" s="6" t="inlineStr">
+        <is>
+          <t>[확인 필요]</t>
+        </is>
+      </c>
+      <c r="AA106" s="6" t="n"/>
+      <c r="AB106" s="6" t="n"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD106" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE106" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>carolina-herrera-good-girl</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Carolina Herrera</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>캐롤리나 헤레라</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Good Girl</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>굿 걸</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Almond, Coffee, Bergamot</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>Tuberose, Jasmine, Orange Blossom</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Tonka Bean, Cacao, Vanilla, Sandalwood</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="n"/>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>whiteFloral</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>sweet, sensual, elegant</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>tooSweet, tooStrong</t>
+        </is>
+      </c>
+      <c r="O107" s="5" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="P107" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q107" s="5" t="inlineStr">
+        <is>
+          <t>가을·겨울 · 저녁</t>
+        </is>
+      </c>
+      <c r="R107" s="5" t="inlineStr">
+        <is>
+          <t>하얀 꽃과 카카오가 어우러진 진하고 달콤한 향</t>
+        </is>
+      </c>
+      <c r="S107" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나도 달콤한 통카빈과 카카오가 오래 남아요</t>
+        </is>
+      </c>
+      <c r="T107" s="5" t="inlineStr">
+        <is>
+          <t>꽃과 달콤함의 진한 정도를 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U107" s="6" t="n"/>
+      <c r="V107" s="6" t="n"/>
+      <c r="W107" s="6" t="n"/>
+      <c r="X107" s="6" t="n"/>
+      <c r="Y107" s="4" t="inlineStr">
+        <is>
+          <t>캐롤리나 헤레라 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z107" s="6" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="AA107" s="6" t="n"/>
+      <c r="AB107" s="6" t="n"/>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD107" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE107" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>ysl-y-edp</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Yves Saint Laurent</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>입생로랑</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Y Eau de Parfum</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>와이 오 드 퍼퓸</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Apple, Ginger, Bergamot</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>Sage, Juniper Berries, Geranium</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Ambroxan, Tonka Bean, Cedar, Vetiver</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="n"/>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>aromatic</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>woody, citrus</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>cool, fresh, deep</t>
+        </is>
+      </c>
+      <c r="N108" s="5" t="n"/>
+      <c r="O108" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P108" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q108" s="5" t="inlineStr">
+        <is>
+          <t>사계절 · 출근</t>
+        </is>
+      </c>
+      <c r="R108" s="5" t="inlineStr">
+        <is>
+          <t>사과와 생강의 상쾌함이 깔끔한 나무 향으로 이어지는 향</t>
+        </is>
+      </c>
+      <c r="S108" s="5" t="inlineStr">
+        <is>
+          <t>몇 시간 뒤엔 깨끗한 앰브록산과 나무 향이 남아요</t>
+        </is>
+      </c>
+      <c r="T108" s="5" t="inlineStr">
+        <is>
+          <t>상쾌한 첫 향이 깔끔하게 정리되는지 맡아보세요</t>
+        </is>
+      </c>
+      <c r="U108" s="6" t="n"/>
+      <c r="V108" s="6" t="n"/>
+      <c r="W108" s="6" t="n"/>
+      <c r="X108" s="6" t="n"/>
+      <c r="Y108" s="4" t="inlineStr">
+        <is>
+          <t>입생로랑 뷰티 백화점</t>
+        </is>
+      </c>
+      <c r="Z108" s="6" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="AA108" s="6" t="n"/>
+      <c r="AB108" s="6" t="n"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD108" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE108" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>lancome-idole</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Lancôme</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>랑콤</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Idôle</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>이돌</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Pear, Bergamot, Pink Pepper</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>Jasmine, Rose</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Vanilla, Musk, Cedar</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="n"/>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>floral</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>musk, fruity</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>lovely, soft, clean</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="n"/>
+      <c r="O109" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P109" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q109" s="5" t="inlineStr">
+        <is>
+          <t>봄·가을 · 데일리</t>
+        </is>
+      </c>
+      <c r="R109" s="5" t="inlineStr">
+        <is>
+          <t>배와 장미, 깨끗한 머스크가 어우러진 산뜻한 꽃 향</t>
+        </is>
+      </c>
+      <c r="S109" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 부드러운 머스크와 바닐라가 남아요</t>
+        </is>
+      </c>
+      <c r="T109" s="5" t="inlineStr">
+        <is>
+          <t>배와 장미의 균형을 손목에서 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U109" s="6" t="n"/>
+      <c r="V109" s="6" t="n"/>
+      <c r="W109" s="6" t="n"/>
+      <c r="X109" s="6" t="n"/>
+      <c r="Y109" s="4" t="inlineStr">
+        <is>
+          <t>랑콤 뷰티 백화점</t>
+        </is>
+      </c>
+      <c r="Z109" s="6" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="AA109" s="6" t="n"/>
+      <c r="AB109" s="6" t="n"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD109" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE109" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>montblanc-explorer</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Montblanc</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>몽블랑</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Explorer</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>익스플로러</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Bergamot, Pink Pepper, Clary Sage</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>Vetiver, Patchouli, Leather</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Ambroxan, Cashmeran</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="n"/>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>woody</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>aromatic, leather</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>calm, deep, fresh</t>
+        </is>
+      </c>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P110" s="5" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="Q110" s="5" t="inlineStr">
+        <is>
+          <t>사계절 · 출근</t>
+        </is>
+      </c>
+      <c r="R110" s="5" t="inlineStr">
+        <is>
+          <t>시트러스로 시작해 가죽과 우디로 이어지는 차분한 향</t>
+        </is>
+      </c>
+      <c r="S110" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 깨끗한 앰브록산과 나무 향이 남아요</t>
+        </is>
+      </c>
+      <c r="T110" s="5" t="inlineStr">
+        <is>
+          <t>가죽 느낌이 부담스럽지 않은지 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U110" s="6" t="n"/>
+      <c r="V110" s="6" t="n"/>
+      <c r="W110" s="6" t="n"/>
+      <c r="X110" s="6" t="n"/>
+      <c r="Y110" s="4" t="inlineStr">
+        <is>
+          <t>몽블랑 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z110" s="6" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="AA110" s="6" t="n"/>
+      <c r="AB110" s="6" t="n"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD110" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE110" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>armani-my-way</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Giorgio Armani</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>조르지오 아르마니</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>My Way</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>마이 웨이</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Bergamot, Orange Blossom</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>Tuberose, Jasmine</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>White Musk, Cedar, Vanilla</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="n"/>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>whiteFloral</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>musk</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>elegant, clean, soft</t>
+        </is>
+      </c>
+      <c r="N111" s="5" t="n"/>
+      <c r="O111" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P111" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q111" s="5" t="inlineStr">
+        <is>
+          <t>봄·가을 · 데이트</t>
+        </is>
+      </c>
+      <c r="R111" s="5" t="inlineStr">
+        <is>
+          <t>하얀 꽃과 머스크가 부드럽게 어우러진 깨끗한 꽃 향</t>
+        </is>
+      </c>
+      <c r="S111" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 보송한 화이트 머스크가 남아요</t>
+        </is>
+      </c>
+      <c r="T111" s="5" t="inlineStr">
+        <is>
+          <t>꽃 향이 진하지 않고 깨끗한지 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U111" s="6" t="n"/>
+      <c r="V111" s="6" t="n"/>
+      <c r="W111" s="6" t="n"/>
+      <c r="X111" s="6" t="n"/>
+      <c r="Y111" s="4" t="inlineStr">
+        <is>
+          <t>조르지오 아르마니 뷰티 백화점</t>
+        </is>
+      </c>
+      <c r="Z111" s="6" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="AA111" s="6" t="n"/>
+      <c r="AB111" s="6" t="n"/>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD111" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE111" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>bvlgari-omnia-crystalline</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Bvlgari</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>불가리</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Omnia Crystalline</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>옴니아 크리스탈린</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Bamboo, Pear</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>Lotus</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Woody Notes, Musk</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="n"/>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>aqua</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>green, musk</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
+          <t>clean, cool, soft</t>
+        </is>
+      </c>
+      <c r="N112" s="5" t="n"/>
+      <c r="O112" s="5" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="P112" s="5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="Q112" s="5" t="inlineStr">
+        <is>
+          <t>봄·여름 · 데일리</t>
+        </is>
+      </c>
+      <c r="R112" s="5" t="inlineStr">
+        <is>
+          <t>대나무와 연꽃처럼 맑고 투명한 물빛 향</t>
+        </is>
+      </c>
+      <c r="S112" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 가벼운 머스크와 나무 향이 남아요</t>
+        </is>
+      </c>
+      <c r="T112" s="5" t="inlineStr">
+        <is>
+          <t>투명한 첫 향이 얼마나 오래가는지 맡아보세요</t>
+        </is>
+      </c>
+      <c r="U112" s="6" t="n"/>
+      <c r="V112" s="6" t="n"/>
+      <c r="W112" s="6" t="n"/>
+      <c r="X112" s="6" t="n"/>
+      <c r="Y112" s="4" t="inlineStr">
+        <is>
+          <t>불가리 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z112" s="6" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="AA112" s="6" t="n"/>
+      <c r="AB112" s="6" t="n"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD112" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE112" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>ysl-mon-paris</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Yves Saint Laurent</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>입생로랑</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Mon Paris</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>몽 파리</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Strawberry, Raspberry, Pear</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Peony</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Patchouli, White Musk</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="n"/>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>floral, gourmand</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>sweet, lovely, elegant</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>tooSweet</t>
+        </is>
+      </c>
+      <c r="O113" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P113" s="5" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="Q113" s="5" t="inlineStr">
+        <is>
+          <t>봄·가을 · 데이트</t>
+        </is>
+      </c>
+      <c r="R113" s="5" t="inlineStr">
+        <is>
+          <t>딸기와 작약, 패출리가 어우러진 달콤한 향</t>
+        </is>
+      </c>
+      <c r="S113" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나면 화이트 머스크와 패출리가 남아요</t>
+        </is>
+      </c>
+      <c r="T113" s="5" t="inlineStr">
+        <is>
+          <t>딸기의 달콤함이 부담스럽지 않은지 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U113" s="6" t="n"/>
+      <c r="V113" s="6" t="n"/>
+      <c r="W113" s="6" t="n"/>
+      <c r="X113" s="6" t="n"/>
+      <c r="Y113" s="4" t="inlineStr">
+        <is>
+          <t>입생로랑 뷰티 백화점</t>
+        </is>
+      </c>
+      <c r="Z113" s="6" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="AA113" s="6" t="n"/>
+      <c r="AB113" s="6" t="n"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD113" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE113" s="6" t="inlineStr">
+        <is>
+          <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>prada-candy</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Prada</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>프라다</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Candy</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>캔디</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>Musk, Benzoin</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Vanilla</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="n"/>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>musk, amber</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
+          <t>sweet, cozy, warm</t>
+        </is>
+      </c>
+      <c r="N114" s="5" t="inlineStr">
+        <is>
+          <t>tooSweet</t>
+        </is>
+      </c>
+      <c r="O114" s="5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P114" s="5" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="Q114" s="5" t="inlineStr">
+        <is>
+          <t>가을·겨울 · 데일리</t>
+        </is>
+      </c>
+      <c r="R114" s="5" t="inlineStr">
+        <is>
+          <t>카라멜 사탕처럼 달콤하고 포근한 향</t>
+        </is>
+      </c>
+      <c r="S114" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나도 달콤한 바닐라와 머스크가 남아요</t>
+        </is>
+      </c>
+      <c r="T114" s="5" t="inlineStr">
+        <is>
+          <t>카라멜의 달콤함이 얼마나 진한지 확인해 보세요</t>
+        </is>
+      </c>
+      <c r="U114" s="6" t="n"/>
+      <c r="V114" s="6" t="n"/>
+      <c r="W114" s="6" t="n"/>
+      <c r="X114" s="6" t="n"/>
+      <c r="Y114" s="4" t="inlineStr">
+        <is>
+          <t>프라다 뷰티 백화점</t>
+        </is>
+      </c>
+      <c r="Z114" s="6" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="AA114" s="6" t="n"/>
+      <c r="AB114" s="6" t="n"/>
+      <c r="AC114" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD114" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE114" s="6" t="inlineStr">
+        <is>
+          <t>낮음 (앱에 표시 안 함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>mugler-alien</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Mugler</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>뮈글러</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Alien</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>에일리언</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Jasmine</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>Cashmeran</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="n"/>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>whiteFloral</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>woody, amber</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>elegant, deep, sensual</t>
+        </is>
+      </c>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>tooStrong</t>
+        </is>
+      </c>
+      <c r="O115" s="5" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="P115" s="5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Q115" s="5" t="inlineStr">
+        <is>
+          <t>가을·겨울 · 저녁</t>
+        </is>
+      </c>
+      <c r="R115" s="5" t="inlineStr">
+        <is>
+          <t>진한 자스민과 따뜻한 나무가 어우러진 개성 있는 향</t>
+        </is>
+      </c>
+      <c r="S115" s="5" t="inlineStr">
+        <is>
+          <t>시간이 지나도 따뜻한 앰버가 오래 남아요</t>
+        </is>
+      </c>
+      <c r="T115" s="5" t="inlineStr">
+        <is>
+          <t>향이 진하니 소량만 뿌려 맡아보세요</t>
+        </is>
+      </c>
+      <c r="U115" s="6" t="n"/>
+      <c r="V115" s="6" t="n"/>
+      <c r="W115" s="6" t="n"/>
+      <c r="X115" s="6" t="n"/>
+      <c r="Y115" s="4" t="inlineStr">
+        <is>
+          <t>뮈글러 향수 매장</t>
+        </is>
+      </c>
+      <c r="Z115" s="6" t="inlineStr">
+        <is>
+          <t>[확인 필요]</t>
+        </is>
+      </c>
+      <c r="AA115" s="6" t="n"/>
+      <c r="AB115" s="6" t="n"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>AI 초안 (공식 확인 전)</t>
+        </is>
+      </c>
+      <c r="AD115" s="4" t="inlineStr">
+        <is>
+          <t>노트·농도 공식 확인 / 국내 정가 / 이미지 / 시향 가능 채널</t>
+        </is>
+      </c>
+      <c r="AE115" s="6" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD100"/>
+  <autoFilter ref="A1:AD115"/>
   <dataValidations count="3">
     <dataValidation sqref="K2:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=options!$A$3:$A$16</formula1>
@@ -13255,7 +15709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13314,7 +15768,7 @@
         </is>
       </c>
       <c r="E2" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A2&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A2&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13340,7 +15794,7 @@
         </is>
       </c>
       <c r="E3" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A3&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A3&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13366,7 +15820,7 @@
         </is>
       </c>
       <c r="E4" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A4&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A4&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13392,7 +15846,7 @@
         </is>
       </c>
       <c r="E5" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A5&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A5&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13418,7 +15872,7 @@
         </is>
       </c>
       <c r="E6" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A6&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A6&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13444,7 +15898,7 @@
         </is>
       </c>
       <c r="E7" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A7&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A7&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13470,7 +15924,7 @@
         </is>
       </c>
       <c r="E8" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A8&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A8&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13496,7 +15950,7 @@
         </is>
       </c>
       <c r="E9" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A9&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A9&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13522,7 +15976,7 @@
         </is>
       </c>
       <c r="E10" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A10&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A10&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13548,7 +16002,7 @@
         </is>
       </c>
       <c r="E11" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A11&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A11&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13574,7 +16028,7 @@
         </is>
       </c>
       <c r="E12" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A12&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A12&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13600,7 +16054,7 @@
         </is>
       </c>
       <c r="E13" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A13&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A13&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13626,7 +16080,7 @@
         </is>
       </c>
       <c r="E14" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A14&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A14&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13652,7 +16106,7 @@
         </is>
       </c>
       <c r="E15" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A15&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A15&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13678,7 +16132,7 @@
         </is>
       </c>
       <c r="E16" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A16&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A16&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13704,7 +16158,7 @@
         </is>
       </c>
       <c r="E17" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A17&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A17&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13730,7 +16184,7 @@
         </is>
       </c>
       <c r="E18" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A18&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A18&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13756,7 +16210,7 @@
         </is>
       </c>
       <c r="E19" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A19&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A19&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13782,7 +16236,7 @@
         </is>
       </c>
       <c r="E20" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A20&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A20&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13808,7 +16262,7 @@
         </is>
       </c>
       <c r="E21" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A21&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A21&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13834,7 +16288,7 @@
         </is>
       </c>
       <c r="E22" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A22&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A22&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13860,7 +16314,7 @@
         </is>
       </c>
       <c r="E23" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A23&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A23&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13886,7 +16340,7 @@
         </is>
       </c>
       <c r="E24" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A24&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A24&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13912,7 +16366,7 @@
         </is>
       </c>
       <c r="E25" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A25&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A25&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13938,7 +16392,7 @@
         </is>
       </c>
       <c r="E26" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A26&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A26&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13964,7 +16418,7 @@
         </is>
       </c>
       <c r="E27" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A27&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A27&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -13990,7 +16444,7 @@
         </is>
       </c>
       <c r="E28" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A28&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A28&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14016,7 +16470,7 @@
         </is>
       </c>
       <c r="E29" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A29&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A29&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14042,7 +16496,7 @@
         </is>
       </c>
       <c r="E30" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A30&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A30&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14068,7 +16522,7 @@
         </is>
       </c>
       <c r="E31" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A31&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A31&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14094,7 +16548,7 @@
         </is>
       </c>
       <c r="E32" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A32&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A32&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14120,7 +16574,7 @@
         </is>
       </c>
       <c r="E33" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A33&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A33&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14146,7 +16600,7 @@
         </is>
       </c>
       <c r="E34" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A34&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A34&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14172,7 +16626,7 @@
         </is>
       </c>
       <c r="E35" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A35&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A35&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14198,7 +16652,7 @@
         </is>
       </c>
       <c r="E36" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A36&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A36&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14224,7 +16678,7 @@
         </is>
       </c>
       <c r="E37" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A37&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A37&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14250,7 +16704,7 @@
         </is>
       </c>
       <c r="E38" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A38&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A38&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14276,7 +16730,7 @@
         </is>
       </c>
       <c r="E39" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A39&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A39&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14302,7 +16756,7 @@
         </is>
       </c>
       <c r="E40" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A40&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A40&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14328,7 +16782,7 @@
         </is>
       </c>
       <c r="E41" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A41&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A41&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14354,7 +16808,7 @@
         </is>
       </c>
       <c r="E42" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A42&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A42&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14380,7 +16834,7 @@
         </is>
       </c>
       <c r="E43" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A43&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A43&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14406,7 +16860,7 @@
         </is>
       </c>
       <c r="E44" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A44&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A44&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14432,7 +16886,7 @@
         </is>
       </c>
       <c r="E45" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A45&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A45&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14458,7 +16912,7 @@
         </is>
       </c>
       <c r="E46" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A46&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A46&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14484,7 +16938,7 @@
         </is>
       </c>
       <c r="E47" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A47&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A47&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14510,7 +16964,7 @@
         </is>
       </c>
       <c r="E48" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A48&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A48&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14536,7 +16990,7 @@
         </is>
       </c>
       <c r="E49" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A49&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A49&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14562,7 +17016,7 @@
         </is>
       </c>
       <c r="E50" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A50&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A50&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14588,7 +17042,7 @@
         </is>
       </c>
       <c r="E51" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A51&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A51&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14614,7 +17068,7 @@
         </is>
       </c>
       <c r="E52" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A52&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A52&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14640,7 +17094,7 @@
         </is>
       </c>
       <c r="E53" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A53&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A53&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14666,7 +17120,7 @@
         </is>
       </c>
       <c r="E54" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A54&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A54&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14692,7 +17146,7 @@
         </is>
       </c>
       <c r="E55" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A55&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A55&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14718,7 +17172,7 @@
         </is>
       </c>
       <c r="E56" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A56&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A56&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14744,7 +17198,7 @@
         </is>
       </c>
       <c r="E57" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A57&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A57&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14770,7 +17224,7 @@
         </is>
       </c>
       <c r="E58" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A58&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A58&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14796,7 +17250,7 @@
         </is>
       </c>
       <c r="E59" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A59&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A59&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14822,7 +17276,7 @@
         </is>
       </c>
       <c r="E60" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A60&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A60&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14848,7 +17302,7 @@
         </is>
       </c>
       <c r="E61" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A61&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A61&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14874,7 +17328,7 @@
         </is>
       </c>
       <c r="E62" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A62&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A62&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14900,7 +17354,7 @@
         </is>
       </c>
       <c r="E63" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A63&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A63&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14926,7 +17380,7 @@
         </is>
       </c>
       <c r="E64" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A64&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A64&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14952,7 +17406,7 @@
         </is>
       </c>
       <c r="E65" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A65&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A65&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -14978,7 +17432,7 @@
         </is>
       </c>
       <c r="E66" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A66&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A66&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15004,7 +17458,7 @@
         </is>
       </c>
       <c r="E67" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A67&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A67&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15030,7 +17484,7 @@
         </is>
       </c>
       <c r="E68" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A68&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A68&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15056,7 +17510,7 @@
         </is>
       </c>
       <c r="E69" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A69&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A69&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15082,7 +17536,7 @@
         </is>
       </c>
       <c r="E70" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A70&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A70&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15108,7 +17562,7 @@
         </is>
       </c>
       <c r="E71" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A71&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A71&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15134,7 +17588,7 @@
         </is>
       </c>
       <c r="E72" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A72&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A72&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15160,7 +17614,7 @@
         </is>
       </c>
       <c r="E73" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A73&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A73&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15186,7 +17640,7 @@
         </is>
       </c>
       <c r="E74" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A74&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A74&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15212,7 +17666,7 @@
         </is>
       </c>
       <c r="E75" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A75&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A75&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15238,7 +17692,7 @@
         </is>
       </c>
       <c r="E76" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A76&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A76&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15264,7 +17718,7 @@
         </is>
       </c>
       <c r="E77" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A77&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A77&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15290,7 +17744,7 @@
         </is>
       </c>
       <c r="E78" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A78&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A78&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15316,7 +17770,7 @@
         </is>
       </c>
       <c r="E79" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A79&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A79&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15342,7 +17796,7 @@
         </is>
       </c>
       <c r="E80" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A80&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A80&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15368,7 +17822,7 @@
         </is>
       </c>
       <c r="E81" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A81&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A81&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15394,7 +17848,7 @@
         </is>
       </c>
       <c r="E82" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A82&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A82&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15420,7 +17874,7 @@
         </is>
       </c>
       <c r="E83" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A83&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A83&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15446,7 +17900,7 @@
         </is>
       </c>
       <c r="E84" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A84&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A84&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15472,7 +17926,7 @@
         </is>
       </c>
       <c r="E85" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A85&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A85&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15498,7 +17952,7 @@
         </is>
       </c>
       <c r="E86" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A86&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A86&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15524,7 +17978,7 @@
         </is>
       </c>
       <c r="E87" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A87&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A87&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15550,7 +18004,7 @@
         </is>
       </c>
       <c r="E88" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A88&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A88&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15576,7 +18030,7 @@
         </is>
       </c>
       <c r="E89" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A89&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A89&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15602,7 +18056,7 @@
         </is>
       </c>
       <c r="E90" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A90&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A90&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15628,7 +18082,7 @@
         </is>
       </c>
       <c r="E91" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A91&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A91&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15654,7 +18108,7 @@
         </is>
       </c>
       <c r="E92" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A92&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A92&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15680,7 +18134,7 @@
         </is>
       </c>
       <c r="E93" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A93&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A93&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15706,7 +18160,7 @@
         </is>
       </c>
       <c r="E94" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A94&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A94&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15732,7 +18186,7 @@
         </is>
       </c>
       <c r="E95" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A95&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A95&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15758,7 +18212,7 @@
         </is>
       </c>
       <c r="E96" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A96&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A96&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15784,7 +18238,7 @@
         </is>
       </c>
       <c r="E97" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A97&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A97&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15810,7 +18264,7 @@
         </is>
       </c>
       <c r="E98" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A98&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A98&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15836,7 +18290,7 @@
         </is>
       </c>
       <c r="E99" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A99&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A99&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15862,7 +18316,7 @@
         </is>
       </c>
       <c r="E100" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A100&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A100&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15888,7 +18342,7 @@
         </is>
       </c>
       <c r="E101" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A101&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A101&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15914,7 +18368,7 @@
         </is>
       </c>
       <c r="E102" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A102&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A102&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15940,7 +18394,7 @@
         </is>
       </c>
       <c r="E103" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A103&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A103&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15966,7 +18420,7 @@
         </is>
       </c>
       <c r="E104" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A104&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A104&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -15992,7 +18446,7 @@
         </is>
       </c>
       <c r="E105" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A105&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A105&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16018,7 +18472,7 @@
         </is>
       </c>
       <c r="E106" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A106&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A106&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16044,7 +18498,7 @@
         </is>
       </c>
       <c r="E107" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A107&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A107&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16070,7 +18524,7 @@
         </is>
       </c>
       <c r="E108" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A108&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A108&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16096,7 +18550,7 @@
         </is>
       </c>
       <c r="E109" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A109&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A109&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16122,7 +18576,7 @@
         </is>
       </c>
       <c r="E110" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A110&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A110&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16148,7 +18602,7 @@
         </is>
       </c>
       <c r="E111" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A111&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A111&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16174,7 +18628,7 @@
         </is>
       </c>
       <c r="E112" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A112&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A112&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16200,7 +18654,7 @@
         </is>
       </c>
       <c r="E113" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A113&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A113&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16226,7 +18680,7 @@
         </is>
       </c>
       <c r="E114" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A114&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A114&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16252,7 +18706,7 @@
         </is>
       </c>
       <c r="E115" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A115&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A115&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16278,7 +18732,7 @@
         </is>
       </c>
       <c r="E116" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A116&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A116&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16304,7 +18758,7 @@
         </is>
       </c>
       <c r="E117" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A117&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A117&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16330,7 +18784,7 @@
         </is>
       </c>
       <c r="E118" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A118&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A118&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16356,7 +18810,7 @@
         </is>
       </c>
       <c r="E119" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A119&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A119&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16382,7 +18836,7 @@
         </is>
       </c>
       <c r="E120" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A120&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A120&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16408,7 +18862,7 @@
         </is>
       </c>
       <c r="E121" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A121&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A121&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16434,7 +18888,7 @@
         </is>
       </c>
       <c r="E122" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A122&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A122&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16460,7 +18914,7 @@
         </is>
       </c>
       <c r="E123" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A123&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A123&amp;"*")</f>
         <v/>
       </c>
     </row>
@@ -16486,12 +18940,64 @@
         </is>
       </c>
       <c r="E124" s="8">
-        <f>COUNTIF(perfumes!$G$2:$I$100,"*"&amp;A124&amp;"*")</f>
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A124&amp;"*")</f>
         <v/>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Gardenia</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>가드니아</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>크리미하고 진한 하얀 꽃 향</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>whiteFloral</t>
+        </is>
+      </c>
+      <c r="E125" s="8">
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A125&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>석류</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>새콤달콤한 붉은 열매 향</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>fruity</t>
+        </is>
+      </c>
+      <c r="E126" s="8">
+        <f>COUNTIF(perfumes!$G$2:$I$115,"*"&amp;A126&amp;"*")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E124"/>
+  <autoFilter ref="A1:E126"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=options!$A$3:$A$16</formula1>
@@ -17237,4 +19743,1574 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>신뢰도</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>앱에 표시</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>후보 채널(조사 결과)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>근거 URL</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>조사 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Acqua di Parma</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.acquadiparma.com/default/en/authorised-retailers.html</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Official page itself 403 on fetch; seen via search snippet. Dept-store boutique (Lotte Jamsil Avenuel) only seen in news articles (not allowed source), so not recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Aesop</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>브랜드 매장</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aesop.com/us/r/aesop-garosu-gil</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Own-brand stores verified via aesop.com search results; dept-store counters not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Annick Goutal</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.apgroup.com/int/ko/news/brand-2016-04-250.html</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Source is Amorepacific (brand owner) 2016 press page; current status of stores not re-verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Atelier Cologne</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Only news/magazine sources (Lotte Jamsil boutique, re-entered Korea 2026) seen; no allowed official source verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Burberry</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>stores.burberry.com Hyundai Seoul page lists no beauty/fragrance service; Beauty Box COEX only from non-allowed article. Unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Bvlgari</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bulgari.com/ko-kr/storelocator/대한민국/gyeonggi-do/gyeonggido/galleria-gwanggyo-store</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Store-locator pages seen via search snippets only (fetch 403). Some are jewelry/parfums boutiques inside dept stores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Byredo</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Flagship stores (Sinsa, Lotte World Mall) only in news sources (fashionbiz, insideretail), not allowed; official site fetch 404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Calvin Klein</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>No oliveyoung.co.kr or official evidence found; only marketplace results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Carolina Herrera</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>https://m-shinsegaemall.ssg.com/mall/disp/brandMain?brandId=3000023035</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Weak: online mall brand page only; offline counter not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Chanel</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.chanel.com/kr/storelocator/store/shinsegae-myeongdong-chanel-fragrance-beauty-counter-16719/</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Fragrance &amp; beauty counters in dept stores; search summary also mentioned duty-free counters (Gimpo, World Tower) but no specific URL seen, so 면세점 not recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Chloé</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>No allowed source verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Creed</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.shilladfs.com/estore/kr/en/p/3390883</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Shilla Duty Free online store listing (pages 403 on fetch); online listing, store counter implied but not confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Davidoff</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>No allowed source verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Dior</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>면세점, 백화점</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>https://m.lotteshopping.com/search/searchResult?cstrCd=0002&amp;searchTerm=%EB%94%94%EC%98%AC
+https://m.shilladfs.com/estore/kr/ko/Skin-Care/%eb%94%94%ec%98%ac/Womens-Fragrance/Miss-Dior/c/D711
+https://www.ssgdfs.com/kr/dispctg/brand/dior</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Snippet-level evidence only. Dior store finder (dior.com/en_us/beauty/find-your-dior-store) exists but could not be fetched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Diptyque</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>면세점, 브랜드 매장</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>https://m.shilladfs.com/estore/kr/en/p/5623016
+https://stores.diptyqueparis.com/en_eu/diptyque-garosugil</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Official store locator lists 2 boutiques (Garosugil, Seongsu). Lotte Dept Store search snippet (m.lotteshopping.com cstrCd=0022) showed 딥티크 in a brand list but department-store channel not firmly verified, so omitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Dolce &amp; Gabbana</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>면세점, 올리브영</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>https://m.oliveyoung.co.kr/m/mtn/brand/A000130
+https://www.etoday.co.kr/news/view/2315438</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Olive Young verified. Duty-free is from a news article only (weak), so excluded from the channel list... see evidence; channels list kept to 올리브영.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Escentric Molecules</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>https://m.shilladfs.com/estore/kr/en/b/escentricmolecules</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Only duty free (online brand page) verified; no offline store evidence found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Ex Nihilo</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>https://m.shilladfs.com/estore/kr/ko/b/exnihilo</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>News snippets (hankyung, heraldk) indicate Shinsegae/Lotte/Hyundai department store counters but those are not allowed source types, so 백화점 left out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Frédéric Malle</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>https://m.shilladfs.com/estore/kr/ko/b/fredericmalle</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Official site fredericmalle.com/kr appeared in results but store list not fetched; Vogue Korea (not allowed) mentions an Itaewon flagship, so 브랜드 매장 unverified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Giorgio Armani</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.shilladfs.com/estore/kr/ko/b/giorgioarmani</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Department store (Shinsegae Gangnam Armani Beauty Store) only from a news article, so not recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Gucci</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>면세점, 백화점</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>https://m.lotteshopping.com/store/brand/detail?cstrCd=0341&amp;brndCd=0044501&amp;cstrShopNo=SHP00000000000064859&amp;flrCd=01
+https://m.shilladfs.com/estore/kr/ko/b/guccifragrance</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Snippet-level; Gucci Beauty counter in Lotte Dept Store inferred from brand-detail page title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Guerlain</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.guerlain.com/kr/ko-kr/c/kr-guerlain-services.html</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Fetch was 403; relied on search snippet of official page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>https://m.shilladfs.com/estore/kr/ko/b/hermes</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>hermes.com lists many Korean boutiques (Shinsegae Main/Gangnam, Hyundai Apgujeong, Dosan Maison) but pages did not state perfume is sold there; Shinsegae Main perfume boutique only in news. So 백화점/브랜드 매장 not recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Hugo Boss</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ehyundai.com/newPortal/DP/FG/FG000000_V.do?branchCd=B00122000</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Likely the fashion store; fragrance counter not confirmed. Shinsegae brand page also exists (brandId=2000002977). No Olive Young evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Initio</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>No allowed-source evidence found (only SSG.com marketplace listings and foreign retailers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Jean Paul Gaultier</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>면세점</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.shilladfs.com/comm/kr/ko/brandView?brand_cd=0232</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Olive Young and department store not verified (search only returned generic Olive Young perfume category).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Jo Malone London</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>백화점, 브랜드 매장</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.jomalone.co.kr/store/1449960/%EC%84%9C%EC%9A%B8%ED%8A%B9%EB%B3%84%EC%8B%9C/%EC%9A%A9%EC%82%B0%EA%B5%AC/4348
+https://www.jomalone.co.kr/trust-mark</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Evidence from search-result summaries of official site, not fetched pages (403).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Juliette Has a Gun</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>편집숍</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>https://chicor.com/brand/0000000886</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Chicor page is online brand listing; offline SIKOR stock not confirmed. Only a temporary 더현대 서울 팝업 (Aug 2026, ended 8/13) found, not counted. Olive Young not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Kilian Paris</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>https://m.lotteshopping.com/shoppingNews/shoppingNewsDetail?shpgNewsNo=SNM00000000000094668</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Lotte news item described a period opening (Aug 18-31); current permanence unverified. Other stores not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Lancôme</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>백화점, 면세점</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>https://m.shilladfs.com/estore/kr/ko/p/5980374
+https://www.ehyundai.com/newPortal/DP/FG/FG000000_V.do?branchCd=B00142000</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Hyundai evidence from search summary; Shilla DFS is online duty-free shop, counters implied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Le Labo</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>브랜드 매장</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lelabofragrances.co.kr/_seoul-boutiques.html</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Standalone boutiques only; department store counters not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Maison Francis Kurkdjian</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.shinsegae.com/store/floor.do</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Also 롯데 잠실점 per hankyung article (not an allowed source). Evidence is search summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Maison Margiela</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>https://m.lotteshopping.com/search/searchResult?cstrCd=0349&amp;searchTerm=%28
+https://www.ehyundai.com/newPortal/DP/FG/FG000000_V.do?branchCd=B00140000</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Evidence from search summaries of department store sites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Marc Jacobs</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>https://m.oliveyoung.co.kr/m/display/getBrandShopDetail.do?onlBrndCd=A000265</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Online listing; offline store stock not confirmed. Department store not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Montblanc</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>올리브영, 백화점</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ehyundai.com/newPortal/DP/FG/FG000000_V.do?branchCd=B00122000
+https://www.oliveyoung.co.kr/store/display/getBrandShopDetail.do?onlBrndCd=A000646</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Department store entry is probably the main (non-fragrance) Montblanc boutique; fragrance counter unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Mugler</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>No verified channel found in allowed sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Narciso Rodriguez</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/display/getBrandShopDetail.do?onlBrndCd=A000586</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Online listing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Nishane</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>No Korean retail evidence found in allowed sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Paco Rabanne</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/search/getSearchMain.do?query=%ED%8C%8C%EC%BD%94%EB%9D%BC%EB%B0%98&amp;onlyOneBrand=A000085&amp;onlBrndCd=A000085</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Only a search-result title seen; page fetch blocked. Shinsegae mall also listed (online).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Parfums de Marly</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Only SSG.com online listings of '퍼퓸드말리 공식수입정품' via 신세계백화점 mall; physical counter not verified (a floor-guide hit was unreliable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Penhaligon's</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>https://m.thehyundai.com/front/dpa/searchSectItem.thd?sectId=219475</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Hyundai Seoul and Hyundai Trade Center per Hankyung article (news, not an allowed source, corroboration only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Prada</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>https://department.ssg.com/disp/brandShop.ssg?brandId=3000082132</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Weak: department-store brand page may be online mall only; news (not allowed source) says Prada Beauty counters at Shinsegae Gangnam and The Hyundai Seoul plus a Seongsu standalone store. No Olive Young evidence; standalone store not verified from an allowed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Tom Ford</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.galleria.co.kr/dispctg/initBrandShop.action?shop_brand_no=37914
+https://www.thehyundai.com/front/dpa/searchSectItem.thd?brndCd=MA03329</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Beauty/fragrance line only; brand pages may be online listings; news says counters at Galleria Apgujeong, Hyundai, Shinsegae Gangnam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Versace</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/display/getBrandShopDetail.do?onlBrndCd=A000040</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Online brand page verified; in-store testing not confirmed. Department store not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Viktor&amp;Rolf</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>https://shinsegaemall.ssg.com/disp/brandShop.ssg?brandId=2000007203</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Weak: only online Shinsegae brand page found; offline counter not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Xerjoff</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>표시 안 함</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.galleria.co.kr/dispctg/initBrandShop.action?shop_brand_no=2300008554
+https://www.thehyundai.com/front/dpa/searchSectItem.thd?brndCd=MA14910&amp;pSectId=30064</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Weak: online brand listings; physical counters not confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Yves Saint Laurent</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>표시</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>백화점</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>https://department.ssg.com/disp/brandShop.ssg?brandId=2011010625
+https://m.lotteshopping.com/store/floor/detail?cstrCd=0016&amp;cstrTownCd=C00401&amp;flrCd=01</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Official site yslbeautykr.com lists customer care for store finding (080-835-0089) but fetch was 403; no Olive Young evidence.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, calm</t>
+          <t>clean, fresh, calm, cool, zesty</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>clean, zesty, elegant</t>
+          <t>clean, zesty, elegant, cool, fresh</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, clean</t>
+          <t>zesty, fresh, clean, cool</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, zesty</t>
+          <t>clean, fresh, zesty, cool</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, fresh, lovely</t>
+          <t>soft, elegant, fresh, lovely, zesty, sweet</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>soft, sweet, elegant, lovely</t>
+          <t>soft, sweet, elegant, lovely, fresh, zesty</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>sweet, cozy, warm, lovely</t>
+          <t>sweet, cozy, warm, lovely, fresh, zesty</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>soft, sweet, zesty, lovely</t>
+          <t>soft, sweet, zesty, lovely, fresh</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm, sweet</t>
+          <t>elegant, warm, sweet, fresh, zesty, lovely</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>cool, calm, fresh</t>
+          <t>cool, calm, fresh, clean</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>fresh, calm, soft</t>
+          <t>fresh, calm, soft, cool</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, calm</t>
+          <t>fresh, clean, calm, cool</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr"/>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>cool, deep, fresh</t>
+          <t>cool, deep, fresh, calm</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, sweet</t>
+          <t>cozy, warm, sweet, calm</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm, fresh</t>
+          <t>elegant, warm, fresh, lovely</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>elegant, sweet, soft, lovely</t>
+          <t>elegant, sweet, soft, lovely, clean</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr"/>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, lovely</t>
+          <t>elegant, soft, lovely, clean</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, calm</t>
+          <t>elegant, soft, calm, clean, lovely</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>elegant, calm</t>
+          <t>elegant, calm, clean, lovely</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>calm, soft, elegant</t>
+          <t>calm, soft, elegant, cozy, lovely</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>calm, deep, soft</t>
+          <t>calm, deep, soft, cozy, elegant</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, calm, lovely</t>
+          <t>soft, elegant, calm, lovely, cozy</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm</t>
+          <t>clean, soft, calm, cozy</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, cozy</t>
+          <t>clean, soft, cozy, calm</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, warm</t>
+          <t>soft, elegant, warm, calm, clean, cozy</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>soft, clean, calm</t>
+          <t>soft, clean, calm, cozy</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>fresh, warm, sweet</t>
+          <t>fresh, warm, sweet, calm, clean, cozy, soft</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>deep, calm, warm</t>
+          <t>deep, calm, warm, sensual</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, deep</t>
+          <t>calm, cozy, deep, warm</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant, sensual</t>
+          <t>deep, warm, elegant, sensual, calm</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, soft</t>
+          <t>calm, cozy, soft, warm, deep</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, sweet, sensual</t>
+          <t>warm, elegant, sweet, sensual, cozy, deep</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, elegant, sensual</t>
+          <t>warm, deep, elegant, sensual, cozy, sweet</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, soft</t>
+          <t>warm, elegant, soft, cozy, sweet, deep</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>sweet, deep, warm, sensual</t>
+          <t>sweet, deep, warm, sensual, cozy</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>sweet, cozy, elegant, lovely</t>
+          <t>sweet, cozy, elegant, lovely, warm</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sensual</t>
+          <t>warm, cozy, deep, sensual, sweet</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>sweet, deep, warm, sensual</t>
+          <t>sweet, deep, warm, sensual, cozy</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, deep</t>
+          <t>cozy, warm, deep, sensual</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm</t>
+          <t>clean, soft, calm, cozy</t>
         </is>
       </c>
       <c r="N52" s="5" t="n"/>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, deep</t>
+          <t>calm, cozy, deep, fresh</t>
         </is>
       </c>
       <c r="N54" s="5" t="n"/>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, zesty</t>
+          <t>fresh, clean, zesty, cool</t>
         </is>
       </c>
       <c r="N55" s="5" t="n"/>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>sweet, soft, elegant</t>
+          <t>sweet, soft, elegant, cozy, warm</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>deep, sweet, warm, sensual</t>
+          <t>deep, sweet, warm, sensual, cozy</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>fresh, deep, elegant</t>
+          <t>fresh, deep, elegant, sweet</t>
         </is>
       </c>
       <c r="N58" s="5" t="n"/>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sensual</t>
+          <t>warm, cozy, deep, sensual, calm</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>fresh, soft, calm</t>
+          <t>fresh, soft, calm, cool</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, sweet, lovely</t>
+          <t>soft, elegant, sweet, lovely, calm, cozy</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, cool</t>
+          <t>zesty, fresh, cool, clean</t>
         </is>
       </c>
       <c r="N67" s="5" t="n"/>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>sweet, soft, fresh, lovely</t>
+          <t>sweet, soft, fresh, lovely, zesty</t>
         </is>
       </c>
       <c r="N68" s="5" t="n"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>calm, deep, fresh</t>
+          <t>calm, deep, fresh, warm</t>
         </is>
       </c>
       <c r="N69" s="5" t="n"/>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, cool</t>
+          <t>fresh, clean, cool, zesty</t>
         </is>
       </c>
       <c r="N70" s="5" t="n"/>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, elegant</t>
+          <t>warm, deep, elegant, calm</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, zesty</t>
+          <t>clean, fresh, zesty, cool</t>
         </is>
       </c>
       <c r="N73" s="5" t="n"/>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>deep, elegant, warm, sensual</t>
+          <t>deep, elegant, warm, sensual, calm</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, cozy, sensual</t>
+          <t>warm, deep, cozy, sensual, sweet</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, soft</t>
+          <t>warm, cozy, soft, sweet, deep</t>
         </is>
       </c>
       <c r="N76" s="5" t="n"/>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant, sensual</t>
+          <t>deep, warm, elegant, sensual, calm</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, elegant</t>
+          <t>fresh, zesty, elegant, sweet, lovely</t>
         </is>
       </c>
       <c r="N78" s="5" t="n"/>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>soft, calm, clean</t>
+          <t>soft, calm, clean, cozy</t>
         </is>
       </c>
       <c r="N79" s="5" t="n"/>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>fresh, warm, soft</t>
+          <t>fresh, warm, soft, clean, zesty</t>
         </is>
       </c>
       <c r="N80" s="5" t="n"/>
@@ -11443,7 +11443,7 @@
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, soft</t>
+          <t>cozy, warm, soft, deep</t>
         </is>
       </c>
       <c r="N82" s="5" t="n"/>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, elegant</t>
+          <t>calm, cozy, elegant, warm, deep</t>
         </is>
       </c>
       <c r="N84" s="5" t="n"/>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, elegant, sensual</t>
+          <t>sweet, warm, elegant, sensual, cozy</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>calm, warm, fresh</t>
+          <t>calm, warm, fresh, deep</t>
         </is>
       </c>
       <c r="N90" s="5" t="n"/>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, cool</t>
+          <t>fresh, clean, cool, calm</t>
         </is>
       </c>
       <c r="N92" s="5" t="n"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, warm</t>
+          <t>zesty, fresh, warm, clean</t>
         </is>
       </c>
       <c r="N93" s="5" t="n"/>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, deep, sensual</t>
+          <t>warm, sweet, deep, sensual, cozy</t>
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm</t>
+          <t>clean, soft, calm, warm</t>
         </is>
       </c>
       <c r="N95" s="5" t="n"/>
@@ -13217,7 +13217,7 @@
       </c>
       <c r="M96" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm</t>
+          <t>clean, soft, calm, cozy</t>
         </is>
       </c>
       <c r="N96" s="5" t="n"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm</t>
+          <t>clean, soft, calm, cozy</t>
         </is>
       </c>
       <c r="N97" s="5" t="n"/>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sensual</t>
+          <t>warm, cozy, deep, sensual, sweet</t>
         </is>
       </c>
       <c r="N100" s="5" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, soft</t>
+          <t>lovely, fresh, soft, elegant</t>
         </is>
       </c>
       <c r="N101" s="5" t="n"/>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>fresh, sweet, warm</t>
+          <t>fresh, sweet, warm, calm</t>
         </is>
       </c>
       <c r="N102" s="5" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, sensual</t>
+          <t>warm, deep, sensual, cozy, sweet</t>
         </is>
       </c>
       <c r="N103" s="5" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, elegant</t>
+          <t>sweet, lovely, elegant, cozy, warm</t>
         </is>
       </c>
       <c r="N104" s="5" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>calm, warm, fresh</t>
+          <t>calm, warm, fresh, deep</t>
         </is>
       </c>
       <c r="N105" s="5" t="n"/>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, clean</t>
+          <t>soft, elegant, clean, lovely</t>
         </is>
       </c>
       <c r="N106" s="5" t="n"/>
@@ -14604,7 +14604,7 @@
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>sweet, sensual, elegant</t>
+          <t>sweet, sensual, elegant, cozy, warm</t>
         </is>
       </c>
       <c r="N107" s="5" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, deep</t>
+          <t>cool, fresh, deep, calm</t>
         </is>
       </c>
       <c r="N108" s="5" t="n"/>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>lovely, soft, clean</t>
+          <t>lovely, soft, clean, elegant</t>
         </is>
       </c>
       <c r="N109" s="5" t="n"/>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
-          <t>calm, deep, fresh</t>
+          <t>calm, deep, fresh, warm</t>
         </is>
       </c>
       <c r="N110" s="5" t="n"/>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>elegant, clean, soft</t>
+          <t>elegant, clean, soft, lovely</t>
         </is>
       </c>
       <c r="N111" s="5" t="n"/>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, elegant</t>
+          <t>sweet, lovely, elegant, fresh, zesty</t>
         </is>
       </c>
       <c r="N113" s="5" t="inlineStr">
@@ -15487,7 +15487,7 @@
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>sweet, cozy, warm</t>
+          <t>sweet, cozy, warm, sensual</t>
         </is>
       </c>
       <c r="N114" s="5" t="inlineStr">

--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -1014,7 +1014,7 @@
           <t>clean, fresh, calm, cool, zesty</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="n"/>
       <c r="O2" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -1147,7 +1147,7 @@
           <t>clean, zesty, elegant, cool, fresh</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="n"/>
       <c r="O3" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1272,7 +1272,7 @@
           <t>zesty, fresh, clean, cool</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="n"/>
       <c r="O4" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -1397,7 +1397,7 @@
           <t>clean, fresh, zesty, cool</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="n"/>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -1522,7 +1522,7 @@
           <t>soft, elegant, fresh, lovely, zesty, sweet</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="n"/>
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -1647,7 +1647,11 @@
           <t>soft, sweet, elegant, lovely, fresh, zesty</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -1921,7 +1925,7 @@
           <t>soft, sweet, zesty, lovely, fresh</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -2046,7 +2050,7 @@
           <t>elegant, warm, sweet, fresh, zesty, lovely</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="n"/>
       <c r="O10" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -2171,7 +2175,7 @@
           <t>cool, clean, fresh</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -2296,7 +2300,7 @@
           <t>cool, calm, fresh, clean</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -2421,7 +2425,11 @@
           <t>cool, clean, fresh</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -2546,7 +2554,7 @@
           <t>fresh, calm, soft, cool</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -2671,7 +2679,7 @@
           <t>fresh, cool, soft</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -2796,7 +2804,7 @@
           <t>fresh, clean, calm, cool</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -2921,7 +2929,11 @@
           <t>cool, deep, fresh, calm</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -3046,7 +3058,11 @@
           <t>calm, deep, clean</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -3173,7 +3189,7 @@
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, spicy</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -3302,7 +3318,7 @@
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral</t>
+          <t>heavyFloral, headache</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -3429,7 +3445,11 @@
           <t>elegant, soft, fresh, lovely</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -3554,7 +3574,7 @@
           <t>elegant, soft, warm, lovely</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="n"/>
       <c r="O22" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -3679,7 +3699,11 @@
           <t>elegant, warm, fresh, lovely</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -3804,7 +3828,7 @@
           <t>elegant, sweet, soft, lovely, clean</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="n"/>
       <c r="O24" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -4058,7 +4082,7 @@
           <t>elegant, soft, calm, clean, lovely</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="n"/>
       <c r="O26" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -4185,7 +4209,7 @@
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t>powdery, heavyFloral</t>
+          <t>powdery, heavyFloral, soapy</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -4699,7 +4723,11 @@
           <t>clean, soft, calm, cozy</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -4844,7 +4872,11 @@
           <t>clean, soft, cozy, calm</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -4989,7 +5021,11 @@
           <t>soft, elegant, warm, calm, clean, cozy</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -5114,7 +5150,11 @@
           <t>soft, clean, calm, cozy</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -5239,7 +5279,11 @@
           <t>fresh, warm, sweet, calm, clean, cozy, soft</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -5364,7 +5408,11 @@
           <t>deep, calm, warm, sensual</t>
         </is>
       </c>
-      <c r="N36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -5489,7 +5537,11 @@
           <t>warm, elegant, fresh</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -5616,7 +5668,7 @@
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, spicy</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -5763,7 +5815,7 @@
           <t>calm, cozy, deep, warm</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="n"/>
       <c r="O39" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -5890,7 +5942,7 @@
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, spicy, headache</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -6017,7 +6069,7 @@
           <t>calm, cozy, soft, warm, deep</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="n"/>
       <c r="O41" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -6164,7 +6216,7 @@
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, spicy</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
@@ -6293,7 +6345,7 @@
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, headache</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -6420,7 +6472,7 @@
           <t>warm, elegant, soft, cozy, sweet, deep</t>
         </is>
       </c>
-      <c r="N44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="n"/>
       <c r="O44" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -6547,7 +6599,7 @@
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet, tooStrong, spicy, headache</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -6805,7 +6857,7 @@
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet, tooStrong, spicy</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
@@ -7063,7 +7115,7 @@
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>smoky</t>
+          <t>smoky, spicy</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
@@ -7341,7 +7393,7 @@
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, smoky</t>
+          <t>tooStrong, smoky, spicy, headache</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
@@ -7468,7 +7520,11 @@
           <t>clean, soft, calm, cozy</t>
         </is>
       </c>
-      <c r="N52" s="5" t="n"/>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -7615,7 +7671,7 @@
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, smoky</t>
+          <t>tooStrong, smoky, spicy, headache</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
@@ -8310,7 +8366,11 @@
           <t>fresh, deep, elegant, sweet</t>
         </is>
       </c>
-      <c r="N58" s="5" t="n"/>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>headache</t>
+        </is>
+      </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
           <t>strong</t>
@@ -8812,7 +8872,7 @@
       </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, heavyFloral</t>
+          <t>tooStrong, heavyFloral, spicy, headache</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
@@ -8941,7 +9001,7 @@
       </c>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, spicy</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
@@ -9070,7 +9130,7 @@
       </c>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral, tooStrong</t>
+          <t>heavyFloral, tooStrong, headache</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
@@ -10122,7 +10182,7 @@
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, spicy</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
@@ -10249,7 +10309,11 @@
           <t>clean, fresh, zesty, cool</t>
         </is>
       </c>
-      <c r="N73" s="5" t="n"/>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -10376,7 +10440,7 @@
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, headache</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
@@ -10632,7 +10696,11 @@
           <t>warm, cozy, soft, sweet, deep</t>
         </is>
       </c>
-      <c r="N76" s="5" t="n"/>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -10759,7 +10827,7 @@
       </c>
       <c r="N77" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, spicy, headache</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
@@ -11011,7 +11079,11 @@
           <t>soft, calm, clean, cozy</t>
         </is>
       </c>
-      <c r="N79" s="5" t="n"/>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -11301,7 +11373,11 @@
           <t>elegant, deep, soft</t>
         </is>
       </c>
-      <c r="N81" s="5" t="n"/>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -11591,7 +11667,11 @@
           <t>warm, cozy, soft</t>
         </is>
       </c>
-      <c r="N83" s="5" t="n"/>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -11970,7 +12050,11 @@
           <t>warm, sweet, elegant, sensual</t>
         </is>
       </c>
-      <c r="N86" s="5" t="n"/>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O86" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -12097,7 +12181,7 @@
       </c>
       <c r="N87" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, spicy</t>
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr">
@@ -12226,7 +12310,7 @@
       </c>
       <c r="N88" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral, tooStrong</t>
+          <t>heavyFloral, tooStrong, headache</t>
         </is>
       </c>
       <c r="O88" s="5" t="inlineStr">
@@ -12355,7 +12439,7 @@
       </c>
       <c r="N89" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, spicy, headache</t>
         </is>
       </c>
       <c r="O89" s="5" t="inlineStr">
@@ -12984,7 +13068,7 @@
       </c>
       <c r="N94" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet, tooStrong, spicy, headache</t>
         </is>
       </c>
       <c r="O94" s="5" t="inlineStr">
@@ -13220,7 +13304,11 @@
           <t>clean, soft, calm, cozy</t>
         </is>
       </c>
-      <c r="N96" s="5" t="n"/>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O96" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -13337,7 +13425,11 @@
           <t>clean, soft, calm, cozy</t>
         </is>
       </c>
-      <c r="N97" s="5" t="n"/>
+      <c r="N97" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O97" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -13589,7 +13681,7 @@
       </c>
       <c r="N99" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, spicy, headache</t>
         </is>
       </c>
       <c r="O99" s="5" t="inlineStr">
@@ -13718,7 +13810,7 @@
       </c>
       <c r="N100" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, headache</t>
         </is>
       </c>
       <c r="O100" s="5" t="inlineStr">
@@ -14101,7 +14193,7 @@
       </c>
       <c r="N103" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet, tooStrong, spicy, headache</t>
         </is>
       </c>
       <c r="O103" s="5" t="inlineStr">
@@ -14357,7 +14449,11 @@
           <t>calm, warm, fresh, deep</t>
         </is>
       </c>
-      <c r="N105" s="5" t="n"/>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O105" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -14609,7 +14705,7 @@
       </c>
       <c r="N107" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet, tooStrong, headache</t>
         </is>
       </c>
       <c r="O107" s="5" t="inlineStr">
@@ -14736,7 +14832,11 @@
           <t>cool, fresh, deep, calm</t>
         </is>
       </c>
-      <c r="N108" s="5" t="n"/>
+      <c r="N108" s="5" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
       <c r="O108" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -15111,7 +15211,11 @@
           <t>elegant, clean, soft, lovely</t>
         </is>
       </c>
-      <c r="N111" s="5" t="n"/>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O111" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -15363,7 +15467,7 @@
       </c>
       <c r="N113" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, soapy</t>
         </is>
       </c>
       <c r="O113" s="5" t="inlineStr">
@@ -15621,7 +15725,7 @@
       </c>
       <c r="N115" s="5" t="inlineStr">
         <is>
-          <t>tooStrong</t>
+          <t>tooStrong, headache</t>
         </is>
       </c>
       <c r="O115" s="5" t="inlineStr">
@@ -19380,6 +19484,16 @@
         <f>COUNTIF(perfumes!$M$2:$M$200,"*"&amp;G8&amp;"*")</f>
         <v/>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>spicy</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>알싸한 향</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -19417,6 +19531,16 @@
       <c r="I9" s="2">
         <f>COUNTIF(perfumes!$M$2:$M$200,"*"&amp;G9&amp;"*")</f>
         <v/>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>비누·세제 같은 향</t>
+        </is>
       </c>
     </row>
     <row r="10">

--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -1397,7 +1397,11 @@
           <t>clean, fresh, zesty, cool</t>
         </is>
       </c>
-      <c r="N5" s="5" t="n"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -1647,11 +1651,7 @@
           <t>soft, sweet, elegant, lovely, fresh, zesty</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N7" s="5" t="n"/>
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -2425,11 +2425,7 @@
           <t>cool, clean, fresh</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -3058,11 +3054,7 @@
           <t>calm, deep, clean</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>spicy</t>
-        </is>
-      </c>
+      <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -3184,7 +3176,7 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, sweet, calm</t>
+          <t>cozy, warm, sweet</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -3318,7 +3310,7 @@
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral, headache</t>
+          <t>heavyFloral, tooSweet, tooStrong, headache</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -3445,11 +3437,7 @@
           <t>elegant, soft, fresh, lovely</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -3699,11 +3687,7 @@
           <t>elegant, warm, fresh, lovely</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -4082,7 +4066,11 @@
           <t>elegant, soft, calm, clean, lovely</t>
         </is>
       </c>
-      <c r="N26" s="5" t="n"/>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>heavyFloral</t>
+        </is>
+      </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -5152,7 +5140,7 @@
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t>soapy</t>
+          <t>powdery, soapy</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -5279,11 +5267,7 @@
           <t>fresh, warm, sweet, calm, clean, cozy, soft</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N35" s="5" t="n"/>
       <c r="O35" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -5668,7 +5652,7 @@
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, spicy</t>
+          <t>tooStrong, smoky</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -5942,7 +5926,7 @@
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, spicy, headache</t>
+          <t>tooStrong, smoky, spicy</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -6216,7 +6200,7 @@
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, spicy</t>
+          <t>tooSweet, tooStrong</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
@@ -6345,7 +6329,7 @@
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, headache</t>
+          <t>tooStrong, powdery</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -6599,7 +6583,7 @@
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong, spicy, headache</t>
+          <t>tooSweet, tooStrong</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -6728,7 +6712,7 @@
       </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, powdery</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
@@ -6857,7 +6841,7 @@
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong, spicy</t>
+          <t>tooSweet, tooStrong</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
@@ -7115,7 +7099,7 @@
       </c>
       <c r="N49" s="5" t="inlineStr">
         <is>
-          <t>smoky, spicy</t>
+          <t>smoky</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
@@ -7393,7 +7377,7 @@
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, smoky, spicy, headache</t>
+          <t>tooSweet, tooStrong, smoky, spicy</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
@@ -7520,11 +7504,7 @@
           <t>clean, soft, calm, cozy</t>
         </is>
       </c>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N52" s="5" t="n"/>
       <c r="O52" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -7671,7 +7651,7 @@
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, smoky, spicy, headache</t>
+          <t>tooStrong, spicy, smoky</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
@@ -7818,7 +7798,11 @@
           <t>calm, cozy, deep, fresh</t>
         </is>
       </c>
-      <c r="N54" s="5" t="n"/>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>smoky</t>
+        </is>
+      </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -8110,7 +8094,7 @@
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, tooStrong</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
@@ -8368,7 +8352,7 @@
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>headache</t>
+          <t>smoky, tooStrong</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -8872,7 +8856,7 @@
       </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, heavyFloral, spicy, headache</t>
+          <t>tooStrong, heavyFloral, spicy, smoky</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
@@ -9765,7 +9749,11 @@
           <t>calm, deep, fresh, warm</t>
         </is>
       </c>
-      <c r="N69" s="5" t="n"/>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>smoky</t>
+        </is>
+      </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -10182,7 +10170,7 @@
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, spicy</t>
+          <t>tooSweet</t>
         </is>
       </c>
       <c r="O72" s="5" t="inlineStr">
@@ -10440,7 +10428,7 @@
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, headache</t>
+          <t>tooStrong, smoky</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
@@ -10696,11 +10684,7 @@
           <t>warm, cozy, soft, sweet, deep</t>
         </is>
       </c>
-      <c r="N76" s="5" t="inlineStr">
-        <is>
-          <t>spicy</t>
-        </is>
-      </c>
+      <c r="N76" s="5" t="n"/>
       <c r="O76" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -10827,7 +10811,7 @@
       </c>
       <c r="N77" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, spicy, headache</t>
+          <t>tooStrong, smoky, headache</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
@@ -11079,11 +11063,7 @@
           <t>soft, calm, clean, cozy</t>
         </is>
       </c>
-      <c r="N79" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N79" s="5" t="n"/>
       <c r="O79" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -11373,11 +11353,7 @@
           <t>elegant, deep, soft</t>
         </is>
       </c>
-      <c r="N81" s="5" t="inlineStr">
-        <is>
-          <t>spicy</t>
-        </is>
-      </c>
+      <c r="N81" s="5" t="n"/>
       <c r="O81" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -11669,7 +11645,7 @@
       </c>
       <c r="N83" s="5" t="inlineStr">
         <is>
-          <t>spicy</t>
+          <t>spicy, smoky</t>
         </is>
       </c>
       <c r="O83" s="5" t="inlineStr">
@@ -12050,11 +12026,7 @@
           <t>warm, sweet, elegant, sensual</t>
         </is>
       </c>
-      <c r="N86" s="5" t="inlineStr">
-        <is>
-          <t>spicy</t>
-        </is>
-      </c>
+      <c r="N86" s="5" t="n"/>
       <c r="O86" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -12181,7 +12153,7 @@
       </c>
       <c r="N87" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, spicy</t>
+          <t>tooStrong, smoky</t>
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr">
@@ -12310,7 +12282,7 @@
       </c>
       <c r="N88" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral, tooStrong, headache</t>
+          <t>heavyFloral, tooStrong, tooSweet, headache</t>
         </is>
       </c>
       <c r="O88" s="5" t="inlineStr">
@@ -12439,7 +12411,7 @@
       </c>
       <c r="N89" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, spicy, headache</t>
+          <t>tooStrong, smoky</t>
         </is>
       </c>
       <c r="O89" s="5" t="inlineStr">
@@ -13068,7 +13040,7 @@
       </c>
       <c r="N94" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong, spicy, headache</t>
+          <t>tooSweet, tooStrong, spicy, smoky</t>
         </is>
       </c>
       <c r="O94" s="5" t="inlineStr">
@@ -13304,11 +13276,7 @@
           <t>clean, soft, calm, cozy</t>
         </is>
       </c>
-      <c r="N96" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N96" s="5" t="n"/>
       <c r="O96" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -13425,11 +13393,7 @@
           <t>clean, soft, calm, cozy</t>
         </is>
       </c>
-      <c r="N97" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N97" s="5" t="n"/>
       <c r="O97" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -13681,7 +13645,7 @@
       </c>
       <c r="N99" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, spicy, headache</t>
+          <t>tooSweet, spicy, smoky</t>
         </is>
       </c>
       <c r="O99" s="5" t="inlineStr">
@@ -13810,7 +13774,7 @@
       </c>
       <c r="N100" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, headache</t>
+          <t>tooSweet, tooStrong</t>
         </is>
       </c>
       <c r="O100" s="5" t="inlineStr">
@@ -14059,7 +14023,7 @@
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>fresh, sweet, warm, calm</t>
+          <t>fresh, sweet, warm</t>
         </is>
       </c>
       <c r="N102" s="5" t="inlineStr">
@@ -14193,7 +14157,7 @@
       </c>
       <c r="N103" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong, spicy, headache</t>
+          <t>tooSweet, tooStrong, spicy</t>
         </is>
       </c>
       <c r="O103" s="5" t="inlineStr">
@@ -14705,7 +14669,7 @@
       </c>
       <c r="N107" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong, headache</t>
+          <t>tooSweet, tooStrong</t>
         </is>
       </c>
       <c r="O107" s="5" t="inlineStr">
@@ -14832,11 +14796,7 @@
           <t>cool, fresh, deep, calm</t>
         </is>
       </c>
-      <c r="N108" s="5" t="inlineStr">
-        <is>
-          <t>spicy</t>
-        </is>
-      </c>
+      <c r="N108" s="5" t="n"/>
       <c r="O108" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -15211,11 +15171,7 @@
           <t>elegant, clean, soft, lovely</t>
         </is>
       </c>
-      <c r="N111" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+      <c r="N111" s="5" t="n"/>
       <c r="O111" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -15467,7 +15423,7 @@
       </c>
       <c r="N113" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, soapy</t>
+          <t>tooSweet</t>
         </is>
       </c>
       <c r="O113" s="5" t="inlineStr">
@@ -15725,7 +15681,7 @@
       </c>
       <c r="N115" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, headache</t>
+          <t>heavyFloral, tooStrong, headache</t>
         </is>
       </c>
       <c r="O115" s="5" t="inlineStr">

--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -1039,7 +1039,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, calm, cool, zesty</t>
+          <t>clean, fresh, zesty, cool, calm</t>
         </is>
       </c>
       <c r="N2" s="5" t="n"/>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>clean, zesty, elegant, cool, fresh</t>
+          <t>fresh, zesty, clean, elegant, cool</t>
         </is>
       </c>
       <c r="N3" s="5" t="n"/>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, fresh, lovely, zesty, sweet</t>
+          <t>soft, fresh, elegant, lovely, sweet</t>
         </is>
       </c>
       <c r="N6" s="5" t="n"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>soft, sweet, elegant, lovely, fresh, zesty</t>
+          <t>soft, lovely, fresh, sweet, elegant</t>
         </is>
       </c>
       <c r="N7" s="5" t="n"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>sweet, cozy, warm, lovely, fresh, zesty</t>
+          <t>sweet, lovely, fresh, warm</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>soft, sweet, zesty, lovely, fresh</t>
+          <t>lovely, fresh, sweet, soft</t>
         </is>
       </c>
       <c r="N9" s="5" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm, sweet, fresh, zesty, lovely</t>
+          <t>elegant, sweet, warm, lovely</t>
         </is>
       </c>
       <c r="N10" s="5" t="n"/>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>cool, clean, fresh</t>
+          <t>cool, fresh, clean</t>
         </is>
       </c>
       <c r="N11" s="5" t="n"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>fresh, calm, soft, cool</t>
+          <t>fresh, calm, soft</t>
         </is>
       </c>
       <c r="N14" s="5" t="n"/>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, calm, cool</t>
+          <t>clean, fresh, calm, cool</t>
         </is>
       </c>
       <c r="N16" s="5" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>cool, deep, fresh, calm</t>
+          <t>fresh, deep, warm</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>high</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>calm, deep, clean</t>
+          <t>fresh, elegant, calm, deep</t>
         </is>
       </c>
       <c r="N18" s="5" t="n"/>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, sweet, calm</t>
+          <t>sweet, warm, sensual, cozy</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>elegant, sweet, warm, lovely</t>
+          <t>sweet, lovely, elegant, warm</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral, tooSweet, tooStrong, headache</t>
+          <t>heavyFloral, tooSweet, headache</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, fresh, lovely</t>
+          <t>soft, lovely, fresh, elegant</t>
         </is>
       </c>
       <c r="N21" s="5" t="n"/>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, warm, lovely</t>
+          <t>soft, lovely, elegant, warm</t>
         </is>
       </c>
       <c r="N22" s="5" t="n"/>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm, fresh, lovely</t>
+          <t>elegant, warm, lovely, fresh</t>
         </is>
       </c>
       <c r="N23" s="5" t="n"/>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>elegant, sweet, soft, lovely, clean</t>
+          <t>elegant, lovely, sweet, soft</t>
         </is>
       </c>
       <c r="N24" s="5" t="n"/>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, lovely, clean</t>
+          <t>lovely, soft, elegant</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, calm, clean, lovely</t>
+          <t>elegant, soft, calm, clean</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>elegant, calm, clean, lovely</t>
+          <t>elegant, clean, soft, calm</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>calm, soft, elegant, cozy, lovely</t>
+          <t>calm, soft, clean, elegant</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>calm, deep, soft, cozy, elegant</t>
+          <t>soft, elegant, cozy, deep, calm</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, calm, lovely, cozy</t>
+          <t>soft, elegant, lovely, clean, calm</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm, cozy</t>
+          <t>clean, soft, calm</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -5034,14 +5034,10 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, warm, calm, clean, cozy</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>soapy</t>
-        </is>
-      </c>
+          <t>sensual, warm, elegant, cozy</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -5163,7 +5159,7 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>soft, clean, calm, cozy</t>
+          <t>soft, clean, cozy, calm</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -5292,7 +5288,7 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>fresh, warm, sweet, calm, clean, cozy, soft</t>
+          <t>fresh, clean, warm, sweet, soft</t>
         </is>
       </c>
       <c r="N35" s="5" t="n"/>
@@ -5417,7 +5413,7 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>deep, calm, warm, sensual</t>
+          <t>deep, warm, calm, fresh</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -5546,7 +5542,7 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, fresh</t>
+          <t>fresh, elegant, warm, lovely</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -5675,12 +5671,12 @@
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>deep, calm, warm, sensual</t>
+          <t>warm, deep, calm, cozy</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, smoky</t>
+          <t>smoky</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -5824,7 +5820,7 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, deep, warm</t>
+          <t>calm, warm, cozy, elegant</t>
         </is>
       </c>
       <c r="N39" s="5" t="n"/>
@@ -5949,12 +5945,12 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant, sensual, calm</t>
+          <t>elegant, deep, warm, sensual</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, smoky, spicy</t>
+          <t>smoky</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -6078,7 +6074,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, soft, warm, deep</t>
+          <t>calm, fresh, warm, cozy</t>
         </is>
       </c>
       <c r="N41" s="5" t="n"/>
@@ -6223,12 +6219,12 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, sweet, sensual, cozy, deep</t>
+          <t>sweet, warm, elegant, cozy</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
@@ -6352,12 +6348,12 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, elegant, sensual, cozy, sweet</t>
+          <t>warm, sensual, elegant, deep, sweet</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, powdery</t>
+          <t>powdery</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -6481,7 +6477,7 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, soft, cozy, sweet, deep</t>
+          <t>warm, elegant, soft, sweet</t>
         </is>
       </c>
       <c r="N44" s="5" t="n"/>
@@ -6606,12 +6602,12 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>sweet, deep, warm, sensual, cozy</t>
+          <t>sweet, sensual, warm, deep</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -6735,7 +6731,7 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>sweet, cozy, elegant, lovely, warm</t>
+          <t>sweet, lovely, cozy, elegant</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -6864,12 +6860,12 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sensual, sweet</t>
+          <t>warm, sweet, cozy, sensual, deep</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
@@ -6993,12 +6989,12 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>sweet, deep, warm, sensual, cozy</t>
+          <t>sweet, deep, sensual, warm</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong, headache</t>
+          <t>tooSweet, headache</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -7122,7 +7118,7 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, deep, sensual</t>
+          <t>cozy, warm, deep, sweet</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
@@ -7271,7 +7267,7 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>deep, cozy, warm, sensual</t>
+          <t>warm, cozy, deep, sensual</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
@@ -7400,12 +7396,12 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, cozy, sensual</t>
+          <t>warm, cozy, deep, sweet, sensual</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong, smoky, spicy</t>
+          <t>tooSweet, smoky</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
@@ -7529,7 +7525,7 @@
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm, cozy</t>
+          <t>clean, soft, calm</t>
         </is>
       </c>
       <c r="N52" s="5" t="n"/>
@@ -7540,7 +7536,7 @@
       </c>
       <c r="P52" s="5" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>high</t>
         </is>
       </c>
       <c r="Q52" s="5" t="inlineStr">
@@ -7674,12 +7670,12 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant, sensual</t>
+          <t>elegant, deep, warm, sensual</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, spicy, smoky</t>
+          <t>spicy, smoky</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
@@ -7823,7 +7819,7 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, deep, fresh</t>
+          <t>calm, cozy, deep</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
@@ -7972,7 +7968,7 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, zesty, cool</t>
+          <t>fresh, zesty, clean, cool</t>
         </is>
       </c>
       <c r="N55" s="5" t="n"/>
@@ -8117,12 +8113,12 @@
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>sweet, soft, elegant, cozy, warm</t>
+          <t>sweet, soft, cozy, warm, lovely</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
@@ -8246,12 +8242,12 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>deep, sweet, warm, sensual, cozy</t>
+          <t>sweet, deep, warm, sensual, cozy</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t>tooSweet, tooStrong</t>
+          <t>tooSweet</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
@@ -8375,12 +8371,12 @@
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>fresh, deep, elegant, sweet</t>
+          <t>fresh, elegant, sweet, deep</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t>smoky, tooStrong</t>
+          <t>smoky</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -8504,7 +8500,7 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, cool</t>
+          <t>fresh, cool, clean</t>
         </is>
       </c>
       <c r="N59" s="5" t="n"/>
@@ -8754,7 +8750,7 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, clean</t>
+          <t>fresh, cool, clean, elegant</t>
         </is>
       </c>
       <c r="N61" s="5" t="n"/>
@@ -8884,7 +8880,7 @@
       </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, heavyFloral, spicy, smoky</t>
+          <t>heavyFloral, spicy, smoky</t>
         </is>
       </c>
       <c r="O62" s="5" t="inlineStr">
@@ -9008,12 +9004,12 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sensual, calm</t>
+          <t>warm, cozy, sensual, deep</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t>tooStrong, spicy</t>
+          <t>spicy</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
@@ -9137,12 +9133,12 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm, sensual</t>
+          <t>elegant, sensual, warm</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral, tooStrong, headache</t>
+          <t>heavyFloral, headache</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
@@ -9266,7 +9262,7 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>fresh, soft, calm, cool</t>
+          <t>fresh, soft, cool, calm</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr">
@@ -9395,7 +9391,7 @@
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, sweet, lovely, calm, cozy</t>
+          <t>soft, sweet, lovely, elegant</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
@@ -9649,7 +9645,7 @@
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>sweet, soft, fresh, lovely, zesty</t>
+          <t>lovely, sweet, soft, fresh</t>
         </is>
       </c>
       <c r="N68" s="5" t="n"/>
@@ -9774,7 +9770,7 @@
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>calm, deep, fresh, warm</t>
+          <t>calm, deep, fresh</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr">
@@ -9923,7 +9919,7 @@
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, cool, zesty</t>
+          <t>fresh, zesty, clean, cool</t>
         </is>
       </c>
       <c r="N70" s="5" t="n"/>
@@ -10068,7 +10064,7 @@
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>elegant, sweet, soft, lovely</t>
+          <t>lovely, elegant, sweet, soft</t>
         </is>
       </c>
       <c r="N71" s="5" t="n"/>
@@ -10193,7 +10189,7 @@
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, elegant, calm</t>
+          <t>warm, elegant, sweet, deep</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr">
@@ -10451,14 +10447,10 @@
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>deep, elegant, warm, sensual, calm</t>
-        </is>
-      </c>
-      <c r="N74" s="5" t="inlineStr">
-        <is>
-          <t>tooStrong, smoky</t>
-        </is>
-      </c>
+          <t>sensual, deep, warm, elegant</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="n"/>
       <c r="O74" s="5" t="inlineStr">
         <is>
           <t>strong</t>
@@ -10466,7 +10458,7 @@
       </c>
       <c r="P74" s="5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="Q74" s="5" t="inlineStr">
@@ -10580,7 +10572,7 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, cozy, sensual, sweet</t>
+          <t>warm, sensual, cozy, deep, sweet</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
@@ -10709,7 +10701,7 @@
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, soft, sweet, deep</t>
+          <t>warm, soft, cozy, sweet</t>
         </is>
       </c>
       <c r="N76" s="5" t="n"/>
@@ -10834,7 +10826,7 @@
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant, sensual, calm</t>
+          <t>deep, warm, sensual, elegant</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
@@ -10963,7 +10955,7 @@
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, elegant, sweet, lovely</t>
+          <t>fresh, zesty, elegant</t>
         </is>
       </c>
       <c r="N78" s="5" t="n"/>
@@ -11088,10 +11080,14 @@
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>soft, calm, clean, cozy</t>
-        </is>
-      </c>
-      <c r="N79" s="5" t="n"/>
+          <t>soft, clean, calm, lovely</t>
+        </is>
+      </c>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>powdery</t>
+        </is>
+      </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -11233,7 +11229,7 @@
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>fresh, warm, soft, clean, zesty</t>
+          <t>fresh, zesty, soft, clean, warm</t>
         </is>
       </c>
       <c r="N80" s="5" t="n"/>
@@ -11523,7 +11519,7 @@
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, soft, deep</t>
+          <t>cozy, warm, soft</t>
         </is>
       </c>
       <c r="N82" s="5" t="n"/>
@@ -11668,7 +11664,7 @@
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, soft</t>
+          <t>warm, cozy, soft, calm</t>
         </is>
       </c>
       <c r="N83" s="5" t="inlineStr">
@@ -11797,7 +11793,7 @@
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, elegant, warm, deep</t>
+          <t>warm, elegant, cozy, calm</t>
         </is>
       </c>
       <c r="N84" s="5" t="n"/>
@@ -11922,7 +11918,7 @@
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, elegant, sensual, cozy</t>
+          <t>sweet, sensual, warm, elegant</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr">
@@ -12051,7 +12047,7 @@
       </c>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, elegant, sensual</t>
+          <t>warm, sweet, elegant</t>
         </is>
       </c>
       <c r="N86" s="5" t="n"/>
@@ -12305,7 +12301,7 @@
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>deep, elegant, warm, sensual</t>
+          <t>sensual, deep, elegant, warm</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
@@ -12434,7 +12430,7 @@
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, sensual</t>
+          <t>warm, sensual, deep</t>
         </is>
       </c>
       <c r="N89" s="5" t="inlineStr">
@@ -12563,7 +12559,7 @@
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>calm, warm, fresh, deep</t>
+          <t>calm, fresh, warm, elegant</t>
         </is>
       </c>
       <c r="N90" s="5" t="n"/>
@@ -12688,7 +12684,7 @@
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, cool</t>
+          <t>fresh, zesty, cool, clean</t>
         </is>
       </c>
       <c r="N91" s="5" t="n"/>
@@ -12938,7 +12934,7 @@
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, warm, clean</t>
+          <t>zesty, fresh, sweet, clean</t>
         </is>
       </c>
       <c r="N93" s="5" t="n"/>
@@ -13063,7 +13059,7 @@
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, deep, sensual, cozy</t>
+          <t>sweet, warm, cozy, sensual, deep</t>
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr">
@@ -13184,7 +13180,7 @@
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm, warm</t>
+          <t>clean, soft, calm</t>
         </is>
       </c>
       <c r="N95" s="5" t="n"/>
@@ -13543,7 +13539,7 @@
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>sweet, elegant, soft, lovely</t>
+          <t>lovely, sweet, elegant, soft</t>
         </is>
       </c>
       <c r="N98" s="5" t="n"/>
@@ -13797,7 +13793,7 @@
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sensual, sweet</t>
+          <t>warm, cozy, sweet, deep</t>
         </is>
       </c>
       <c r="N100" s="5" t="inlineStr">
@@ -13926,7 +13922,7 @@
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, soft, elegant</t>
+          <t>fresh, zesty, lovely, soft</t>
         </is>
       </c>
       <c r="N101" s="5" t="n"/>
@@ -14051,7 +14047,7 @@
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>fresh, sweet, warm, calm</t>
+          <t>fresh, sweet, warm</t>
         </is>
       </c>
       <c r="N102" s="5" t="inlineStr">
@@ -14180,7 +14176,7 @@
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, sensual, cozy, sweet</t>
+          <t>sweet, warm, sensual, deep</t>
         </is>
       </c>
       <c r="N103" s="5" t="inlineStr">
@@ -14309,7 +14305,7 @@
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, elegant, cozy, warm</t>
+          <t>sweet, lovely, elegant</t>
         </is>
       </c>
       <c r="N104" s="5" t="inlineStr">
@@ -14438,7 +14434,7 @@
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>calm, warm, fresh, deep</t>
+          <t>fresh, warm, calm</t>
         </is>
       </c>
       <c r="N105" s="5" t="inlineStr">
@@ -14567,7 +14563,7 @@
       </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, clean, lovely</t>
+          <t>clean, soft, lovely, elegant</t>
         </is>
       </c>
       <c r="N106" s="5" t="n"/>
@@ -14692,7 +14688,7 @@
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>sweet, sensual, elegant, cozy, warm</t>
+          <t>sweet, sensual, elegant, warm</t>
         </is>
       </c>
       <c r="N107" s="5" t="inlineStr">
@@ -14821,7 +14817,7 @@
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, deep, calm</t>
+          <t>fresh, cool, calm</t>
         </is>
       </c>
       <c r="N108" s="5" t="n"/>
@@ -15071,7 +15067,7 @@
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
-          <t>calm, deep, fresh, warm</t>
+          <t>fresh, warm, deep</t>
         </is>
       </c>
       <c r="N110" s="5" t="n"/>
@@ -15446,7 +15442,7 @@
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, elegant, fresh, zesty</t>
+          <t>sweet, lovely, fresh, elegant</t>
         </is>
       </c>
       <c r="N113" s="5" t="inlineStr">
@@ -15580,7 +15576,7 @@
       </c>
       <c r="N114" s="5" t="inlineStr">
         <is>
-          <t>tooSweet</t>
+          <t>tooSweet, powdery</t>
         </is>
       </c>
       <c r="O114" s="5" t="inlineStr">
@@ -15704,12 +15700,12 @@
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>elegant, deep, sensual</t>
+          <t>sensual, deep, elegant, warm</t>
         </is>
       </c>
       <c r="N115" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral, tooStrong, headache</t>
+          <t>heavyFloral, headache</t>
         </is>
       </c>
       <c r="O115" s="5" t="inlineStr">
@@ -16333,7 +16329,7 @@
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, calm, cozy, lovely</t>
+          <t>elegant, soft, calm, cozy</t>
         </is>
       </c>
       <c r="N120" s="5" t="inlineStr">
@@ -16462,7 +16458,7 @@
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>sensual, warm, deep, cozy, sweet</t>
+          <t>sensual, sweet, warm, deep</t>
         </is>
       </c>
       <c r="N121" s="5" t="inlineStr">
@@ -17099,7 +17095,7 @@
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>warm, soft, elegant, cozy, sweet, deep</t>
+          <t>warm, soft, cozy, elegant</t>
         </is>
       </c>
       <c r="N126" s="5" t="n"/>
@@ -17389,7 +17385,7 @@
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>fresh, calm, clean, warm</t>
+          <t>fresh, clean, calm</t>
         </is>
       </c>
       <c r="N128" s="5" t="n"/>
@@ -17812,7 +17808,7 @@
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm, sensual, calm, deep</t>
+          <t>sensual, warm, elegant, deep</t>
         </is>
       </c>
       <c r="N131" s="5" t="n"/>
@@ -18191,7 +18187,7 @@
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, sensual, calm</t>
+          <t>deep, warm, sensual</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
@@ -18953,7 +18949,7 @@
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, elegant, calm, cozy, lovely</t>
+          <t>clean, soft, elegant, calm</t>
         </is>
       </c>
       <c r="N140" s="5" t="inlineStr">
@@ -19082,7 +19078,7 @@
       </c>
       <c r="M141" s="5" t="inlineStr">
         <is>
-          <t>lovely, soft, elegant</t>
+          <t>lovely, soft, elegant, warm</t>
         </is>
       </c>
       <c r="N141" s="5" t="inlineStr">
@@ -19211,7 +19207,7 @@
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, soft, clean, elegant</t>
+          <t>lovely, fresh, soft, elegant</t>
         </is>
       </c>
       <c r="N142" s="5" t="n"/>
@@ -19336,7 +19332,7 @@
       </c>
       <c r="M143" s="5" t="inlineStr">
         <is>
-          <t>calm, soft, clean, cool</t>
+          <t>calm, soft, cozy, clean</t>
         </is>
       </c>
       <c r="N143" s="5" t="n"/>
@@ -19755,7 +19751,7 @@
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, calm</t>
+          <t>fresh, cool, clean</t>
         </is>
       </c>
       <c r="N146" s="5" t="n"/>
@@ -20005,7 +20001,7 @@
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
-          <t>sensual, warm, sweet, cozy</t>
+          <t>sweet, sensual, warm</t>
         </is>
       </c>
       <c r="N148" s="5" t="inlineStr">
@@ -20134,7 +20130,7 @@
       </c>
       <c r="M149" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, sensual, cozy</t>
+          <t>sweet, warm, cozy, fresh</t>
         </is>
       </c>
       <c r="N149" s="5" t="inlineStr">
@@ -20388,7 +20384,7 @@
       </c>
       <c r="M151" s="5" t="inlineStr">
         <is>
-          <t>soft, lovely, fresh, elegant</t>
+          <t>soft, fresh, lovely, sweet</t>
         </is>
       </c>
       <c r="N151" s="5" t="n"/>
@@ -20638,10 +20634,14 @@
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
-          <t>clean, calm, soft, lovely, elegant</t>
-        </is>
-      </c>
-      <c r="N153" s="5" t="n"/>
+          <t>clean, calm, soft, elegant</t>
+        </is>
+      </c>
+      <c r="N153" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O153" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, clean, calm</t>
+          <t>fresh, cool, clean</t>
         </is>
       </c>
       <c r="N156" s="5" t="n"/>
@@ -21154,12 +21154,12 @@
       </c>
       <c r="M157" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, sensual</t>
+          <t>warm, sensual, elegant, sweet</t>
         </is>
       </c>
       <c r="N157" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral</t>
+          <t>powdery</t>
         </is>
       </c>
       <c r="O157" s="5" t="inlineStr">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, calm, lovely</t>
+          <t>soft, fresh, elegant, calm</t>
         </is>
       </c>
       <c r="N158" s="5" t="n"/>
@@ -21665,7 +21665,11 @@
           <t>soft, clean, cozy, calm</t>
         </is>
       </c>
-      <c r="N161" s="5" t="n"/>
+      <c r="N161" s="5" t="inlineStr">
+        <is>
+          <t>powdery, soapy</t>
+        </is>
+      </c>
       <c r="O161" s="5" t="inlineStr">
         <is>
           <t>medium</t>
@@ -21791,7 +21795,7 @@
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>calm, soft, cozy, warm, deep</t>
+          <t>calm, soft, cozy, warm</t>
         </is>
       </c>
       <c r="N162" s="5" t="n"/>
@@ -22504,7 +22508,7 @@
       </c>
       <c r="M167" s="5" t="inlineStr">
         <is>
-          <t>fresh, lovely, soft, zesty, sweet</t>
+          <t>fresh, zesty, sweet, lovely</t>
         </is>
       </c>
       <c r="N167" s="5" t="n"/>
@@ -22629,7 +22633,7 @@
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>clean, calm, cool</t>
+          <t>clean, fresh, calm, cool</t>
         </is>
       </c>
       <c r="N168" s="5" t="n"/>
@@ -22754,7 +22758,7 @@
       </c>
       <c r="M169" s="5" t="inlineStr">
         <is>
-          <t>lovely, sweet, soft, fresh, zesty</t>
+          <t>lovely, sweet, soft, fresh</t>
         </is>
       </c>
       <c r="N169" s="5" t="n"/>
@@ -23540,7 +23544,7 @@
       </c>
       <c r="M175" s="5" t="inlineStr">
         <is>
-          <t>fresh, elegant, lovely</t>
+          <t>fresh, soft, lovely, elegant</t>
         </is>
       </c>
       <c r="N175" s="5" t="n"/>
@@ -23677,7 +23681,7 @@
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>calm, fresh, elegant, warm, deep</t>
+          <t>fresh, calm, elegant, deep</t>
         </is>
       </c>
       <c r="N176" s="5" t="n"/>
@@ -23951,7 +23955,7 @@
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>calm, deep, soft, warm</t>
+          <t>calm, soft, warm, elegant</t>
         </is>
       </c>
       <c r="N178" s="5" t="n"/>
@@ -24362,10 +24366,14 @@
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>zesty, lovely, soft, clean, cool, fresh</t>
-        </is>
-      </c>
-      <c r="N181" s="5" t="n"/>
+          <t>zesty, fresh, clean, sweet, soft</t>
+        </is>
+      </c>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>soapy</t>
+        </is>
+      </c>
       <c r="O181" s="5" t="inlineStr">
         <is>
           <t>light</t>
@@ -24373,7 +24381,7 @@
       </c>
       <c r="P181" s="5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="Q181" s="5" t="inlineStr">
@@ -24495,7 +24503,7 @@
       </c>
       <c r="M182" s="5" t="inlineStr">
         <is>
-          <t>calm, fresh, soft, cool</t>
+          <t>calm, fresh, soft, cozy</t>
         </is>
       </c>
       <c r="N182" s="5" t="n"/>
@@ -24785,7 +24793,7 @@
       </c>
       <c r="M184" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, lovely, clean</t>
+          <t>elegant, soft, lovely, sweet</t>
         </is>
       </c>
       <c r="N184" s="5" t="inlineStr">
@@ -24934,7 +24942,7 @@
       </c>
       <c r="M185" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, soft, cool, zesty</t>
+          <t>clean, fresh, soft, zesty</t>
         </is>
       </c>
       <c r="N185" s="5" t="n"/>
@@ -25079,7 +25087,7 @@
       </c>
       <c r="M186" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, cozy, sweet, sensual</t>
+          <t>warm, deep, sweet, sensual</t>
         </is>
       </c>
       <c r="N186" s="5" t="n"/>
@@ -25214,17 +25222,17 @@
       <c r="J187" s="6" t="n"/>
       <c r="K187" s="5" t="inlineStr">
         <is>
-          <t>fruity</t>
+          <t>floral</t>
         </is>
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>floral</t>
+          <t>citrus</t>
         </is>
       </c>
       <c r="M187" s="5" t="inlineStr">
         <is>
-          <t>fresh, lovely, zesty, sweet</t>
+          <t>fresh, soft, lovely, elegant</t>
         </is>
       </c>
       <c r="N187" s="5" t="n"/>
@@ -25733,7 +25741,7 @@
       </c>
       <c r="N191" s="5" t="inlineStr">
         <is>
-          <t>heavyFloral</t>
+          <t>heavyFloral, spicy</t>
         </is>
       </c>
       <c r="O191" s="5" t="inlineStr">
@@ -26002,12 +26010,12 @@
       </c>
       <c r="M193" s="5" t="inlineStr">
         <is>
-          <t>deep, sensual, warm</t>
+          <t>sweet, warm, sensual, deep</t>
         </is>
       </c>
       <c r="N193" s="5" t="inlineStr">
         <is>
-          <t>smoky</t>
+          <t>tooSweet</t>
         </is>
       </c>
       <c r="O193" s="5" t="inlineStr">
@@ -26139,7 +26147,7 @@
       </c>
       <c r="M194" s="5" t="inlineStr">
         <is>
-          <t>elegant, sensual, warm</t>
+          <t>elegant, sensual, warm, sweet</t>
         </is>
       </c>
       <c r="N194" s="5" t="inlineStr">
@@ -26268,7 +26276,7 @@
       </c>
       <c r="M195" s="5" t="inlineStr">
         <is>
-          <t>zesty, lovely, soft, fresh, sweet</t>
+          <t>fresh, zesty, soft, sweet</t>
         </is>
       </c>
       <c r="N195" s="5" t="n"/>
@@ -26393,12 +26401,12 @@
       </c>
       <c r="M196" s="5" t="inlineStr">
         <is>
-          <t>soft, cozy, lovely, calm, clean</t>
+          <t>soft, cozy, sweet, lovely</t>
         </is>
       </c>
       <c r="N196" s="5" t="inlineStr">
         <is>
-          <t>powdery</t>
+          <t>powdery, tooSweet</t>
         </is>
       </c>
       <c r="O196" s="5" t="inlineStr">
@@ -26925,7 +26933,7 @@
       </c>
       <c r="M200" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, sweet, sensual</t>
+          <t>cozy, warm, sweet, soft</t>
         </is>
       </c>
       <c r="N200" s="5" t="n"/>
@@ -27058,7 +27066,7 @@
       </c>
       <c r="M201" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, soft, elegant</t>
+          <t>lovely, fresh, soft</t>
         </is>
       </c>
       <c r="N201" s="5" t="n"/>
@@ -27320,7 +27328,7 @@
       </c>
       <c r="M203" s="5" t="inlineStr">
         <is>
-          <t>fresh, elegant, zesty, sweet, lovely</t>
+          <t>fresh, zesty, elegant, sweet</t>
         </is>
       </c>
       <c r="N203" s="5" t="n"/>
@@ -27457,7 +27465,7 @@
       </c>
       <c r="M204" s="5" t="inlineStr">
         <is>
-          <t>fresh, deep, warm, calm</t>
+          <t>fresh, warm, deep</t>
         </is>
       </c>
       <c r="N204" s="5" t="inlineStr">
@@ -28150,7 +28158,7 @@
       </c>
       <c r="M209" s="5" t="inlineStr">
         <is>
-          <t>deep, sensual, warm, cozy, sweet</t>
+          <t>deep, sensual, warm, elegant</t>
         </is>
       </c>
       <c r="N209" s="5" t="inlineStr">
@@ -28412,7 +28420,7 @@
       </c>
       <c r="M211" s="5" t="inlineStr">
         <is>
-          <t>warm, sensual, elegant, cozy, sweet, deep</t>
+          <t>warm, sweet, sensual, cozy, deep</t>
         </is>
       </c>
       <c r="N211" s="5" t="inlineStr">
@@ -28549,7 +28557,7 @@
       </c>
       <c r="M212" s="5" t="inlineStr">
         <is>
-          <t>soft, cozy, calm, clean</t>
+          <t>soft, cozy, calm, warm</t>
         </is>
       </c>
       <c r="N212" s="5" t="n"/>
@@ -28560,7 +28568,7 @@
       </c>
       <c r="P212" s="5" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>high</t>
         </is>
       </c>
       <c r="Q212" s="5" t="inlineStr">
@@ -28670,7 +28678,7 @@
       </c>
       <c r="M213" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, soft, calm, cozy</t>
+          <t>clean, fresh, soft, calm</t>
         </is>
       </c>
       <c r="N213" s="5" t="n"/>

--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -1079,12 +1079,12 @@
       <c r="X2" s="6" t="n"/>
       <c r="Y2" s="4" t="inlineStr">
         <is>
-          <t>아쿠아 디 파르마 백화점</t>
+          <t>아쿠아디파르마</t>
         </is>
       </c>
       <c r="Z2" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA2" s="6" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AE2" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       <c r="X3" s="6" t="n"/>
       <c r="Y3" s="4" t="inlineStr">
         <is>
-          <t>톰 포드 뷰티 백화점</t>
+          <t>톰 포드 백화점</t>
         </is>
       </c>
       <c r="Z3" s="6" t="inlineStr">
@@ -1466,12 +1466,12 @@
       <c r="X5" s="6" t="n"/>
       <c r="Y5" s="4" t="inlineStr">
         <is>
-          <t>캘빈클라인 향수 백화점</t>
+          <t>올리브영 향수</t>
         </is>
       </c>
       <c r="Z5" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA5" s="6" t="n"/>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="AE5" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       <c r="X6" s="6" t="n"/>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>조말론 런던 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z6" s="6" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>버버리 향수 백화점</t>
+          <t>버버리 백화점</t>
         </is>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA8" s="6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AE8" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       <c r="X9" s="6" t="n"/>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>마크제이콥스 데이지 백화점</t>
+          <t>마크제이콥스</t>
         </is>
       </c>
       <c r="Z9" s="6" t="inlineStr">
@@ -2115,7 +2115,7 @@
       <c r="X10" s="6" t="n"/>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>조르지오 아르마니 뷰티 백화점</t>
+          <t>조르지오 아르마니 백화점</t>
         </is>
       </c>
       <c r="Z10" s="6" t="inlineStr">
@@ -2240,12 +2240,12 @@
       <c r="X11" s="6" t="n"/>
       <c r="Y11" s="4" t="inlineStr">
         <is>
-          <t>다비도프 쿨워터 백화점</t>
+          <t>올리브영 향수</t>
         </is>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA11" s="6" t="n"/>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AE11" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       <c r="X12" s="6" t="n"/>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>조말론 런던 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z12" s="6" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="X13" s="6" t="n"/>
       <c r="Y13" s="4" t="inlineStr">
         <is>
-          <t>조르지오 아르마니 뷰티 백화점</t>
+          <t>조르지오 아르마니 백화점</t>
         </is>
       </c>
       <c r="Z13" s="6" t="inlineStr">
@@ -2615,7 +2615,7 @@
       <c r="X14" s="6" t="n"/>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z14" s="6" t="inlineStr">
@@ -2740,12 +2740,12 @@
       <c r="X15" s="6" t="n"/>
       <c r="Y15" s="4" t="inlineStr">
         <is>
-          <t>에르메스 뷰티 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA15" s="6" t="n"/>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AE15" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       <c r="X16" s="6" t="n"/>
       <c r="Y16" s="4" t="inlineStr">
         <is>
-          <t>불가리 향수 백화점</t>
+          <t>불가리 백화점</t>
         </is>
       </c>
       <c r="Z16" s="6" t="inlineStr">
@@ -2994,7 +2994,7 @@
       <c r="X17" s="6" t="n"/>
       <c r="Y17" s="4" t="inlineStr">
         <is>
-          <t>디올 뷰티 백화점</t>
+          <t>디올 백화점</t>
         </is>
       </c>
       <c r="Z17" s="6" t="inlineStr">
@@ -3248,7 +3248,7 @@
       <c r="X19" s="6" t="n"/>
       <c r="Y19" s="4" t="inlineStr">
         <is>
-          <t>장폴고티에 향수 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z19" s="6" t="inlineStr">
@@ -3377,7 +3377,7 @@
       <c r="X20" s="6" t="n"/>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>빅터앤롤프 플라워밤 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z20" s="6" t="inlineStr">
@@ -3502,7 +3502,7 @@
       <c r="X21" s="6" t="n"/>
       <c r="Y21" s="4" t="inlineStr">
         <is>
-          <t>디올 뷰티 백화점</t>
+          <t>디올 백화점</t>
         </is>
       </c>
       <c r="Z21" s="6" t="inlineStr">
@@ -3627,7 +3627,7 @@
       <c r="X22" s="6" t="n"/>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>조말론 런던 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z22" s="6" t="inlineStr">
@@ -3877,7 +3877,7 @@
       <c r="X24" s="6" t="n"/>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>디올 뷰티 백화점</t>
+          <t>디올 백화점</t>
         </is>
       </c>
       <c r="Z24" s="6" t="inlineStr">
@@ -4006,7 +4006,7 @@
       <c r="X25" s="6" t="n"/>
       <c r="Y25" s="4" t="inlineStr">
         <is>
-          <t>구찌 뷰티 백화점</t>
+          <t>구찌 향수</t>
         </is>
       </c>
       <c r="Z25" s="6" t="inlineStr">
@@ -4135,7 +4135,7 @@
       <c r="X26" s="6" t="n"/>
       <c r="Y26" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z26" s="6" t="inlineStr">
@@ -4393,7 +4393,7 @@
       <c r="X28" s="6" t="n"/>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>프라다 뷰티 백화점</t>
+          <t>프라다 백화점</t>
         </is>
       </c>
       <c r="Z28" s="6" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="X29" s="6" t="n"/>
       <c r="Y29" s="4" t="inlineStr">
         <is>
-          <t>디올 뷰티 백화점</t>
+          <t>디올 백화점</t>
         </is>
       </c>
       <c r="Z29" s="6" t="inlineStr">
@@ -4651,12 +4651,12 @@
       <c r="X30" s="6" t="n"/>
       <c r="Y30" s="4" t="inlineStr">
         <is>
-          <t>끌로에 향수 백화점</t>
+          <t>끌로에 백화점</t>
         </is>
       </c>
       <c r="Z30" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA30" s="6" t="n"/>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="AE30" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -4792,12 +4792,12 @@
       </c>
       <c r="Y31" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z31" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA31" s="6" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AE31" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="Y32" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 레플리카 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z32" s="6" t="inlineStr">
@@ -5074,7 +5074,7 @@
       <c r="X33" s="6" t="n"/>
       <c r="Y33" s="4" t="inlineStr">
         <is>
-          <t>나르시소 로드리게즈 백화점</t>
+          <t>올리브영 향수</t>
         </is>
       </c>
       <c r="Z33" s="6" t="inlineStr">
@@ -5203,7 +5203,7 @@
       <c r="X34" s="6" t="n"/>
       <c r="Y34" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z34" s="6" t="inlineStr">
@@ -5328,7 +5328,7 @@
       <c r="X35" s="6" t="n"/>
       <c r="Y35" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 레플리카 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z35" s="6" t="inlineStr">
@@ -5457,12 +5457,12 @@
       <c r="X36" s="6" t="n"/>
       <c r="Y36" s="4" t="inlineStr">
         <is>
-          <t>에르메스 뷰티 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z36" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA36" s="6" t="n"/>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AE36" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -5586,12 +5586,12 @@
       <c r="X37" s="6" t="n"/>
       <c r="Y37" s="4" t="inlineStr">
         <is>
-          <t>에르메스 뷰티 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA37" s="6" t="n"/>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AE37" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Y38" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z38" s="6" t="inlineStr">
@@ -5860,7 +5860,7 @@
       <c r="X39" s="6" t="n"/>
       <c r="Y39" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z39" s="6" t="inlineStr">
@@ -5989,7 +5989,7 @@
       <c r="X40" s="6" t="n"/>
       <c r="Y40" s="4" t="inlineStr">
         <is>
-          <t>톰 포드 뷰티 백화점</t>
+          <t>톰 포드 백화점</t>
         </is>
       </c>
       <c r="Z40" s="6" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="Y41" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z41" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA41" s="6" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AE41" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       <c r="X42" s="6" t="n"/>
       <c r="Y42" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z42" s="6" t="inlineStr">
@@ -6392,7 +6392,7 @@
       <c r="X43" s="6" t="n"/>
       <c r="Y43" s="4" t="inlineStr">
         <is>
-          <t>겔랑 향수 백화점</t>
+          <t>겔랑</t>
         </is>
       </c>
       <c r="Z43" s="6" t="inlineStr">
@@ -6517,7 +6517,7 @@
       <c r="X44" s="6" t="n"/>
       <c r="Y44" s="4" t="inlineStr">
         <is>
-          <t>입생로랑 뷰티 백화점</t>
+          <t>입생로랑 백화점</t>
         </is>
       </c>
       <c r="Z44" s="6" t="inlineStr">
@@ -6646,7 +6646,7 @@
       <c r="X45" s="6" t="n"/>
       <c r="Y45" s="4" t="inlineStr">
         <is>
-          <t>입생로랑 뷰티 백화점</t>
+          <t>입생로랑 백화점</t>
         </is>
       </c>
       <c r="Z45" s="6" t="inlineStr">
@@ -6775,12 +6775,12 @@
       <c r="X46" s="6" t="n"/>
       <c r="Y46" s="4" t="inlineStr">
         <is>
-          <t>랑콤 뷰티 백화점</t>
+          <t>랑콤 백화점</t>
         </is>
       </c>
       <c r="Z46" s="6" t="inlineStr">
         <is>
-          <t>백화점</t>
+          <t>백화점, 올리브영</t>
         </is>
       </c>
       <c r="AA46" s="6" t="n"/>
@@ -6904,7 +6904,7 @@
       <c r="X47" s="6" t="n"/>
       <c r="Y47" s="4" t="inlineStr">
         <is>
-          <t>킬리안 파리 백화점</t>
+          <t>킬리안 백화점</t>
         </is>
       </c>
       <c r="Z47" s="6" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AE47" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7033,7 @@
       <c r="X48" s="6" t="n"/>
       <c r="Y48" s="4" t="inlineStr">
         <is>
-          <t>뮈글러 엔젤 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z48" s="6" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="Y49" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 레플리카 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z49" s="6" t="inlineStr">
@@ -7311,7 +7311,7 @@
       <c r="X50" s="6" t="n"/>
       <c r="Y50" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 레플리카 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z50" s="6" t="inlineStr">
@@ -7440,7 +7440,7 @@
       <c r="X51" s="6" t="n"/>
       <c r="Y51" s="4" t="inlineStr">
         <is>
-          <t>톰 포드 뷰티 백화점</t>
+          <t>톰 포드 백화점</t>
         </is>
       </c>
       <c r="Z51" s="6" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="Y52" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z52" s="6" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="Y53" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z53" s="6" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="Y54" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z54" s="6" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Y55" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z55" s="6" t="inlineStr">
@@ -8157,7 +8157,7 @@
       <c r="X56" s="6" t="n"/>
       <c r="Y56" s="4" t="inlineStr">
         <is>
-          <t>킬리안 파리 백화점</t>
+          <t>킬리안 백화점</t>
         </is>
       </c>
       <c r="Z56" s="6" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AE56" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       <c r="X57" s="6" t="n"/>
       <c r="Y57" s="4" t="inlineStr">
         <is>
-          <t>킬리안 파리 백화점</t>
+          <t>킬리안 백화점</t>
         </is>
       </c>
       <c r="Z57" s="6" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="AE57" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -8415,12 +8415,12 @@
       <c r="X58" s="6" t="n"/>
       <c r="Y58" s="4" t="inlineStr">
         <is>
-          <t>크리드 백화점</t>
+          <t>크리드 향수</t>
         </is>
       </c>
       <c r="Z58" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA58" s="6" t="n"/>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="AE58" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -8540,12 +8540,12 @@
       <c r="X59" s="6" t="n"/>
       <c r="Y59" s="4" t="inlineStr">
         <is>
-          <t>크리드 백화점</t>
+          <t>크리드 향수</t>
         </is>
       </c>
       <c r="Z59" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA59" s="6" t="n"/>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AE59" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -8665,12 +8665,12 @@
       <c r="X60" s="6" t="n"/>
       <c r="Y60" s="4" t="inlineStr">
         <is>
-          <t>크리드 백화점</t>
+          <t>크리드 향수</t>
         </is>
       </c>
       <c r="Z60" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA60" s="6" t="n"/>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="AE60" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -8790,12 +8790,12 @@
       <c r="X61" s="6" t="n"/>
       <c r="Y61" s="4" t="inlineStr">
         <is>
-          <t>크리드 백화점</t>
+          <t>크리드 향수</t>
         </is>
       </c>
       <c r="Z61" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA61" s="6" t="n"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="AE61" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -8924,7 +8924,7 @@
       </c>
       <c r="Z62" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA62" s="6" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="AE62" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="Z63" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA63" s="6" t="n"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="AE63" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="Z64" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA64" s="6" t="n"/>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="AE64" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="Z65" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA65" s="6" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AE65" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="Z66" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA66" s="6" t="n"/>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AE66" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
       <c r="X67" s="6" t="n"/>
       <c r="Y67" s="4" t="inlineStr">
         <is>
-          <t>아닉 구딸 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z67" s="6" t="inlineStr">
@@ -9685,7 +9685,7 @@
       <c r="X68" s="6" t="n"/>
       <c r="Y68" s="4" t="inlineStr">
         <is>
-          <t>아닉 구딸 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z68" s="6" t="inlineStr">
@@ -10104,12 +10104,12 @@
       <c r="X71" s="6" t="n"/>
       <c r="Y71" s="4" t="inlineStr">
         <is>
-          <t>퍼퓸 드 말리 백화점</t>
+          <t>퍼퓸드말리</t>
         </is>
       </c>
       <c r="Z71" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA71" s="6" t="n"/>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AE71" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -10233,12 +10233,12 @@
       <c r="X72" s="6" t="n"/>
       <c r="Y72" s="4" t="inlineStr">
         <is>
-          <t>퍼퓸 드 말리 백화점</t>
+          <t>퍼퓸드말리</t>
         </is>
       </c>
       <c r="Z72" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA72" s="6" t="n"/>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="AE72" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       <c r="X73" s="6" t="n"/>
       <c r="Y73" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z73" s="6" t="inlineStr">
@@ -10487,7 +10487,7 @@
       <c r="X74" s="6" t="n"/>
       <c r="Y74" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z74" s="6" t="inlineStr">
@@ -10616,7 +10616,7 @@
       <c r="X75" s="6" t="n"/>
       <c r="Y75" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z75" s="6" t="inlineStr">
@@ -10741,7 +10741,7 @@
       <c r="X76" s="6" t="n"/>
       <c r="Y76" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z76" s="6" t="inlineStr">
@@ -10870,7 +10870,7 @@
       <c r="X77" s="6" t="n"/>
       <c r="Y77" s="4" t="inlineStr">
         <is>
-          <t>이니시오 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z77" s="6" t="inlineStr">
@@ -10995,12 +10995,12 @@
       <c r="X78" s="6" t="n"/>
       <c r="Y78" s="4" t="inlineStr">
         <is>
-          <t>니샤네 백화점</t>
+          <t>퍼퓸갤러리</t>
         </is>
       </c>
       <c r="Z78" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>편집숍(퍼퓸갤러리)</t>
         </is>
       </c>
       <c r="AA78" s="6" t="n"/>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="AE78" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11136,12 +11136,12 @@
       </c>
       <c r="Y79" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z79" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA79" s="6" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="AE79" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11281,12 +11281,12 @@
       </c>
       <c r="Y80" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z80" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA80" s="6" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="AE80" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="Y81" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z81" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA81" s="6" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="AE81" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11571,12 +11571,12 @@
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z82" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA82" s="6" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="AE82" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       <c r="X83" s="6" t="n"/>
       <c r="Y83" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z83" s="6" t="inlineStr">
@@ -11833,7 +11833,7 @@
       <c r="X84" s="6" t="n"/>
       <c r="Y84" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z84" s="6" t="inlineStr">
@@ -11962,7 +11962,7 @@
       <c r="X85" s="6" t="n"/>
       <c r="Y85" s="4" t="inlineStr">
         <is>
-          <t>톰 포드 뷰티 백화점</t>
+          <t>톰 포드 백화점</t>
         </is>
       </c>
       <c r="Z85" s="6" t="inlineStr">
@@ -12087,7 +12087,7 @@
       <c r="X86" s="6" t="n"/>
       <c r="Y86" s="4" t="inlineStr">
         <is>
-          <t>톰 포드 뷰티 백화점</t>
+          <t>톰 포드 백화점</t>
         </is>
       </c>
       <c r="Z86" s="6" t="inlineStr">
@@ -12216,7 +12216,7 @@
       <c r="X87" s="6" t="n"/>
       <c r="Y87" s="4" t="inlineStr">
         <is>
-          <t>톰 포드 뷰티 백화점</t>
+          <t>톰 포드 백화점</t>
         </is>
       </c>
       <c r="Z87" s="6" t="inlineStr">
@@ -12345,7 +12345,7 @@
       <c r="X88" s="6" t="n"/>
       <c r="Y88" s="4" t="inlineStr">
         <is>
-          <t>톰 포드 뷰티 백화점</t>
+          <t>톰 포드 백화점</t>
         </is>
       </c>
       <c r="Z88" s="6" t="inlineStr">
@@ -12474,7 +12474,7 @@
       <c r="X89" s="6" t="n"/>
       <c r="Y89" s="4" t="inlineStr">
         <is>
-          <t>톰 포드 뷰티 백화점</t>
+          <t>톰 포드 백화점</t>
         </is>
       </c>
       <c r="Z89" s="6" t="inlineStr">
@@ -12599,12 +12599,12 @@
       <c r="X90" s="6" t="n"/>
       <c r="Y90" s="4" t="inlineStr">
         <is>
-          <t>에르메스 뷰티 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z90" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA90" s="6" t="n"/>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="AE90" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -12724,12 +12724,12 @@
       <c r="X91" s="6" t="n"/>
       <c r="Y91" s="4" t="inlineStr">
         <is>
-          <t>아쿠아 디 파르마 백화점</t>
+          <t>아쿠아디파르마</t>
         </is>
       </c>
       <c r="Z91" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA91" s="6" t="n"/>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="AE91" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -12849,7 +12849,7 @@
       <c r="X92" s="6" t="n"/>
       <c r="Y92" s="4" t="inlineStr">
         <is>
-          <t>펜할리곤스 백화점</t>
+          <t>펜할리곤스</t>
         </is>
       </c>
       <c r="Z92" s="6" t="inlineStr">
@@ -12974,12 +12974,12 @@
       <c r="X93" s="6" t="n"/>
       <c r="Y93" s="4" t="inlineStr">
         <is>
-          <t>아틀리에 코롱 백화점</t>
+          <t>아틀리에 코롱</t>
         </is>
       </c>
       <c r="Z93" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA93" s="6" t="n"/>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="AE93" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       <c r="X94" s="6" t="n"/>
       <c r="Y94" s="4" t="inlineStr">
         <is>
-          <t>제르조프 백화점</t>
+          <t>퍼퓸갤러리</t>
         </is>
       </c>
       <c r="Z94" s="6" t="inlineStr">
         <is>
-          <t>백화점</t>
+          <t>편집숍(퍼퓸갤러리)</t>
         </is>
       </c>
       <c r="AA94" s="6" t="n"/>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AE94" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       <c r="X95" s="6" t="n"/>
       <c r="Y95" s="4" t="inlineStr">
         <is>
-          <t>에센트릭 몰큘스 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z95" s="6" t="inlineStr">
@@ -13337,7 +13337,7 @@
       <c r="X96" s="6" t="n"/>
       <c r="Y96" s="4" t="inlineStr">
         <is>
-          <t>에센트릭 몰큘스 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z96" s="6" t="inlineStr">
@@ -13454,12 +13454,12 @@
       <c r="X97" s="6" t="n"/>
       <c r="Y97" s="4" t="inlineStr">
         <is>
-          <t>줄리엣 해즈 어 건 백화점</t>
+          <t>줄리엣 해즈 어 건</t>
         </is>
       </c>
       <c r="Z97" s="6" t="inlineStr">
         <is>
-          <t>편집숍</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA97" s="6" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="AE97" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -13579,12 +13579,12 @@
       <c r="X98" s="6" t="n"/>
       <c r="Y98" s="4" t="inlineStr">
         <is>
-          <t>엑스 니힐로 백화점</t>
+          <t>엑스니힐로</t>
         </is>
       </c>
       <c r="Z98" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="AA98" s="6" t="n"/>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="AE98" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -13708,12 +13708,12 @@
       <c r="X99" s="6" t="n"/>
       <c r="Y99" s="4" t="inlineStr">
         <is>
-          <t>퍼퓸 드 말리 백화점</t>
+          <t>퍼퓸드말리</t>
         </is>
       </c>
       <c r="Z99" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA99" s="6" t="n"/>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AE99" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -13962,7 +13962,7 @@
       <c r="X101" s="6" t="n"/>
       <c r="Y101" s="4" t="inlineStr">
         <is>
-          <t>베르사체 향수 매장</t>
+          <t>베르사체 백화점</t>
         </is>
       </c>
       <c r="Z101" s="6" t="inlineStr">
@@ -14091,7 +14091,7 @@
       <c r="X102" s="6" t="n"/>
       <c r="Y102" s="4" t="inlineStr">
         <is>
-          <t>베르사체 향수 매장</t>
+          <t>베르사체 백화점</t>
         </is>
       </c>
       <c r="Z102" s="6" t="inlineStr">
@@ -14220,7 +14220,7 @@
       <c r="X103" s="6" t="n"/>
       <c r="Y103" s="4" t="inlineStr">
         <is>
-          <t>파코 라반 향수 매장</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z103" s="6" t="inlineStr">
@@ -14349,7 +14349,7 @@
       <c r="X104" s="6" t="n"/>
       <c r="Y104" s="4" t="inlineStr">
         <is>
-          <t>파코 라반 향수 매장</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z104" s="6" t="inlineStr">
@@ -14478,7 +14478,7 @@
       <c r="X105" s="6" t="n"/>
       <c r="Y105" s="4" t="inlineStr">
         <is>
-          <t>휴고 보스 향수 매장</t>
+          <t>휴고 보스 백화점</t>
         </is>
       </c>
       <c r="Z105" s="6" t="inlineStr">
@@ -14603,12 +14603,12 @@
       <c r="X106" s="6" t="n"/>
       <c r="Y106" s="4" t="inlineStr">
         <is>
-          <t>캘빈클라인 향수 매장</t>
+          <t>올리브영 향수</t>
         </is>
       </c>
       <c r="Z106" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA106" s="6" t="n"/>
@@ -14625,7 +14625,7 @@
       </c>
       <c r="AE106" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
       <c r="X107" s="6" t="n"/>
       <c r="Y107" s="4" t="inlineStr">
         <is>
-          <t>캐롤리나 헤레라 향수 매장</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z107" s="6" t="inlineStr">
@@ -14857,7 +14857,7 @@
       <c r="X108" s="6" t="n"/>
       <c r="Y108" s="4" t="inlineStr">
         <is>
-          <t>입생로랑 뷰티 백화점</t>
+          <t>입생로랑 백화점</t>
         </is>
       </c>
       <c r="Z108" s="6" t="inlineStr">
@@ -14982,12 +14982,12 @@
       <c r="X109" s="6" t="n"/>
       <c r="Y109" s="4" t="inlineStr">
         <is>
-          <t>랑콤 뷰티 백화점</t>
+          <t>랑콤 백화점</t>
         </is>
       </c>
       <c r="Z109" s="6" t="inlineStr">
         <is>
-          <t>백화점</t>
+          <t>백화점, 올리브영</t>
         </is>
       </c>
       <c r="AA109" s="6" t="n"/>
@@ -15107,7 +15107,7 @@
       <c r="X110" s="6" t="n"/>
       <c r="Y110" s="4" t="inlineStr">
         <is>
-          <t>몽블랑 향수 매장</t>
+          <t>올리브영 향수</t>
         </is>
       </c>
       <c r="Z110" s="6" t="inlineStr">
@@ -15232,7 +15232,7 @@
       <c r="X111" s="6" t="n"/>
       <c r="Y111" s="4" t="inlineStr">
         <is>
-          <t>조르지오 아르마니 뷰티 백화점</t>
+          <t>조르지오 아르마니 백화점</t>
         </is>
       </c>
       <c r="Z111" s="6" t="inlineStr">
@@ -15357,7 +15357,7 @@
       <c r="X112" s="6" t="n"/>
       <c r="Y112" s="4" t="inlineStr">
         <is>
-          <t>불가리 향수 매장</t>
+          <t>불가리 백화점</t>
         </is>
       </c>
       <c r="Z112" s="6" t="inlineStr">
@@ -15486,7 +15486,7 @@
       <c r="X113" s="6" t="n"/>
       <c r="Y113" s="4" t="inlineStr">
         <is>
-          <t>입생로랑 뷰티 백화점</t>
+          <t>입생로랑 백화점</t>
         </is>
       </c>
       <c r="Z113" s="6" t="inlineStr">
@@ -15615,7 +15615,7 @@
       <c r="X114" s="6" t="n"/>
       <c r="Y114" s="4" t="inlineStr">
         <is>
-          <t>프라다 뷰티 백화점</t>
+          <t>프라다 백화점</t>
         </is>
       </c>
       <c r="Z114" s="6" t="inlineStr">
@@ -15744,7 +15744,7 @@
       <c r="X115" s="6" t="n"/>
       <c r="Y115" s="4" t="inlineStr">
         <is>
-          <t>뮈글러 향수 매장</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z115" s="6" t="inlineStr">
@@ -15869,7 +15869,7 @@
       <c r="X116" s="6" t="n"/>
       <c r="Y116" s="4" t="inlineStr">
         <is>
-          <t>샤넬 백화점</t>
+          <t>샤넬 뷰티 백화점</t>
         </is>
       </c>
       <c r="Z116" s="6" t="inlineStr">
@@ -15994,7 +15994,7 @@
       <c r="X117" s="6" t="n"/>
       <c r="Y117" s="4" t="inlineStr">
         <is>
-          <t>샤넬 백화점</t>
+          <t>샤넬 뷰티 백화점</t>
         </is>
       </c>
       <c r="Z117" s="6" t="inlineStr">
@@ -16119,7 +16119,7 @@
       <c r="X118" s="6" t="n"/>
       <c r="Y118" s="4" t="inlineStr">
         <is>
-          <t>샤넬 백화점</t>
+          <t>샤넬 뷰티 백화점</t>
         </is>
       </c>
       <c r="Z118" s="6" t="inlineStr">
@@ -17147,12 +17147,12 @@
       </c>
       <c r="Y126" s="4" t="inlineStr">
         <is>
-          <t>에르메스 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z126" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA126" s="6" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="AE126" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -17292,12 +17292,12 @@
       </c>
       <c r="Y127" s="4" t="inlineStr">
         <is>
-          <t>에르메스 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z127" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA127" s="6" t="inlineStr">
@@ -17322,7 +17322,7 @@
       </c>
       <c r="AE127" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -17425,12 +17425,12 @@
       <c r="X128" s="6" t="n"/>
       <c r="Y128" s="4" t="inlineStr">
         <is>
-          <t>에르메스 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z128" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA128" s="6" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="AE128" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -17570,12 +17570,12 @@
       </c>
       <c r="Y129" s="4" t="inlineStr">
         <is>
-          <t>에르메스 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z129" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA129" s="6" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="AE129" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -17715,12 +17715,12 @@
       </c>
       <c r="Y130" s="4" t="inlineStr">
         <is>
-          <t>에르메스 백화점</t>
+          <t>에르메스 향수</t>
         </is>
       </c>
       <c r="Z130" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA130" s="6" t="inlineStr">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="AE130" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="Z141" s="6" t="inlineStr">
         <is>
-          <t>백화점</t>
+          <t>백화점, 올리브영</t>
         </is>
       </c>
       <c r="AA141" s="6" t="n"/>
@@ -19247,7 +19247,7 @@
       <c r="X142" s="6" t="n"/>
       <c r="Y142" s="4" t="inlineStr">
         <is>
-          <t>구찌 백화점</t>
+          <t>구찌 향수</t>
         </is>
       </c>
       <c r="Z142" s="6" t="inlineStr">
@@ -19372,7 +19372,7 @@
       <c r="X143" s="6" t="n"/>
       <c r="Y143" s="4" t="inlineStr">
         <is>
-          <t>구찌 백화점</t>
+          <t>구찌 향수</t>
         </is>
       </c>
       <c r="Z143" s="6" t="inlineStr">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="Z144" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA144" s="6" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="AE144" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="Z145" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA145" s="6" t="inlineStr">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="AE145" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -20045,7 +20045,7 @@
       <c r="X148" s="6" t="n"/>
       <c r="Y148" s="4" t="inlineStr">
         <is>
-          <t>장 폴 고티에 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z148" s="6" t="inlineStr">
@@ -20174,7 +20174,7 @@
       <c r="X149" s="6" t="n"/>
       <c r="Y149" s="4" t="inlineStr">
         <is>
-          <t>장 폴 고티에 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z149" s="6" t="inlineStr">
@@ -20299,7 +20299,7 @@
       <c r="X150" s="6" t="n"/>
       <c r="Y150" s="4" t="inlineStr">
         <is>
-          <t>장 폴 고티에 백화점</t>
+          <t>백화점 향수</t>
         </is>
       </c>
       <c r="Z150" s="6" t="inlineStr">
@@ -20424,7 +20424,7 @@
       <c r="X151" s="6" t="n"/>
       <c r="Y151" s="4" t="inlineStr">
         <is>
-          <t>마크 제이콥스 백화점</t>
+          <t>마크제이콥스</t>
         </is>
       </c>
       <c r="Z151" s="6" t="inlineStr">
@@ -20549,7 +20549,7 @@
       <c r="X152" s="6" t="n"/>
       <c r="Y152" s="4" t="inlineStr">
         <is>
-          <t>마크 제이콥스 백화점</t>
+          <t>마크제이콥스</t>
         </is>
       </c>
       <c r="Z152" s="6" t="inlineStr">
@@ -20678,7 +20678,7 @@
       <c r="X153" s="6" t="n"/>
       <c r="Y153" s="4" t="inlineStr">
         <is>
-          <t>이세이 미야케 백화점</t>
+          <t>올리브영 향수</t>
         </is>
       </c>
       <c r="Z153" s="6" t="inlineStr">
@@ -20811,7 +20811,7 @@
       <c r="X154" s="6" t="n"/>
       <c r="Y154" s="4" t="inlineStr">
         <is>
-          <t>이세이 미야케 백화점</t>
+          <t>올리브영 향수</t>
         </is>
       </c>
       <c r="Z154" s="6" t="inlineStr">
@@ -20936,7 +20936,7 @@
       <c r="X155" s="6" t="n"/>
       <c r="Y155" s="4" t="inlineStr">
         <is>
-          <t>돌체 앤 가바나 백화점</t>
+          <t>돌체앤가바나 백화점</t>
         </is>
       </c>
       <c r="Z155" s="6" t="inlineStr">
@@ -21061,7 +21061,7 @@
       <c r="X156" s="6" t="n"/>
       <c r="Y156" s="4" t="inlineStr">
         <is>
-          <t>돌체 앤 가바나 백화점</t>
+          <t>돌체앤가바나 백화점</t>
         </is>
       </c>
       <c r="Z156" s="6" t="inlineStr">
@@ -21198,7 +21198,7 @@
       <c r="X157" s="6" t="n"/>
       <c r="Y157" s="4" t="inlineStr">
         <is>
-          <t>돌체 앤 가바나 백화점</t>
+          <t>돌체앤가바나 백화점</t>
         </is>
       </c>
       <c r="Z157" s="6" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="Z158" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA158" s="6" t="n"/>
@@ -21345,7 +21345,7 @@
       </c>
       <c r="AE158" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -21453,7 +21453,7 @@
       </c>
       <c r="Z159" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="AA159" s="6" t="n"/>
@@ -21470,7 +21470,7 @@
       </c>
       <c r="AE159" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -21573,7 +21573,7 @@
       <c r="X160" s="6" t="n"/>
       <c r="Y160" s="4" t="inlineStr">
         <is>
-          <t>엘리자베스 아덴 올리브영</t>
+          <t>엘리자베스아덴</t>
         </is>
       </c>
       <c r="Z160" s="6" t="inlineStr">
@@ -21706,7 +21706,7 @@
       <c r="X161" s="6" t="n"/>
       <c r="Y161" s="4" t="inlineStr">
         <is>
-          <t>나르시소 로드리게즈 백화점</t>
+          <t>올리브영 향수</t>
         </is>
       </c>
       <c r="Z161" s="6" t="inlineStr">
@@ -21847,12 +21847,12 @@
       </c>
       <c r="Y162" s="4" t="inlineStr">
         <is>
-          <t>논픽션 올리브영</t>
+          <t>논픽션</t>
         </is>
       </c>
       <c r="Z162" s="6" t="inlineStr">
         <is>
-          <t>공식몰 · 올리브영 · 편집숍</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA162" s="6" t="inlineStr">
@@ -21877,7 +21877,7 @@
       </c>
       <c r="AE162" s="6" t="inlineStr">
         <is>
-          <t>미확인 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -21996,12 +21996,12 @@
       </c>
       <c r="Y163" s="4" t="inlineStr">
         <is>
-          <t>논픽션 올리브영</t>
+          <t>논픽션</t>
         </is>
       </c>
       <c r="Z163" s="6" t="inlineStr">
         <is>
-          <t>공식몰 · 올리브영 · 편집숍</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA163" s="6" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="AE163" s="6" t="inlineStr">
         <is>
-          <t>미확인 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -22149,12 +22149,12 @@
       </c>
       <c r="Y164" s="4" t="inlineStr">
         <is>
-          <t>논픽션 올리브영</t>
+          <t>논픽션</t>
         </is>
       </c>
       <c r="Z164" s="6" t="inlineStr">
         <is>
-          <t>공식몰 · 올리브영 · 편집숍</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="AA164" s="6" t="inlineStr">
@@ -22179,7 +22179,7 @@
       </c>
       <c r="AE164" s="6" t="inlineStr">
         <is>
-          <t>미확인 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="Y165" s="4" t="inlineStr">
         <is>
-          <t>러쉬 매장</t>
+          <t>러쉬</t>
         </is>
       </c>
       <c r="Z165" s="6" t="inlineStr">
@@ -22427,7 +22427,7 @@
       <c r="X166" s="6" t="n"/>
       <c r="Y166" s="4" t="inlineStr">
         <is>
-          <t>조 말론 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z166" s="6" t="inlineStr">
@@ -22548,7 +22548,7 @@
       <c r="X167" s="6" t="n"/>
       <c r="Y167" s="4" t="inlineStr">
         <is>
-          <t>조 말론 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z167" s="6" t="inlineStr">
@@ -22673,7 +22673,7 @@
       <c r="X168" s="6" t="n"/>
       <c r="Y168" s="4" t="inlineStr">
         <is>
-          <t>조 말론 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z168" s="6" t="inlineStr">
@@ -22798,7 +22798,7 @@
       <c r="X169" s="6" t="n"/>
       <c r="Y169" s="4" t="inlineStr">
         <is>
-          <t>조 말론 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z169" s="6" t="inlineStr">
@@ -22927,7 +22927,7 @@
       <c r="X170" s="6" t="n"/>
       <c r="Y170" s="4" t="inlineStr">
         <is>
-          <t>조 말론 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z170" s="6" t="inlineStr">
@@ -23052,7 +23052,7 @@
       <c r="X171" s="6" t="n"/>
       <c r="Y171" s="4" t="inlineStr">
         <is>
-          <t>조 말론 백화점</t>
+          <t>조말론런던</t>
         </is>
       </c>
       <c r="Z171" s="6" t="inlineStr">
@@ -23177,7 +23177,7 @@
       <c r="X172" s="6" t="n"/>
       <c r="Y172" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z172" s="6" t="inlineStr">
@@ -23314,7 +23314,7 @@
       <c r="X173" s="6" t="n"/>
       <c r="Y173" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z173" s="6" t="inlineStr">
@@ -23447,7 +23447,7 @@
       <c r="X174" s="6" t="n"/>
       <c r="Y174" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z174" s="6" t="inlineStr">
@@ -23584,7 +23584,7 @@
       <c r="X175" s="6" t="n"/>
       <c r="Y175" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z175" s="6" t="inlineStr">
@@ -23721,7 +23721,7 @@
       <c r="X176" s="6" t="n"/>
       <c r="Y176" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z176" s="6" t="inlineStr">
@@ -23858,7 +23858,7 @@
       <c r="X177" s="6" t="n"/>
       <c r="Y177" s="4" t="inlineStr">
         <is>
-          <t>딥티크 백화점</t>
+          <t>Diptyque 백화점</t>
         </is>
       </c>
       <c r="Z177" s="6" t="inlineStr">
@@ -23995,12 +23995,12 @@
       <c r="X178" s="6" t="n"/>
       <c r="Y178" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z178" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA178" s="6" t="inlineStr">
@@ -24025,7 +24025,7 @@
       </c>
       <c r="AE178" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -24132,12 +24132,12 @@
       <c r="X179" s="6" t="n"/>
       <c r="Y179" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z179" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA179" s="6" t="inlineStr">
@@ -24162,7 +24162,7 @@
       </c>
       <c r="AE179" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -24269,12 +24269,12 @@
       <c r="X180" s="6" t="n"/>
       <c r="Y180" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z180" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA180" s="6" t="inlineStr">
@@ -24299,7 +24299,7 @@
       </c>
       <c r="AE180" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -24410,12 +24410,12 @@
       <c r="X181" s="6" t="n"/>
       <c r="Y181" s="4" t="inlineStr">
         <is>
-          <t>바이레도 백화점</t>
+          <t>바이레도</t>
         </is>
       </c>
       <c r="Z181" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA181" s="6" t="inlineStr">
@@ -24440,7 +24440,7 @@
       </c>
       <c r="AE181" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="Y182" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z182" s="6" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="Y183" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z183" s="6" t="inlineStr">
@@ -24849,7 +24849,7 @@
       </c>
       <c r="Y184" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z184" s="6" t="inlineStr">
@@ -24994,7 +24994,7 @@
       </c>
       <c r="Y185" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z185" s="6" t="inlineStr">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="Y186" s="4" t="inlineStr">
         <is>
-          <t>르 라보 백화점</t>
+          <t>르 라보 성수</t>
         </is>
       </c>
       <c r="Z186" s="6" t="inlineStr">
@@ -25272,7 +25272,7 @@
       <c r="X187" s="6" t="n"/>
       <c r="Y187" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z187" s="6" t="inlineStr">
@@ -25397,7 +25397,7 @@
       <c r="X188" s="6" t="n"/>
       <c r="Y188" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z188" s="6" t="inlineStr">
@@ -25522,7 +25522,7 @@
       <c r="X189" s="6" t="n"/>
       <c r="Y189" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z189" s="6" t="inlineStr">
@@ -25651,7 +25651,7 @@
       <c r="X190" s="6" t="n"/>
       <c r="Y190" s="4" t="inlineStr">
         <is>
-          <t>메종 프란시스 커정 백화점</t>
+          <t>메종프란시스커정</t>
         </is>
       </c>
       <c r="Z190" s="6" t="inlineStr">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="AE194" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -26338,7 +26338,7 @@
       </c>
       <c r="AE195" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -26467,7 +26467,7 @@
       </c>
       <c r="AE196" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -26570,7 +26570,7 @@
       <c r="X197" s="6" t="n"/>
       <c r="Y197" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z197" s="6" t="inlineStr">
@@ -26703,7 +26703,7 @@
       <c r="X198" s="6" t="n"/>
       <c r="Y198" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z198" s="6" t="inlineStr">
@@ -26840,7 +26840,7 @@
       <c r="X199" s="6" t="n"/>
       <c r="Y199" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z199" s="6" t="inlineStr">
@@ -26973,7 +26973,7 @@
       <c r="X200" s="6" t="n"/>
       <c r="Y200" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z200" s="6" t="inlineStr">
@@ -27106,7 +27106,7 @@
       <c r="X201" s="6" t="n"/>
       <c r="Y201" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z201" s="6" t="inlineStr">
@@ -27239,7 +27239,7 @@
       <c r="X202" s="6" t="n"/>
       <c r="Y202" s="4" t="inlineStr">
         <is>
-          <t>메종 마르지엘라 백화점</t>
+          <t>메종 마르지엘라 향수</t>
         </is>
       </c>
       <c r="Z202" s="6" t="inlineStr">
@@ -27368,12 +27368,12 @@
       <c r="X203" s="6" t="n"/>
       <c r="Y203" s="4" t="inlineStr">
         <is>
-          <t>크리드 백화점</t>
+          <t>크리드 향수</t>
         </is>
       </c>
       <c r="Z203" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA203" s="6" t="inlineStr">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="AE203" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -27509,12 +27509,12 @@
       <c r="X204" s="6" t="n"/>
       <c r="Y204" s="4" t="inlineStr">
         <is>
-          <t>크리드 백화점</t>
+          <t>크리드 향수</t>
         </is>
       </c>
       <c r="Z204" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA204" s="6" t="inlineStr">
@@ -27539,7 +27539,7 @@
       </c>
       <c r="AE204" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -27646,12 +27646,12 @@
       <c r="X205" s="6" t="n"/>
       <c r="Y205" s="4" t="inlineStr">
         <is>
-          <t>크리드 백화점</t>
+          <t>크리드 향수</t>
         </is>
       </c>
       <c r="Z205" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA205" s="6" t="inlineStr">
@@ -27676,7 +27676,7 @@
       </c>
       <c r="AE205" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -27787,12 +27787,12 @@
       <c r="X206" s="6" t="n"/>
       <c r="Y206" s="4" t="inlineStr">
         <is>
-          <t>크리드 백화점</t>
+          <t>크리드 향수</t>
         </is>
       </c>
       <c r="Z206" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA206" s="6" t="inlineStr">
@@ -27817,7 +27817,7 @@
       </c>
       <c r="AE206" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -27924,12 +27924,12 @@
       <c r="X207" s="6" t="n"/>
       <c r="Y207" s="4" t="inlineStr">
         <is>
-          <t>파르팜 드 말리 백화점</t>
+          <t>퍼퓸드말리</t>
         </is>
       </c>
       <c r="Z207" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA207" s="6" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="AE207" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -28061,12 +28061,12 @@
       <c r="X208" s="6" t="n"/>
       <c r="Y208" s="4" t="inlineStr">
         <is>
-          <t>파르팜 드 말리 백화점</t>
+          <t>퍼퓸드말리</t>
         </is>
       </c>
       <c r="Z208" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA208" s="6" t="inlineStr">
@@ -28091,7 +28091,7 @@
       </c>
       <c r="AE208" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -28202,7 +28202,7 @@
       <c r="X209" s="6" t="n"/>
       <c r="Y209" s="4" t="inlineStr">
         <is>
-          <t>펜할리곤스 백화점</t>
+          <t>펜할리곤스</t>
         </is>
       </c>
       <c r="Z209" s="6" t="inlineStr">
@@ -28331,7 +28331,7 @@
       <c r="X210" s="6" t="n"/>
       <c r="Y210" s="4" t="inlineStr">
         <is>
-          <t>펜할리곤스 백화점</t>
+          <t>펜할리곤스</t>
         </is>
       </c>
       <c r="Z210" s="6" t="inlineStr">
@@ -28464,12 +28464,12 @@
       <c r="X211" s="6" t="n"/>
       <c r="Y211" s="4" t="inlineStr">
         <is>
-          <t>니샤네 백화점</t>
+          <t>퍼퓸갤러리</t>
         </is>
       </c>
       <c r="Z211" s="6" t="inlineStr">
         <is>
-          <t>[확인 필요]</t>
+          <t>편집숍(퍼퓸갤러리)</t>
         </is>
       </c>
       <c r="AA211" s="6" t="inlineStr">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="AE211" s="6" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -28602,7 +28602,7 @@
       </c>
       <c r="Z212" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA212" s="6" t="n"/>
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AE212" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -28723,7 +28723,7 @@
       </c>
       <c r="Z213" s="6" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="AA213" s="6" t="n"/>
@@ -28740,7 +28740,7 @@
       </c>
       <c r="AE213" s="6" t="inlineStr">
         <is>
-          <t>낮음 (앱에 표시 안 함)</t>
+          <t>보통 (앱에 표시)</t>
         </is>
       </c>
     </row>
@@ -32958,27 +32958,27 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>https://www.acquadiparma.com/default/en/authorised-retailers.html</t>
+          <t>https://map.naver.com/p/search/%EC%95%84%EC%BF%A0%EC%95%84%EB%94%94%ED%8C%8C%EB%A5%B4%EB%A7%88</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Official page itself 403 on fetch; seen via search snippet. Dept-store boutique (Lotte Jamsil Avenuel) only seen in news articles (not allowed source), so not recorded.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33054,27 +33054,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://map.naver.com/p/search/%EC%95%84%ED%8B%80%EB%A6%AC%EC%97%90%20%EC%BD%94%EB%A1%B1</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Only news/magazine sources (Lotte Jamsil boutique, re-entered Korea 2026) seen; no allowed official source verified.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33086,27 +33086,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>stores.burberry.com Hyundai Seoul page lists no beauty/fragrance service; Beauty Box COEX only from non-allowed article. Unverified.</t>
+          <t>stores.burberry.com Hyundai Seoul page lists no beauty/fragrance service; Beauty Box COEX only from non-allowed article. Unverified. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -33150,27 +33150,27 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://map.naver.com/p/search/%EB%B0%94%EC%9D%B4%EB%A0%88%EB%8F%84</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Flagship stores (Sinsa, Lotte World Mall) only in news sources (fashionbiz, insideretail), not allowed; official site fetch 404.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33182,27 +33182,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>No oliveyoung.co.kr or official evidence found; only marketplace results.</t>
+          <t>No oliveyoung.co.kr or official evidence found; only marketplace results. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -33278,27 +33278,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>No allowed source verified.</t>
+          <t>No allowed source verified. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -33310,27 +33310,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>https://www.shilladfs.com/estore/kr/en/p/3390883</t>
+          <t>https://map.naver.com/p/search/%ED%81%AC%EB%A6%AC%EB%93%9C%20%ED%96%A5%EC%88%98</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Shilla Duty Free online store listing (pages 403 on fetch); online listing, store counter implied but not confirmed.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33342,27 +33342,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>No allowed source verified.</t>
+          <t>No allowed source verified. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -33451,7 +33451,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>면세점, 올리브영</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Olive Young verified. Duty-free is from a news article only (weak), so excluded from the channel list... see evidence; channels list kept to 올리브영.</t>
+          <t>Olive Young verified. Duty-free is from a news article only (weak), so excluded from the channel list... see evidence; channels list kept to 올리브영. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -33506,27 +33506,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>https://m.shilladfs.com/estore/kr/ko/b/exnihilo</t>
+          <t>https://map.naver.com/p/search/%EC%97%91%EC%8A%A4%EB%8B%88%ED%9E%90%EB%A1%9C</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>News snippets (hankyung, heraldk) indicate Shinsegae/Lotte/Hyundai department store counters but those are not allowed source types, so 백화점 left out.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33538,27 +33538,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://m.shilladfs.com/estore/kr/ko/b/fredericmalle</t>
+          <t>https://map.naver.com/p/search/%ED%94%84%EB%A0%88%EB%8D%B0%EB%A6%AD%20%EB%A7%90%20%EB%B0%B1%ED%99%94%EC%A0%90</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Official site fredericmalle.com/kr appeared in results but store list not fetched; Vogue Korea (not allowed) mentions an Itaewon flagship, so 브랜드 매장 unverified.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33667,27 +33667,27 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>면세점</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://m.shilladfs.com/estore/kr/ko/b/hermes</t>
+          <t>https://map.naver.com/p/search/%EC%97%90%EB%A5%B4%EB%A9%94%EC%8A%A4%20%ED%96%A5%EC%88%98</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>hermes.com lists many Korean boutiques (Shinsegae Main/Gangnam, Hyundai Apgujeong, Dosan Maison) but pages did not state perfume is sold there; Shinsegae Main perfume boutique only in news. So 백화점/브랜드 매장 not recorded.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33828,27 +33828,27 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>편집숍</t>
+          <t>백화점</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://chicor.com/brand/0000000886</t>
+          <t>https://map.naver.com/p/search/%EC%A4%84%EB%A6%AC%EC%97%A3%20%ED%95%B4%EC%A6%88%20%EC%96%B4%20%EA%B1%B4</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Chicor page is online brand listing; offline SIKOR stock not confirmed. Only a temporary 더현대 서울 팝업 (Aug 2026, ended 8/13) found, not counted. Olive Young not verified.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33860,12 +33860,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -33875,12 +33875,12 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://m.lotteshopping.com/shoppingNews/shoppingNewsDetail?shpgNewsNo=SNM00000000000094668</t>
+          <t>https://map.naver.com/p/search/%ED%82%AC%EB%A6%AC%EC%95%88%20%EB%B0%B1%ED%99%94%EC%A0%90</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Lotte news item described a period opening (Aug 18-31); current permanence unverified. Other stores not verified.</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -33902,7 +33902,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>백화점, 면세점</t>
+          <t>백화점, 올리브영</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -33913,7 +33913,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Hyundai evidence from search summary; Shilla DFS is online duty-free shop, counters implied.</t>
+          <t>Hyundai evidence from search summary; Shilla DFS is online duty-free shop, counters implied. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -34042,7 +34042,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Online listing; offline store stock not confirmed. Department store not verified.</t>
+          <t>Online listing; offline store stock not confirmed. Department store not verified. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -34064,7 +34064,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>올리브영, 백화점</t>
+          <t>올리브영</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -34075,7 +34075,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Department store entry is probably the main (non-fragrance) Montblanc boutique; fragrance counter unconfirmed.</t>
+          <t>Department store entry is probably the main (non-fragrance) Montblanc boutique; fragrance counter unconfirmed. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Online listing.</t>
+          <t>Online listing. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -34151,27 +34151,27 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>편집숍(퍼퓸갤러리)</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://map.naver.com/p/search/%ED%8D%BC%ED%93%B8%EA%B0%A4%EB%9F%AC%EB%A6%AC</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>No Korean retail evidence found in allowed sources.</t>
+          <t>네이버 지도에서 '니샤네' 검색 시 퍼퓸갤러리 매장이 표시됨(2026-10-13). 2024년 퍼퓸갤러리 공식 런칭 보도(mydaily). 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -34215,27 +34215,27 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>백화점, 면세점</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://map.naver.com/p/search/%ED%8D%BC%ED%93%B8%EB%93%9C%EB%A7%90%EB%A6%AC</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Only SSG.com online listings of '퍼퓸드말리 공식수입정품' via 신세계백화점 mall; physical counter not verified (a floor-guide hit was unreliable).</t>
+          <t>네이버 지도 검색(2026-10-13)에서 이 브랜드의 매장·카운터(화장품·향수 분류)가 확인됨. 공식 매장 목록은 아님.</t>
         </is>
       </c>
     </row>
@@ -34364,7 +34364,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Online brand page verified; in-store testing not confirmed. Department store not verified.</t>
+          <t>Online brand page verified; in-store testing not confirmed. Department store not verified. | 올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
         </is>
       </c>
     </row>
@@ -34408,28 +34408,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>낮음</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>백화점</t>
+          <t>편집숍(퍼퓸갤러리)</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>https://www.galleria.co.kr/dispctg/initBrandShop.action?shop_brand_no=2300008554
-https://www.thehyundai.com/front/dpa/searchSectItem.thd?brndCd=MA14910&amp;pSectId=30064</t>
+          <t>https://map.naver.com/p/search/%ED%8D%BC%ED%93%B8%EA%B0%A4%EB%9F%AC%EB%A6%AC</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Weak: online brand listings; physical counters not confirmed.</t>
+          <t>네이버 지도에서 '제르조프' 검색 시 퍼퓸갤러리 매장이 표시됨(2026-10-13). 브랜드 취급 여부는 매장 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -34474,25 +34473,29 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>미확인</t>
+          <t>보통</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>표시 안 함</t>
+          <t>표시</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>공식몰 · 올리브영 · 편집숍</t>
+          <t>브랜드 매장</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>https://nonfiction.kr/</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n"/>
+          <t>https://map.naver.com/p/search/%EB%85%BC%ED%94%BD%EC%85%98</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>네이버 지도에서 논픽션 삼청·성수·신사가 '화장품,향수'로 확인됨(2026-10-13). 매거진 보도와 일치. 공식 목록은 아님.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -34548,7 +34551,11 @@
           <t>https://www.ssg.com/disp/brandShop.ssg?brandId=2000003268</t>
         </is>
       </c>
-      <c r="F51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -34576,7 +34583,11 @@
           <t>https://www.elizabetharden.co.kr/</t>
         </is>
       </c>
-      <c r="F52" s="4" t="n"/>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>올리브영 향수 Top 120 브랜드 목록(2026-10-13, 온라인 브랜드 필터)에 있음. 매장별 취급·시향 가능 여부는 확인하지 못함.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/perfumes-draft.xlsx
+++ b/docs/perfumes-draft.xlsx
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE213"/>
+  <dimension ref="A1:AG213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -979,6 +979,16 @@
           <t>channels_status</t>
         </is>
       </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>mood_scores</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>moods_v1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1039,7 +1049,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, zesty, cool, calm</t>
+          <t>clean, fresh, zesty, calm, cool</t>
         </is>
       </c>
       <c r="N2" s="5" t="n"/>
@@ -1112,6 +1122,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,zesty:2,calm:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>clean, fresh, zesty, cool, calm</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1172,7 +1192,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, clean, elegant, cool</t>
+          <t>fresh, zesty, elegant, clean, cool</t>
         </is>
       </c>
       <c r="N3" s="5" t="n"/>
@@ -1237,6 +1257,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,elegant:2,clean:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>fresh, zesty, clean, elegant, cool</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1297,7 +1327,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, clean, cool</t>
+          <t>clean, fresh, zesty, cool, lovely</t>
         </is>
       </c>
       <c r="N4" s="5" t="n"/>
@@ -1362,6 +1392,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,zesty:2,cool:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>zesty, fresh, clean, cool</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1422,7 +1462,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, zesty, cool</t>
+          <t>clean, fresh, zesty, cool, soft</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -1491,6 +1531,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,zesty:2,cool:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>clean, fresh, zesty, cool</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1551,7 +1601,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>soft, fresh, elegant, lovely, sweet</t>
+          <t>lovely, soft, fresh, sweet, elegant</t>
         </is>
       </c>
       <c r="N6" s="5" t="n"/>
@@ -1616,6 +1666,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>lovely:2,soft:2,fresh:1,sweet:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>soft, fresh, elegant, lovely, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1676,7 +1736,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>soft, lovely, fresh, sweet, elegant</t>
+          <t>fresh, lovely, soft, sweet, elegant</t>
         </is>
       </c>
       <c r="N7" s="5" t="n"/>
@@ -1741,6 +1801,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>fresh:2,lovely:2,soft:2,sweet:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>soft, lovely, fresh, sweet, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1801,7 +1871,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, fresh, warm</t>
+          <t>sweet, lovely, cozy, fresh, warm</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -1890,6 +1960,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,cozy:1,fresh:1,warm:1</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>sweet, lovely, fresh, warm</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1950,7 +2030,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, sweet, soft</t>
+          <t>sweet, lovely, fresh, zesty, soft</t>
         </is>
       </c>
       <c r="N9" s="5" t="n"/>
@@ -2015,6 +2095,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,fresh:1,zesty:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>lovely, fresh, sweet, soft</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2075,7 +2165,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>elegant, sweet, warm, lovely</t>
+          <t>sweet, elegant, warm, lovely, sensual</t>
         </is>
       </c>
       <c r="N10" s="5" t="n"/>
@@ -2140,6 +2230,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>sweet:2,elegant:2,warm:1,lovely:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>elegant, sweet, warm, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2200,7 +2300,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, clean</t>
+          <t>clean, cool, calm, fresh</t>
         </is>
       </c>
       <c r="N11" s="5" t="n"/>
@@ -2265,6 +2365,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,calm:1,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>cool, fresh, clean</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2325,7 +2435,7 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>cool, calm, fresh, clean</t>
+          <t>clean, cool, calm, fresh, soft</t>
         </is>
       </c>
       <c r="N12" s="5" t="n"/>
@@ -2390,6 +2500,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,calm:1,fresh:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>cool, calm, fresh, clean</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2450,7 +2570,7 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>cool, clean, fresh</t>
+          <t>clean, cool, fresh, calm, zesty</t>
         </is>
       </c>
       <c r="N13" s="5" t="n"/>
@@ -2515,6 +2635,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,fresh:2,calm:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>cool, clean, fresh</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2575,7 +2705,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>fresh, calm, soft</t>
+          <t>calm, fresh, cool, soft</t>
         </is>
       </c>
       <c r="N14" s="5" t="n"/>
@@ -2640,6 +2770,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>calm:2,fresh:2,cool:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>fresh, calm, soft</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2700,7 +2840,7 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, soft</t>
+          <t>cool, fresh, calm, soft</t>
         </is>
       </c>
       <c r="N15" s="5" t="n"/>
@@ -2765,6 +2905,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,calm:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>fresh, cool, soft</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2825,7 +2975,7 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, calm, cool</t>
+          <t>clean, fresh, calm, cool, soft</t>
         </is>
       </c>
       <c r="N16" s="5" t="n"/>
@@ -2890,6 +3040,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,calm:1,cool:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>clean, fresh, calm, cool</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2950,7 +3110,7 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>fresh, deep, warm</t>
+          <t>fresh, warm, clean, deep</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
@@ -3019,6 +3179,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>fresh:2,warm:2,clean:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>fresh, deep, warm</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3079,7 +3249,7 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>fresh, elegant, calm, deep</t>
+          <t>fresh, calm, cool, elegant, deep</t>
         </is>
       </c>
       <c r="N18" s="5" t="n"/>
@@ -3144,6 +3314,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>fresh:2,calm:1,cool:1,elegant:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>fresh, elegant, calm, deep</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3204,7 +3384,7 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, sensual, cozy</t>
+          <t>warm, sweet, sensual, cozy, fresh, deep</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
@@ -3273,6 +3453,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,sensual:2,cozy:1,fresh:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>sweet, warm, sensual, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3333,7 +3523,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, elegant, warm</t>
+          <t>sweet, lovely, warm, elegant, sensual</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -3402,6 +3592,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,warm:1,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>sweet, lovely, elegant, warm</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3462,7 +3662,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>soft, lovely, fresh, elegant</t>
+          <t>lovely, soft, clean, fresh, elegant</t>
         </is>
       </c>
       <c r="N21" s="5" t="n"/>
@@ -3527,6 +3727,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>lovely:2,soft:2,clean:1,fresh:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>soft, lovely, fresh, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3587,7 +3797,7 @@
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>soft, lovely, elegant, warm</t>
+          <t>lovely, soft, warm, elegant, sensual</t>
         </is>
       </c>
       <c r="N22" s="5" t="n"/>
@@ -3652,6 +3862,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>lovely:2,soft:2,warm:1,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>soft, lovely, elegant, warm</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3712,7 +3932,7 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm, lovely, fresh</t>
+          <t>lovely, elegant, fresh, zesty, warm, sensual</t>
         </is>
       </c>
       <c r="N23" s="5" t="n"/>
@@ -3777,6 +3997,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,fresh:1,zesty:1,warm:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>elegant, warm, lovely, fresh</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3837,7 +4067,7 @@
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>elegant, lovely, sweet, soft</t>
+          <t>lovely, elegant, sweet, sensual, soft</t>
         </is>
       </c>
       <c r="N24" s="5" t="n"/>
@@ -3902,6 +4132,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,sweet:1,sensual:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>elegant, lovely, sweet, soft</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3962,7 +4202,7 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>lovely, soft, elegant</t>
+          <t>lovely, elegant, sensual, soft</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
@@ -4031,6 +4271,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,sensual:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>lovely, soft, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -4091,7 +4341,7 @@
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, calm, clean</t>
+          <t>elegant, soft, calm, clean, lovely</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
@@ -4160,6 +4410,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>elegant:2,soft:2,calm:1,clean:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>elegant, soft, calm, clean</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -4220,7 +4480,7 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>elegant, clean, soft, calm</t>
+          <t>elegant, soft, calm, clean, sensual</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -4289,6 +4549,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>elegant:2,soft:2,calm:1,clean:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>elegant, clean, soft, calm</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -4349,7 +4619,7 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>calm, soft, clean, elegant</t>
+          <t>calm, clean, soft, elegant</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -4418,6 +4688,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>calm:2,clean:2,soft:2,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>calm, soft, clean, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4478,7 +4758,7 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, cozy, deep, calm</t>
+          <t>elegant, soft, calm, cozy, sweet, deep</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -4547,6 +4827,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>elegant:2,soft:2,calm:1,cozy:1,sweet:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>soft, elegant, cozy, deep, calm</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4607,7 +4897,7 @@
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, lovely, clean, calm</t>
+          <t>lovely, soft, calm, clean, elegant</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr">
@@ -4676,6 +4966,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>lovely:2,soft:2,calm:1,clean:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>soft, elegant, lovely, clean, calm</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -4736,7 +5036,7 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm</t>
+          <t>clean, soft, calm, elegant</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr">
@@ -4825,6 +5125,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>clean:2,soft:2,calm:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>clean, soft, calm</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4885,7 +5195,7 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, cozy, calm</t>
+          <t>clean, cozy, soft, calm</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
@@ -4974,6 +5284,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>clean:2,cozy:2,soft:2,calm:1</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>clean, soft, cozy, calm</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -5034,7 +5354,7 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>sensual, warm, elegant, cozy</t>
+          <t>cozy, sensual, warm, elegant, soft</t>
         </is>
       </c>
       <c r="N33" s="5" t="n"/>
@@ -5099,6 +5419,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>cozy:2,sensual:2,warm:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>sensual, warm, elegant, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -5159,7 +5489,7 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>soft, clean, cozy, calm</t>
+          <t>cozy, soft, calm, clean, sensual</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -5228,6 +5558,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>cozy:2,soft:2,calm:1,clean:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>soft, clean, cozy, calm</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -5288,7 +5628,7 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, warm, sweet, soft</t>
+          <t>sweet, soft, clean, cozy, fresh, warm</t>
         </is>
       </c>
       <c r="N35" s="5" t="n"/>
@@ -5353,6 +5693,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>sweet:2,soft:2,clean:1,cozy:1,fresh:1,warm:1</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>fresh, clean, warm, sweet, soft</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -5413,7 +5763,7 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, calm, fresh</t>
+          <t>warm, deep, calm, fresh</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -5482,6 +5832,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,calm:1,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>deep, warm, calm, fresh</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -5542,7 +5902,7 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>fresh, elegant, warm, lovely</t>
+          <t>fresh, lovely, zesty, warm, elegant, sensual</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr">
@@ -5611,6 +5971,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>fresh:2,lovely:2,zesty:1,warm:1,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>fresh, elegant, warm, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -5671,7 +6041,7 @@
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, calm, cozy</t>
+          <t>warm, deep, calm, cozy, sensual</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr">
@@ -5760,6 +6130,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,calm:1,cozy:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>warm, deep, calm, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -5820,7 +6200,7 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>calm, warm, cozy, elegant</t>
+          <t>calm, warm, cozy, elegant, deep</t>
         </is>
       </c>
       <c r="N39" s="5" t="n"/>
@@ -5885,6 +6265,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>calm:2,warm:2,cozy:1,elegant:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>calm, warm, cozy, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5945,7 +6335,7 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>elegant, deep, warm, sensual</t>
+          <t>warm, deep, sensual, elegant</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
@@ -6014,6 +6404,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>elegant, deep, warm, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -6074,7 +6474,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>calm, fresh, warm, cozy</t>
+          <t>fresh, warm, calm, cozy, deep</t>
         </is>
       </c>
       <c r="N41" s="5" t="n"/>
@@ -6159,6 +6559,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>fresh:2,warm:2,calm:1,cozy:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>calm, fresh, warm, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -6219,7 +6629,7 @@
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, elegant, cozy</t>
+          <t>warm, sweet, cozy, elegant, sensual</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
@@ -6288,6 +6698,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,cozy:1,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>sweet, warm, elegant, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -6348,7 +6768,7 @@
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>warm, sensual, elegant, deep, sweet</t>
+          <t>warm, elegant, deep, sensual, sweet</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr">
@@ -6417,6 +6837,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>warm:2,elegant:2,deep:2,sensual:2,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>warm, sensual, elegant, deep, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -6477,7 +6907,7 @@
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, soft, sweet</t>
+          <t>warm, sweet, elegant, sensual, soft</t>
         </is>
       </c>
       <c r="N44" s="5" t="n"/>
@@ -6542,6 +6972,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,elegant:1,sensual:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>warm, elegant, soft, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -6602,7 +7042,7 @@
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>sweet, sensual, warm, deep</t>
+          <t>sweet, deep, sensual, warm</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
@@ -6671,6 +7111,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>sweet:2,deep:2,sensual:2,warm:1</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>sweet, sensual, warm, deep</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -6731,7 +7181,7 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, cozy, elegant</t>
+          <t>sweet, lovely, cozy, warm, elegant</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -6800,6 +7250,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,cozy:1,warm:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>sweet, lovely, cozy, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -6860,7 +7320,7 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, cozy, sensual, deep</t>
+          <t>cozy, warm, sweet, deep, sensual</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
@@ -6929,6 +7389,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,sweet:2,deep:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>warm, sweet, cozy, sensual, deep</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -6989,7 +7459,7 @@
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>sweet, deep, sensual, warm</t>
+          <t>sweet, deep, sensual, cozy, warm</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr">
@@ -7058,6 +7528,16 @@
           <t>미확인</t>
         </is>
       </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>sweet:2,deep:2,sensual:2,cozy:1,warm:1</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>sweet, deep, sensual, warm</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -7118,7 +7598,7 @@
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, deep, sweet</t>
+          <t>cozy, warm, deep, sweet, sensual</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr">
@@ -7207,6 +7687,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,deep:2,sweet:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>cozy, warm, deep, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -7267,7 +7757,7 @@
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sensual</t>
+          <t>warm, deep, sensual, cozy, sweet</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr">
@@ -7336,6 +7826,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,cozy:1,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>warm, cozy, deep, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -7396,7 +7896,7 @@
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sweet, sensual</t>
+          <t>warm, sweet, deep, cozy, sensual</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
@@ -7465,6 +7965,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,deep:2,cozy:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>warm, cozy, deep, sweet, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -7525,7 +8035,7 @@
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm</t>
+          <t>clean, calm, sensual, soft</t>
         </is>
       </c>
       <c r="N52" s="5" t="n"/>
@@ -7610,6 +8120,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>clean:2,calm:1,sensual:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>clean, soft, calm</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -7670,7 +8190,7 @@
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>elegant, deep, warm, sensual</t>
+          <t>deep, sensual, warm, elegant</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
@@ -7759,6 +8279,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>deep:2,sensual:2,warm:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>elegant, deep, warm, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -7819,7 +8349,7 @@
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>calm, cozy, deep</t>
+          <t>calm, cozy, warm, deep</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr">
@@ -7908,6 +8438,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>calm:2,cozy:1,warm:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>calm, cozy, deep</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -7968,7 +8508,7 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, clean, cool</t>
+          <t>clean, fresh, zesty, cool</t>
         </is>
       </c>
       <c r="N55" s="5" t="n"/>
@@ -8053,6 +8593,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,zesty:2,cool:1</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>fresh, zesty, clean, cool</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -8113,7 +8663,7 @@
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>sweet, soft, cozy, warm, lovely</t>
+          <t>sweet, lovely, soft, cozy, warm</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
@@ -8182,6 +8732,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,soft:2,cozy:1,warm:1</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>sweet, soft, cozy, warm, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -8242,7 +8802,7 @@
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>sweet, deep, warm, sensual, cozy</t>
+          <t>sweet, deep, cozy, warm, sensual</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
@@ -8311,6 +8871,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>sweet:2,deep:2,cozy:1,warm:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>sweet, deep, warm, sensual, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -8371,7 +8941,7 @@
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>fresh, elegant, sweet, deep</t>
+          <t>deep, fresh, warm, sweet, elegant</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr">
@@ -8440,6 +9010,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>deep:2,fresh:1,warm:1,sweet:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>fresh, elegant, sweet, deep</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -8500,7 +9080,7 @@
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, clean</t>
+          <t>clean, fresh, calm, cool, zesty</t>
         </is>
       </c>
       <c r="N59" s="5" t="n"/>
@@ -8565,6 +9145,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,calm:1,cool:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>fresh, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -8625,7 +9215,7 @@
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, clean</t>
+          <t>clean, cool, fresh, zesty</t>
         </is>
       </c>
       <c r="N60" s="5" t="n"/>
@@ -8690,6 +9280,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,fresh:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>cool, fresh, clean</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -8750,7 +9350,7 @@
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, clean, elegant</t>
+          <t>cool, fresh, clean, zesty, elegant</t>
         </is>
       </c>
       <c r="N61" s="5" t="n"/>
@@ -8815,6 +9415,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,clean:1,zesty:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>fresh, cool, clean, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -8875,7 +9485,7 @@
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>elegant, deep, warm, sensual</t>
+          <t>elegant, deep, sensual, warm</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr">
@@ -8944,6 +9554,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>elegant:2,deep:2,sensual:2,warm:1</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>elegant, deep, warm, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -9004,7 +9624,7 @@
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, sensual, deep</t>
+          <t>cozy, warm, sensual, deep, soft</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr">
@@ -9073,6 +9693,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,sensual:2,deep:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>warm, cozy, sensual, deep</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -9133,7 +9763,7 @@
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>elegant, sensual, warm</t>
+          <t>elegant, sensual, warm, sweet, lovely</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr">
@@ -9202,6 +9832,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>elegant:2,sensual:2,warm:1,sweet:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>elegant, sensual, warm</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -9262,7 +9902,7 @@
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>fresh, soft, cool, calm</t>
+          <t>fresh, soft, calm, clean, cool, lovely</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr">
@@ -9331,6 +9971,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>fresh:2,soft:2,calm:1,clean:1,cool:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>fresh, soft, cool, calm</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -9391,7 +10041,7 @@
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>soft, sweet, lovely, elegant</t>
+          <t>sweet, lovely, soft, elegant, sensual</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
@@ -9460,6 +10110,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,soft:2,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>soft, sweet, lovely, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -9520,7 +10180,7 @@
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, cool, clean</t>
+          <t>cool, fresh, zesty, clean</t>
         </is>
       </c>
       <c r="N67" s="5" t="n"/>
@@ -9585,6 +10245,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,zesty:2,clean:1</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>zesty, fresh, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -9645,7 +10315,7 @@
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>lovely, sweet, soft, fresh</t>
+          <t>lovely, soft, fresh, sweet</t>
         </is>
       </c>
       <c r="N68" s="5" t="n"/>
@@ -9710,6 +10380,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>lovely:2,soft:2,fresh:1,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>lovely, sweet, soft, fresh</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -9859,6 +10539,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>calm:2,deep:2,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>calm, deep, fresh</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -9919,7 +10609,7 @@
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, clean, cool</t>
+          <t>fresh, zesty, calm, clean, cool</t>
         </is>
       </c>
       <c r="N70" s="5" t="n"/>
@@ -10004,6 +10694,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,calm:1,clean:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>fresh, zesty, clean, cool</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -10064,7 +10764,7 @@
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>lovely, elegant, sweet, soft</t>
+          <t>sweet, lovely, elegant, sensual, soft</t>
         </is>
       </c>
       <c r="N71" s="5" t="n"/>
@@ -10129,6 +10829,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,elegant:2,sensual:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>lovely, elegant, sweet, soft</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -10189,7 +10899,7 @@
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, sweet, deep</t>
+          <t>warm, sweet, elegant, deep, sensual</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr">
@@ -10258,6 +10968,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,elegant:1,deep:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>warm, elegant, sweet, deep</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -10318,7 +11038,7 @@
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, zesty, cool</t>
+          <t>clean, fresh, cool, zesty, soft</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr">
@@ -10387,6 +11107,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,cool:1,zesty:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>clean, fresh, zesty, cool</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -10447,7 +11177,7 @@
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>sensual, deep, warm, elegant</t>
+          <t>deep, sensual, warm, sweet, elegant</t>
         </is>
       </c>
       <c r="N74" s="5" t="n"/>
@@ -10512,6 +11242,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>deep:2,sensual:2,warm:1,sweet:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>sensual, deep, warm, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -10572,7 +11312,7 @@
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>warm, sensual, cozy, deep, sweet</t>
+          <t>warm, sweet, sensual, cozy, deep</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
@@ -10641,6 +11381,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,sensual:2,cozy:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>warm, sensual, cozy, deep, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -10701,7 +11451,7 @@
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>warm, soft, cozy, sweet</t>
+          <t>cozy, warm, sweet, sensual, soft</t>
         </is>
       </c>
       <c r="N76" s="5" t="n"/>
@@ -10766,6 +11516,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,sweet:1,sensual:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>warm, soft, cozy, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -10826,7 +11586,7 @@
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, sensual, elegant</t>
+          <t>warm, deep, sensual, elegant</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr">
@@ -10895,6 +11655,16 @@
           <t>미확인</t>
         </is>
       </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>deep, warm, sensual, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -10955,7 +11725,7 @@
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, elegant</t>
+          <t>fresh, zesty, calm, elegant</t>
         </is>
       </c>
       <c r="N78" s="5" t="n"/>
@@ -11020,6 +11790,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,calm:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>fresh, zesty, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -11080,7 +11860,7 @@
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>soft, clean, calm, lovely</t>
+          <t>calm, soft, clean, lovely, elegant</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr">
@@ -11169,6 +11949,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>calm:2,soft:2,clean:1,lovely:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>soft, clean, calm, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -11229,7 +12019,7 @@
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, soft, clean, warm</t>
+          <t>fresh, zesty, clean, warm, soft</t>
         </is>
       </c>
       <c r="N80" s="5" t="n"/>
@@ -11314,6 +12104,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,clean:1,warm:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>fresh, zesty, soft, clean, warm</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -11374,7 +12174,7 @@
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>elegant, deep, soft</t>
+          <t>elegant, lovely, deep, sensual, soft</t>
         </is>
       </c>
       <c r="N81" s="5" t="n"/>
@@ -11459,6 +12259,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>elegant:2,lovely:1,deep:1,sensual:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>elegant, deep, soft</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -11519,7 +12329,7 @@
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, soft</t>
+          <t>cozy, warm, sweet, deep, soft</t>
         </is>
       </c>
       <c r="N82" s="5" t="n"/>
@@ -11604,6 +12414,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,sweet:1,deep:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>cozy, warm, soft</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -11664,7 +12484,7 @@
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, soft, calm</t>
+          <t>cozy, warm, calm, sweet, soft</t>
         </is>
       </c>
       <c r="N83" s="5" t="inlineStr">
@@ -11733,6 +12553,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,calm:1,sweet:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>warm, cozy, soft, calm</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -11793,7 +12623,7 @@
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>warm, elegant, cozy, calm</t>
+          <t>warm, calm, cozy, elegant, sensual</t>
         </is>
       </c>
       <c r="N84" s="5" t="n"/>
@@ -11858,6 +12688,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>warm:2,calm:1,cozy:1,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>warm, elegant, cozy, calm</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -11918,7 +12758,7 @@
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>sweet, sensual, warm, elegant</t>
+          <t>warm, sweet, sensual, elegant, deep</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr">
@@ -11987,6 +12827,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,sensual:2,elegant:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>sweet, sensual, warm, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -12047,7 +12897,7 @@
       </c>
       <c r="M86" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, elegant</t>
+          <t>warm, sweet, lovely, elegant, sensual</t>
         </is>
       </c>
       <c r="N86" s="5" t="n"/>
@@ -12112,6 +12962,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,lovely:1,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>warm, sweet, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -12172,7 +13032,7 @@
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant, sensual</t>
+          <t>deep, sensual, warm, elegant</t>
         </is>
       </c>
       <c r="N87" s="5" t="inlineStr">
@@ -12241,6 +13101,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>deep:2,sensual:2,warm:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>deep, warm, elegant, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -12301,7 +13171,7 @@
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>sensual, deep, elegant, warm</t>
+          <t>deep, sensual, warm, sweet, elegant</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
@@ -12370,6 +13240,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>deep:2,sensual:2,warm:1,sweet:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>sensual, deep, elegant, warm</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -12430,7 +13310,7 @@
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>warm, sensual, deep</t>
+          <t>warm, deep, sensual, cozy</t>
         </is>
       </c>
       <c r="N89" s="5" t="inlineStr">
@@ -12499,6 +13379,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,cozy:1</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>warm, sensual, deep</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -12559,7 +13449,7 @@
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>calm, fresh, warm, elegant</t>
+          <t>calm, cozy, fresh, warm, elegant</t>
         </is>
       </c>
       <c r="N90" s="5" t="n"/>
@@ -12624,6 +13514,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>calm:2,cozy:1,fresh:1,warm:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>calm, fresh, warm, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -12684,7 +13584,7 @@
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, cool, clean</t>
+          <t>cool, fresh, calm, clean, zesty</t>
         </is>
       </c>
       <c r="N91" s="5" t="n"/>
@@ -12749,6 +13649,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,calm:1,clean:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>fresh, zesty, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -12809,7 +13719,7 @@
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, cool, calm</t>
+          <t>cool, fresh, calm, clean, zesty</t>
         </is>
       </c>
       <c r="N92" s="5" t="n"/>
@@ -12874,6 +13784,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,calm:1,clean:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>fresh, clean, cool, calm</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -12934,7 +13854,7 @@
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, sweet, clean</t>
+          <t>fresh, zesty, clean, sweet</t>
         </is>
       </c>
       <c r="N93" s="5" t="n"/>
@@ -12999,6 +13919,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,clean:1,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>zesty, fresh, sweet, clean</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -13059,7 +13989,7 @@
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, cozy, sensual, deep</t>
+          <t>warm, sweet, sensual, cozy, deep</t>
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr">
@@ -13128,6 +14058,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,sensual:2,cozy:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>sweet, warm, cozy, sensual, deep</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -13180,7 +14120,7 @@
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, calm</t>
+          <t>calm, clean, cool, soft</t>
         </is>
       </c>
       <c r="N95" s="5" t="n"/>
@@ -13245,6 +14185,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>calm:2,clean:2,cool:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>clean, soft, calm</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -13362,6 +14312,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>clean:2,soft:2,calm:1,cozy:1</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>clean, soft, calm, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -13479,6 +14439,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>clean:2,soft:2,calm:1,cozy:1</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>clean, soft, calm, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -13539,7 +14509,7 @@
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>lovely, sweet, elegant, soft</t>
+          <t>sweet, lovely, elegant, soft</t>
         </is>
       </c>
       <c r="N98" s="5" t="n"/>
@@ -13604,6 +14574,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>lovely, sweet, elegant, soft</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -13664,7 +14644,7 @@
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, deep, sensual</t>
+          <t>warm, deep, cozy, sweet, sensual</t>
         </is>
       </c>
       <c r="N99" s="5" t="inlineStr">
@@ -13733,6 +14713,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,cozy:1,sweet:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>warm, cozy, deep, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -13793,7 +14783,7 @@
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, sweet, deep</t>
+          <t>cozy, warm, sweet, deep, sensual</t>
         </is>
       </c>
       <c r="N100" s="5" t="inlineStr">
@@ -13862,6 +14852,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,sweet:2,deep:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>warm, cozy, sweet, deep</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -13922,7 +14922,7 @@
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, lovely, soft</t>
+          <t>zesty, lovely, clean, fresh, soft</t>
         </is>
       </c>
       <c r="N101" s="5" t="n"/>
@@ -13987,6 +14987,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>zesty:2,lovely:2,clean:1,fresh:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>fresh, zesty, lovely, soft</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -14047,7 +15057,7 @@
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>fresh, sweet, warm</t>
+          <t>fresh, sweet, warm, sensual</t>
         </is>
       </c>
       <c r="N102" s="5" t="inlineStr">
@@ -14116,6 +15126,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>fresh:2,sweet:2,warm:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>fresh, sweet, warm</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -14176,7 +15196,7 @@
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, sensual, deep</t>
+          <t>warm, sweet, deep, sensual</t>
         </is>
       </c>
       <c r="N103" s="5" t="inlineStr">
@@ -14245,6 +15265,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,deep:2,sensual:2</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>sweet, warm, sensual, deep</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -14305,7 +15335,7 @@
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, elegant</t>
+          <t>sweet, warm, lovely, elegant, sensual</t>
         </is>
       </c>
       <c r="N104" s="5" t="inlineStr">
@@ -14374,6 +15404,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>sweet:2,warm:1,lovely:1,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>sweet, lovely, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -14434,7 +15474,7 @@
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>fresh, warm, calm</t>
+          <t>fresh, calm, zesty, warm</t>
         </is>
       </c>
       <c r="N105" s="5" t="inlineStr">
@@ -14503,6 +15543,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>fresh:2,calm:1,zesty:1,warm:1</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>fresh, warm, calm</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -14628,6 +15678,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>clean:2,soft:2,lovely:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>clean, soft, lovely, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -14688,7 +15748,7 @@
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>sweet, sensual, elegant, warm</t>
+          <t>sweet, sensual, cozy, warm, elegant, deep</t>
         </is>
       </c>
       <c r="N107" s="5" t="inlineStr">
@@ -14757,6 +15817,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>sweet:2,sensual:2,cozy:1,warm:1,elegant:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>sweet, sensual, elegant, warm</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -14817,7 +15887,7 @@
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, calm</t>
+          <t>fresh, calm, clean, cool</t>
         </is>
       </c>
       <c r="N108" s="5" t="n"/>
@@ -14882,6 +15952,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>fresh:2,calm:1,clean:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>fresh, cool, calm</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -14942,7 +16022,7 @@
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>lovely, soft, clean, elegant</t>
+          <t>lovely, elegant, clean, sweet, soft</t>
         </is>
       </c>
       <c r="N109" s="5" t="n"/>
@@ -15007,6 +16087,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,clean:1,sweet:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>lovely, soft, clean, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -15067,7 +16157,7 @@
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
-          <t>fresh, warm, deep</t>
+          <t>warm, calm, clean, fresh, deep</t>
         </is>
       </c>
       <c r="N110" s="5" t="n"/>
@@ -15132,6 +16222,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>warm:2,calm:1,clean:1,fresh:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>fresh, warm, deep</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -15192,7 +16292,7 @@
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>elegant, clean, soft, lovely</t>
+          <t>elegant, soft, clean, lovely, sensual</t>
         </is>
       </c>
       <c r="N111" s="5" t="n"/>
@@ -15257,6 +16357,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>elegant:2,soft:2,clean:1,lovely:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>elegant, clean, soft, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -15317,7 +16427,7 @@
       </c>
       <c r="M112" s="5" t="inlineStr">
         <is>
-          <t>clean, cool, soft</t>
+          <t>clean, cool, calm, fresh, soft</t>
         </is>
       </c>
       <c r="N112" s="5" t="n"/>
@@ -15382,6 +16492,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,calm:1,fresh:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>clean, cool, soft</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -15442,7 +16562,7 @@
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>sweet, lovely, fresh, elegant</t>
+          <t>sweet, lovely, fresh, elegant, sensual</t>
         </is>
       </c>
       <c r="N113" s="5" t="inlineStr">
@@ -15511,6 +16631,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,fresh:1,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>sweet, lovely, fresh, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -15571,7 +16701,7 @@
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>sweet, cozy, warm, sensual</t>
+          <t>cozy, sweet, warm, sensual, soft</t>
         </is>
       </c>
       <c r="N114" s="5" t="inlineStr">
@@ -15640,6 +16770,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>cozy:2,sweet:2,warm:1,sensual:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>sweet, cozy, warm, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -15700,7 +16840,7 @@
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>sensual, deep, elegant, warm</t>
+          <t>warm, deep, sensual, elegant</t>
         </is>
       </c>
       <c r="N115" s="5" t="inlineStr">
@@ -15769,6 +16909,16 @@
           <t>미확인</t>
         </is>
       </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>sensual, deep, elegant, warm</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -15829,7 +16979,7 @@
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
-          <t>elegant, warm, lovely</t>
+          <t>elegant, zesty, warm, lovely, soft</t>
         </is>
       </c>
       <c r="N116" s="5" t="n"/>
@@ -15894,6 +17044,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>elegant:2,zesty:1,warm:1,lovely:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>elegant, warm, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -15954,7 +17114,7 @@
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
-          <t>elegant, lovely, fresh, clean</t>
+          <t>lovely, clean, fresh, zesty, elegant</t>
         </is>
       </c>
       <c r="N117" s="5" t="n"/>
@@ -16019,6 +17179,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>lovely:2,clean:1,fresh:1,zesty:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>elegant, lovely, fresh, clean</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -16144,6 +17314,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,clean:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>fresh, zesty, clean, cool</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -16204,7 +17384,7 @@
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
-          <t>lovely, soft, elegant</t>
+          <t>lovely, elegant, soft, clean, cozy</t>
         </is>
       </c>
       <c r="N119" s="5" t="n"/>
@@ -16269,6 +17449,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,soft:2,clean:1,cozy:1</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>lovely, soft, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -16329,7 +17519,7 @@
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, calm, cozy</t>
+          <t>elegant, calm, cozy, deep, soft</t>
         </is>
       </c>
       <c r="N120" s="5" t="inlineStr">
@@ -16398,6 +17588,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>elegant:2,calm:1,cozy:1,deep:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>elegant, soft, calm, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -16458,7 +17658,7 @@
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>sensual, sweet, warm, deep</t>
+          <t>sweet, deep, sensual, cozy, warm</t>
         </is>
       </c>
       <c r="N121" s="5" t="inlineStr">
@@ -16527,6 +17727,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>sweet:2,deep:2,sensual:2,cozy:1,warm:1</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>sensual, sweet, warm, deep</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -16587,7 +17797,7 @@
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, elegant, sensual</t>
+          <t>warm, deep, elegant, sensual</t>
         </is>
       </c>
       <c r="N122" s="5" t="inlineStr">
@@ -16656,6 +17866,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,elegant:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>deep, warm, elegant, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -16716,7 +17936,7 @@
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, elegant</t>
+          <t>fresh, lovely, zesty, elegant</t>
         </is>
       </c>
       <c r="N123" s="5" t="n"/>
@@ -16781,6 +18001,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>fresh:2,lovely:2,zesty:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>lovely, fresh, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -16841,7 +18071,7 @@
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, calm, cool</t>
+          <t>clean, fresh, calm, cool, zesty</t>
         </is>
       </c>
       <c r="N124" s="5" t="n"/>
@@ -16906,6 +18136,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,calm:1,cool:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>fresh, clean, calm, cool</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -16966,7 +18206,7 @@
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>sensual, warm, deep</t>
+          <t>warm, sensual, cozy, sweet, deep</t>
         </is>
       </c>
       <c r="N125" s="5" t="inlineStr">
@@ -17035,6 +18275,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>warm:2,sensual:2,cozy:1,sweet:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>sensual, warm, deep</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -17095,7 +18345,7 @@
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>warm, soft, cozy, elegant</t>
+          <t>warm, cozy, fresh, elegant, soft</t>
         </is>
       </c>
       <c r="N126" s="5" t="n"/>
@@ -17180,6 +18430,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>warm:2,cozy:1,fresh:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>warm, soft, cozy, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -17240,7 +18500,7 @@
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, calm</t>
+          <t>cool, fresh, calm, clean, zesty</t>
         </is>
       </c>
       <c r="N127" s="5" t="n"/>
@@ -17325,6 +18585,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,calm:1,clean:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>fresh, cool, calm</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -17385,7 +18655,7 @@
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, calm</t>
+          <t>clean, fresh, calm, cool, zesty</t>
         </is>
       </c>
       <c r="N128" s="5" t="n"/>
@@ -17458,6 +18728,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,calm:1,cool:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>fresh, clean, calm</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -17518,7 +18798,7 @@
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, cool</t>
+          <t>clean, calm, cool, fresh</t>
         </is>
       </c>
       <c r="N129" s="5" t="n"/>
@@ -17603,6 +18883,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>clean:2,calm:1,cool:1,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>fresh, clean, cool</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -17663,7 +18953,7 @@
       </c>
       <c r="M130" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, cool, clean</t>
+          <t>cool, fresh, zesty, clean</t>
         </is>
       </c>
       <c r="N130" s="5" t="n"/>
@@ -17748,6 +19038,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,zesty:2,clean:1</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>fresh, zesty, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -17808,7 +19108,7 @@
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>sensual, warm, elegant, deep</t>
+          <t>warm, sensual, sweet, elegant, deep</t>
         </is>
       </c>
       <c r="N131" s="5" t="n"/>
@@ -17873,6 +19173,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>warm:2,sensual:2,sweet:1,elegant:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>sensual, warm, elegant, deep</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -17933,7 +19243,7 @@
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, lovely, cool</t>
+          <t>clean, cool, fresh, lovely, soft</t>
         </is>
       </c>
       <c r="N132" s="5" t="n"/>
@@ -17998,6 +19308,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,fresh:2,lovely:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>fresh, clean, lovely, cool</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -18058,7 +19378,7 @@
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, sweet, sensual</t>
+          <t>warm, sweet, cozy, sensual</t>
         </is>
       </c>
       <c r="N133" s="5" t="inlineStr">
@@ -18127,6 +19447,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,cozy:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>warm, cozy, sweet, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -18187,7 +19517,7 @@
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, sensual</t>
+          <t>warm, deep, sensual, sweet</t>
         </is>
       </c>
       <c r="N134" s="5" t="inlineStr">
@@ -18256,6 +19586,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>deep, warm, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -18316,7 +19656,7 @@
       </c>
       <c r="M135" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, clean</t>
+          <t>clean, cool, fresh</t>
         </is>
       </c>
       <c r="N135" s="5" t="n"/>
@@ -18381,6 +19721,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>fresh, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -18441,7 +19791,7 @@
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, lovely</t>
+          <t>elegant, soft, calm, lovely</t>
         </is>
       </c>
       <c r="N136" s="5" t="inlineStr">
@@ -18510,6 +19860,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>elegant:2,soft:2,calm:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>soft, elegant, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -18570,7 +19930,7 @@
       </c>
       <c r="M137" s="5" t="inlineStr">
         <is>
-          <t>elegant, sensual, warm</t>
+          <t>elegant, sensual, cozy, warm, lovely, soft</t>
         </is>
       </c>
       <c r="N137" s="5" t="inlineStr">
@@ -18639,6 +19999,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>elegant:2,sensual:2,cozy:1,warm:1,lovely:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>elegant, sensual, warm</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -18699,7 +20069,7 @@
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
-          <t>cool, clean, fresh, calm</t>
+          <t>clean, cool, calm, fresh</t>
         </is>
       </c>
       <c r="N138" s="5" t="n"/>
@@ -18764,6 +20134,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,calm:1,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>cool, clean, fresh, calm</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -18824,7 +20204,7 @@
       </c>
       <c r="M139" s="5" t="inlineStr">
         <is>
-          <t>clean, elegant, soft, lovely</t>
+          <t>clean, elegant, lovely, soft</t>
         </is>
       </c>
       <c r="N139" s="5" t="n"/>
@@ -18889,6 +20269,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>clean:2,elegant:2,lovely:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>clean, elegant, soft, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -18949,7 +20339,7 @@
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, elegant, calm</t>
+          <t>calm, elegant, soft, clean</t>
         </is>
       </c>
       <c r="N140" s="5" t="inlineStr">
@@ -19018,6 +20408,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>calm:2,elegant:2,soft:2,clean:1</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>clean, soft, elegant, calm</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -19078,7 +20478,7 @@
       </c>
       <c r="M141" s="5" t="inlineStr">
         <is>
-          <t>lovely, soft, elegant, warm</t>
+          <t>lovely, elegant, soft, warm, sweet</t>
         </is>
       </c>
       <c r="N141" s="5" t="inlineStr">
@@ -19147,6 +20547,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,soft:2,warm:1,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>lovely, soft, elegant, warm</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -19207,7 +20617,7 @@
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, soft, elegant</t>
+          <t>lovely, clean, fresh, sweet, elegant, soft</t>
         </is>
       </c>
       <c r="N142" s="5" t="n"/>
@@ -19272,6 +20682,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>lovely:2,clean:1,fresh:1,sweet:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>lovely, fresh, soft, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -19332,7 +20752,7 @@
       </c>
       <c r="M143" s="5" t="inlineStr">
         <is>
-          <t>calm, soft, cozy, clean</t>
+          <t>calm, soft, clean, cozy</t>
         </is>
       </c>
       <c r="N143" s="5" t="n"/>
@@ -19397,6 +20817,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>calm:2,soft:2,clean:1,cozy:1</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>calm, soft, cozy, clean</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -19457,7 +20887,7 @@
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, calm, warm</t>
+          <t>clean, fresh, calm, warm</t>
         </is>
       </c>
       <c r="N144" s="5" t="n"/>
@@ -19542,6 +20972,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,calm:1,warm:1</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>fresh, clean, calm, warm</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -19602,7 +21042,7 @@
       </c>
       <c r="M145" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, sensual, cozy</t>
+          <t>warm, sweet, sensual, cozy, deep</t>
         </is>
       </c>
       <c r="N145" s="5" t="inlineStr">
@@ -19691,6 +21131,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,sensual:2,cozy:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>warm, sweet, sensual, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -19751,7 +21201,7 @@
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, clean</t>
+          <t>cool, fresh, clean, zesty</t>
         </is>
       </c>
       <c r="N146" s="5" t="n"/>
@@ -19816,6 +21266,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,clean:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>fresh, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -19876,7 +21336,7 @@
       </c>
       <c r="M147" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, zesty, cool</t>
+          <t>clean, zesty, cool, fresh, soft</t>
         </is>
       </c>
       <c r="N147" s="5" t="n"/>
@@ -19941,6 +21401,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>clean:2,zesty:2,cool:1,fresh:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>clean, fresh, zesty, cool</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -20001,7 +21471,7 @@
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
-          <t>sweet, sensual, warm</t>
+          <t>warm, sweet, sensual, cozy</t>
         </is>
       </c>
       <c r="N148" s="5" t="inlineStr">
@@ -20070,6 +21540,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,sensual:2,cozy:1</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>sweet, sensual, warm</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -20130,7 +21610,7 @@
       </c>
       <c r="M149" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, cozy, fresh</t>
+          <t>sweet, cozy, fresh, warm, sensual</t>
         </is>
       </c>
       <c r="N149" s="5" t="inlineStr">
@@ -20199,6 +21679,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>sweet:2,cozy:1,fresh:1,warm:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>sweet, warm, cozy, fresh</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -20324,6 +21814,16 @@
           <t>낮음 (앱에 표시 안 함)</t>
         </is>
       </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,cozy:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>warm, sweet, cozy, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -20384,7 +21884,7 @@
       </c>
       <c r="M151" s="5" t="inlineStr">
         <is>
-          <t>soft, fresh, lovely, sweet</t>
+          <t>lovely, soft, fresh, zesty, sweet</t>
         </is>
       </c>
       <c r="N151" s="5" t="n"/>
@@ -20449,6 +21949,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>lovely:2,soft:2,fresh:1,zesty:1,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>soft, fresh, lovely, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -20509,7 +22019,7 @@
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
-          <t>fresh, lovely, zesty, sweet</t>
+          <t>fresh, zesty, lovely, sweet</t>
         </is>
       </c>
       <c r="N152" s="5" t="n"/>
@@ -20574,6 +22084,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,lovely:2,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>fresh, lovely, zesty, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -20634,7 +22154,7 @@
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
-          <t>clean, calm, soft, elegant</t>
+          <t>clean, calm, cool, elegant, soft</t>
         </is>
       </c>
       <c r="N153" s="5" t="inlineStr">
@@ -20711,6 +22231,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>clean:2,calm:1,cool:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>clean, calm, soft, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -20771,7 +22301,7 @@
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, cool</t>
+          <t>clean, cool, calm, fresh, zesty</t>
         </is>
       </c>
       <c r="N154" s="5" t="n"/>
@@ -20836,6 +22366,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,calm:1,fresh:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>clean, fresh, cool</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -20896,7 +22436,7 @@
       </c>
       <c r="M155" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, zesty, clean</t>
+          <t>clean, cool, zesty, fresh, soft</t>
         </is>
       </c>
       <c r="N155" s="5" t="n"/>
@@ -20961,6 +22501,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,zesty:2,fresh:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>cool, fresh, zesty, clean</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -21021,7 +22571,7 @@
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, clean</t>
+          <t>cool, fresh, clean, zesty</t>
         </is>
       </c>
       <c r="N156" s="5" t="n"/>
@@ -21094,6 +22644,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,clean:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>fresh, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -21154,7 +22714,7 @@
       </c>
       <c r="M157" s="5" t="inlineStr">
         <is>
-          <t>warm, sensual, elegant, sweet</t>
+          <t>sweet, elegant, warm, lovely, sensual</t>
         </is>
       </c>
       <c r="N157" s="5" t="inlineStr">
@@ -21223,6 +22783,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>sweet:2,elegant:2,warm:1,lovely:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>warm, sensual, elegant, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -21283,7 +22853,7 @@
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>soft, fresh, elegant, calm</t>
+          <t>calm, elegant, fresh, lovely, soft</t>
         </is>
       </c>
       <c r="N158" s="5" t="n"/>
@@ -21348,6 +22918,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>calm:2,elegant:2,fresh:1,lovely:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>soft, fresh, elegant, calm</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -21408,7 +22988,7 @@
       </c>
       <c r="M159" s="5" t="inlineStr">
         <is>
-          <t>lovely, soft, elegant, clean</t>
+          <t>lovely, clean, elegant, soft</t>
         </is>
       </c>
       <c r="N159" s="5" t="n"/>
@@ -21473,6 +23053,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>lovely:2,clean:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>lovely, soft, elegant, clean</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -21533,7 +23123,7 @@
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, calm, cool</t>
+          <t>clean, fresh, calm, cool, zesty</t>
         </is>
       </c>
       <c r="N160" s="5" t="n"/>
@@ -21598,6 +23188,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,calm:1,cool:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>fresh, clean, calm, cool</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -21662,7 +23262,7 @@
       </c>
       <c r="M161" s="5" t="inlineStr">
         <is>
-          <t>soft, clean, cozy, calm</t>
+          <t>clean, cozy, soft, calm, lovely</t>
         </is>
       </c>
       <c r="N161" s="5" t="inlineStr">
@@ -21731,6 +23331,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>clean:2,cozy:2,soft:2,calm:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>soft, clean, cozy, calm</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -21795,7 +23405,7 @@
       </c>
       <c r="M162" s="5" t="inlineStr">
         <is>
-          <t>calm, soft, cozy, warm</t>
+          <t>calm, cozy, warm, elegant, soft</t>
         </is>
       </c>
       <c r="N162" s="5" t="n"/>
@@ -21880,6 +23490,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>calm:2,cozy:2,warm:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>calm, soft, cozy, warm</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -21944,7 +23564,7 @@
       </c>
       <c r="M163" s="5" t="inlineStr">
         <is>
-          <t>warm, cozy, calm, deep</t>
+          <t>cozy, warm, calm, deep</t>
         </is>
       </c>
       <c r="N163" s="5" t="n"/>
@@ -22029,6 +23649,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,calm:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>warm, cozy, calm, deep</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -22093,7 +23723,7 @@
       </c>
       <c r="M164" s="5" t="inlineStr">
         <is>
-          <t>deep, warm, sensual, cozy, sweet</t>
+          <t>warm, deep, sensual, cozy, sweet</t>
         </is>
       </c>
       <c r="N164" s="5" t="inlineStr">
@@ -22182,6 +23812,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,cozy:1,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>deep, warm, sensual, cozy, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -22242,7 +23882,7 @@
       </c>
       <c r="M165" s="5" t="inlineStr">
         <is>
-          <t>fresh, clean, cool, calm</t>
+          <t>cool, fresh, calm, clean</t>
         </is>
       </c>
       <c r="N165" s="5" t="n"/>
@@ -22327,6 +23967,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,calm:1,clean:1</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>fresh, clean, cool, calm</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -22387,7 +24037,7 @@
       </c>
       <c r="M166" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, cool, clean</t>
+          <t>cool, fresh, zesty, clean</t>
         </is>
       </c>
       <c r="N166" s="5" t="n"/>
@@ -22452,6 +24102,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,zesty:2,clean:1</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>zesty, fresh, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -22508,7 +24168,7 @@
       </c>
       <c r="M167" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, sweet, lovely</t>
+          <t>fresh, sweet, zesty, lovely</t>
         </is>
       </c>
       <c r="N167" s="5" t="n"/>
@@ -22573,6 +24233,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>fresh:2,sweet:2,zesty:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>fresh, zesty, sweet, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -22633,7 +24303,7 @@
       </c>
       <c r="M168" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, calm, cool</t>
+          <t>calm, clean, cool, fresh, soft</t>
         </is>
       </c>
       <c r="N168" s="5" t="n"/>
@@ -22698,6 +24368,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>calm:2,clean:2,cool:1,fresh:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>clean, fresh, calm, cool</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -22758,7 +24438,7 @@
       </c>
       <c r="M169" s="5" t="inlineStr">
         <is>
-          <t>lovely, sweet, soft, fresh</t>
+          <t>sweet, lovely, fresh, zesty, soft</t>
         </is>
       </c>
       <c r="N169" s="5" t="n"/>
@@ -22823,6 +24503,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>sweet:2,lovely:2,fresh:1,zesty:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>lovely, sweet, soft, fresh</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -22883,7 +24573,7 @@
       </c>
       <c r="M170" s="5" t="inlineStr">
         <is>
-          <t>deep, sensual, warm, elegant</t>
+          <t>elegant, deep, sensual, warm</t>
         </is>
       </c>
       <c r="N170" s="5" t="inlineStr">
@@ -22952,6 +24642,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>elegant:2,deep:2,sensual:2,warm:1</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>deep, sensual, warm, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -23012,7 +24712,7 @@
       </c>
       <c r="M171" s="5" t="inlineStr">
         <is>
-          <t>cozy, warm, sweet, sensual</t>
+          <t>cozy, warm, sweet, deep, sensual</t>
         </is>
       </c>
       <c r="N171" s="5" t="n"/>
@@ -23077,6 +24777,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,sweet:2,deep:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>cozy, warm, sweet, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -23210,6 +24920,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>fresh:2,lovely:2,calm:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>fresh, lovely, calm, cool</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -23274,7 +24994,7 @@
       </c>
       <c r="M173" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, elegant</t>
+          <t>fresh, lovely, elegant, clean</t>
         </is>
       </c>
       <c r="N173" s="5" t="n"/>
@@ -23347,6 +25067,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>fresh:2,lovely:2,elegant:2,clean:1</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>lovely, fresh, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -23407,7 +25137,7 @@
       </c>
       <c r="M174" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, cool, clean</t>
+          <t>fresh, zesty, clean, cool</t>
         </is>
       </c>
       <c r="N174" s="5" t="n"/>
@@ -23480,6 +25210,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,clean:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>zesty, fresh, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -23544,7 +25284,7 @@
       </c>
       <c r="M175" s="5" t="inlineStr">
         <is>
-          <t>fresh, soft, lovely, elegant</t>
+          <t>fresh, lovely, elegant, soft</t>
         </is>
       </c>
       <c r="N175" s="5" t="n"/>
@@ -23617,6 +25357,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>fresh:2,lovely:2,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>fresh, soft, lovely, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -23681,7 +25431,7 @@
       </c>
       <c r="M176" s="5" t="inlineStr">
         <is>
-          <t>fresh, calm, elegant, deep</t>
+          <t>calm, fresh, cool, elegant, deep</t>
         </is>
       </c>
       <c r="N176" s="5" t="n"/>
@@ -23754,6 +25504,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>calm:2,fresh:2,cool:1,elegant:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>fresh, calm, elegant, deep</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -23818,7 +25578,7 @@
       </c>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>soft, clean, calm, cozy</t>
+          <t>soft, calm, clean, cozy</t>
         </is>
       </c>
       <c r="N177" s="5" t="n"/>
@@ -23891,6 +25651,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>soft:2,calm:1,clean:1,cozy:1</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>soft, clean, calm, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -23955,7 +25725,7 @@
       </c>
       <c r="M178" s="5" t="inlineStr">
         <is>
-          <t>calm, soft, warm, elegant</t>
+          <t>calm, clean, elegant, soft</t>
         </is>
       </c>
       <c r="N178" s="5" t="n"/>
@@ -24028,6 +25798,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>calm:2,clean:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>calm, soft, warm, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -24092,7 +25872,7 @@
       </c>
       <c r="M179" s="5" t="inlineStr">
         <is>
-          <t>fresh, calm, clean, cool, zesty</t>
+          <t>clean, fresh, calm, cool, zesty</t>
         </is>
       </c>
       <c r="N179" s="5" t="n"/>
@@ -24165,6 +25945,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,calm:1,cool:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>fresh, calm, clean, cool, zesty</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -24229,7 +26019,7 @@
       </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
-          <t>warm, sensual, deep, cozy, sweet</t>
+          <t>warm, sensual, cozy, sweet, deep</t>
         </is>
       </c>
       <c r="N180" s="5" t="n"/>
@@ -24302,6 +26092,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>warm:2,sensual:2,cozy:1,sweet:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>warm, sensual, deep, cozy, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -24366,7 +26166,7 @@
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>zesty, fresh, clean, sweet, soft</t>
+          <t>clean, fresh, zesty, sweet, soft</t>
         </is>
       </c>
       <c r="N181" s="5" t="inlineStr">
@@ -24443,6 +26243,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>clean:2,fresh:2,zesty:2,sweet:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>zesty, fresh, clean, sweet, soft</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -24503,7 +26313,7 @@
       </c>
       <c r="M182" s="5" t="inlineStr">
         <is>
-          <t>calm, fresh, soft, cozy</t>
+          <t>calm, fresh, cozy, soft</t>
         </is>
       </c>
       <c r="N182" s="5" t="n"/>
@@ -24588,6 +26398,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>calm:2,fresh:2,cozy:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>calm, fresh, soft, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -24648,7 +26468,7 @@
       </c>
       <c r="M183" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, clean, lovely</t>
+          <t>elegant, soft, clean, cozy, lovely, sensual</t>
         </is>
       </c>
       <c r="N183" s="5" t="n"/>
@@ -24733,6 +26553,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>elegant:2,soft:2,clean:1,cozy:1,lovely:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>soft, elegant, clean, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -24793,7 +26623,7 @@
       </c>
       <c r="M184" s="5" t="inlineStr">
         <is>
-          <t>elegant, soft, lovely, sweet</t>
+          <t>lovely, elegant, clean, cozy, sweet, soft</t>
         </is>
       </c>
       <c r="N184" s="5" t="inlineStr">
@@ -24882,6 +26712,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,clean:1,cozy:1,sweet:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>elegant, soft, lovely, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -24942,7 +26782,7 @@
       </c>
       <c r="M185" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, soft, zesty</t>
+          <t>clean, zesty, fresh, elegant, soft</t>
         </is>
       </c>
       <c r="N185" s="5" t="n"/>
@@ -25027,6 +26867,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>clean:2,zesty:2,fresh:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>clean, fresh, soft, zesty</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -25087,7 +26937,7 @@
       </c>
       <c r="M186" s="5" t="inlineStr">
         <is>
-          <t>warm, deep, sweet, sensual</t>
+          <t>warm, deep, sensual, sweet</t>
         </is>
       </c>
       <c r="N186" s="5" t="n"/>
@@ -25172,6 +27022,16 @@
           <t>높음 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>warm, deep, sweet, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -25232,7 +27092,7 @@
       </c>
       <c r="M187" s="5" t="inlineStr">
         <is>
-          <t>fresh, soft, lovely, elegant</t>
+          <t>lovely, elegant, fresh, zesty, soft</t>
         </is>
       </c>
       <c r="N187" s="5" t="n"/>
@@ -25297,6 +27157,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,fresh:1,zesty:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>fresh, soft, lovely, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -25357,7 +27227,7 @@
       </c>
       <c r="M188" s="5" t="inlineStr">
         <is>
-          <t>lovely, elegant, soft</t>
+          <t>lovely, elegant, sweet, soft</t>
         </is>
       </c>
       <c r="N188" s="5" t="n"/>
@@ -25422,6 +27292,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>lovely:2,elegant:2,sweet:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>lovely, elegant, soft</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -25482,7 +27362,7 @@
       </c>
       <c r="M189" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, zesty, clean</t>
+          <t>cool, zesty, clean, fresh</t>
         </is>
       </c>
       <c r="N189" s="5" t="n"/>
@@ -25547,6 +27427,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>cool:2,zesty:2,clean:1,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>cool, fresh, zesty, clean</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -25607,7 +27497,7 @@
       </c>
       <c r="M190" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, elegant, lovely</t>
+          <t>clean, soft, lovely, elegant</t>
         </is>
       </c>
       <c r="N190" s="5" t="inlineStr">
@@ -25676,6 +27566,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>clean:2,soft:2,lovely:1,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>clean, soft, elegant, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -25736,7 +27636,7 @@
       </c>
       <c r="M191" s="5" t="inlineStr">
         <is>
-          <t>elegant, sensual, deep</t>
+          <t>elegant, deep, sensual, warm</t>
         </is>
       </c>
       <c r="N191" s="5" t="inlineStr">
@@ -25813,6 +27713,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>elegant:2,deep:2,sensual:2,warm:1</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>elegant, sensual, deep</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -25873,7 +27783,7 @@
       </c>
       <c r="M192" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, sensual</t>
+          <t>warm, sweet, sensual, deep</t>
         </is>
       </c>
       <c r="N192" s="5" t="inlineStr">
@@ -25950,6 +27860,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,sensual:2,deep:1</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>sweet, warm, sensual</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -26010,7 +27930,7 @@
       </c>
       <c r="M193" s="5" t="inlineStr">
         <is>
-          <t>sweet, warm, sensual, deep</t>
+          <t>warm, deep, sensual, sweet</t>
         </is>
       </c>
       <c r="N193" s="5" t="inlineStr">
@@ -26087,6 +28007,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>sweet, warm, sensual, deep</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -26147,7 +28077,7 @@
       </c>
       <c r="M194" s="5" t="inlineStr">
         <is>
-          <t>elegant, sensual, warm, sweet</t>
+          <t>elegant, sensual, warm, sweet, lovely</t>
         </is>
       </c>
       <c r="N194" s="5" t="inlineStr">
@@ -26216,6 +28146,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>elegant:2,sensual:2,warm:1,sweet:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>elegant, sensual, warm, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -26276,7 +28216,7 @@
       </c>
       <c r="M195" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, soft, sweet</t>
+          <t>zesty, sweet, fresh, soft</t>
         </is>
       </c>
       <c r="N195" s="5" t="n"/>
@@ -26341,6 +28281,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>zesty:2,sweet:2,fresh:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>fresh, zesty, soft, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -26401,7 +28351,7 @@
       </c>
       <c r="M196" s="5" t="inlineStr">
         <is>
-          <t>soft, cozy, sweet, lovely</t>
+          <t>cozy, sweet, soft, clean, lovely</t>
         </is>
       </c>
       <c r="N196" s="5" t="inlineStr">
@@ -26470,6 +28420,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>cozy:2,sweet:2,soft:2,clean:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>soft, cozy, sweet, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -26530,7 +28490,7 @@
       </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, clean, cool</t>
+          <t>fresh, zesty, calm, clean, cool</t>
         </is>
       </c>
       <c r="N197" s="5" t="n"/>
@@ -26603,6 +28563,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>fresh:2,zesty:2,calm:1,clean:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>fresh, zesty, clean, cool</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -26663,7 +28633,7 @@
       </c>
       <c r="M198" s="5" t="inlineStr">
         <is>
-          <t>fresh, calm, soft, clean, cool</t>
+          <t>calm, clean, cool, fresh, soft</t>
         </is>
       </c>
       <c r="N198" s="5" t="n"/>
@@ -26736,6 +28706,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>calm:2,clean:2,cool:1,fresh:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>fresh, calm, soft, clean, cool</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -26796,7 +28776,7 @@
       </c>
       <c r="M199" s="5" t="inlineStr">
         <is>
-          <t>clean, soft, fresh, calm, cozy</t>
+          <t>clean, soft, calm, cozy, fresh</t>
         </is>
       </c>
       <c r="N199" s="5" t="inlineStr">
@@ -26873,6 +28853,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>clean:2,soft:2,calm:1,cozy:1,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>clean, soft, fresh, calm, cozy</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -27006,6 +28996,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>cozy:2,warm:2,sweet:2,soft:1</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>cozy, warm, sweet, soft</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -27066,7 +29066,7 @@
       </c>
       <c r="M201" s="5" t="inlineStr">
         <is>
-          <t>lovely, fresh, soft</t>
+          <t>fresh, lovely, sweet, soft</t>
         </is>
       </c>
       <c r="N201" s="5" t="n"/>
@@ -27139,6 +29139,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>fresh:2,lovely:2,sweet:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>lovely, fresh, soft</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -27199,7 +29209,7 @@
       </c>
       <c r="M202" s="5" t="inlineStr">
         <is>
-          <t>cool, fresh, clean</t>
+          <t>clean, cool, fresh, calm</t>
         </is>
       </c>
       <c r="N202" s="5" t="n"/>
@@ -27264,6 +29274,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,fresh:2,calm:1</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>cool, fresh, clean</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -27328,7 +29348,7 @@
       </c>
       <c r="M203" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, elegant, sweet</t>
+          <t>fresh, elegant, zesty, sweet, lovely</t>
         </is>
       </c>
       <c r="N203" s="5" t="n"/>
@@ -27401,6 +29421,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>fresh:2,elegant:2,zesty:1,sweet:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>fresh, zesty, elegant, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -27465,7 +29495,7 @@
       </c>
       <c r="M204" s="5" t="inlineStr">
         <is>
-          <t>fresh, warm, deep</t>
+          <t>warm, fresh, deep</t>
         </is>
       </c>
       <c r="N204" s="5" t="inlineStr">
@@ -27542,6 +29572,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>warm:2,fresh:1,deep:1</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>fresh, warm, deep</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -27606,7 +29646,7 @@
       </c>
       <c r="M205" s="5" t="inlineStr">
         <is>
-          <t>fresh, zesty, cool, clean</t>
+          <t>cool, fresh, clean, zesty, sweet</t>
         </is>
       </c>
       <c r="N205" s="5" t="n"/>
@@ -27679,6 +29719,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>cool:2,fresh:2,clean:1,zesty:1,sweet:1</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>fresh, zesty, cool, clean</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -27743,7 +29793,7 @@
       </c>
       <c r="M206" s="5" t="inlineStr">
         <is>
-          <t>soft, elegant, clean, lovely</t>
+          <t>elegant, soft, clean, lovely</t>
         </is>
       </c>
       <c r="N206" s="5" t="inlineStr">
@@ -27820,6 +29870,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>elegant:2,soft:2,clean:1,lovely:1</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>soft, elegant, clean, lovely</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -27884,7 +29944,7 @@
       </c>
       <c r="M207" s="5" t="inlineStr">
         <is>
-          <t>warm, soft, elegant, cozy, sweet</t>
+          <t>cozy, sweet, warm, elegant, soft</t>
         </is>
       </c>
       <c r="N207" s="5" t="n"/>
@@ -27957,6 +30017,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>cozy:2,sweet:2,warm:1,elegant:1,soft:1</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>warm, soft, elegant, cozy, sweet</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -28021,7 +30091,7 @@
       </c>
       <c r="M208" s="5" t="inlineStr">
         <is>
-          <t>fresh, cool, clean, calm</t>
+          <t>clean, cool, fresh, calm, zesty</t>
         </is>
       </c>
       <c r="N208" s="5" t="n"/>
@@ -28094,6 +30164,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>clean:2,cool:2,fresh:2,calm:1,zesty:1</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>fresh, cool, clean, calm</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -28158,7 +30238,7 @@
       </c>
       <c r="M209" s="5" t="inlineStr">
         <is>
-          <t>deep, sensual, warm, elegant</t>
+          <t>warm, deep, sensual, elegant</t>
         </is>
       </c>
       <c r="N209" s="5" t="inlineStr">
@@ -28227,6 +30307,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>warm:2,deep:2,sensual:2,elegant:1</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>deep, sensual, warm, elegant</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -28356,6 +30446,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>fresh:2,calm:1,clean:1,cool:1</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>fresh, calm, clean, cool</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -28420,7 +30520,7 @@
       </c>
       <c r="M211" s="5" t="inlineStr">
         <is>
-          <t>warm, sweet, sensual, cozy, deep</t>
+          <t>warm, sweet, deep, sensual, cozy</t>
         </is>
       </c>
       <c r="N211" s="5" t="inlineStr">
@@ -28497,6 +30597,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>warm:2,sweet:2,deep:2,sensual:2,cozy:1</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>warm, sweet, sensual, cozy, deep</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -28557,7 +30667,7 @@
       </c>
       <c r="M212" s="5" t="inlineStr">
         <is>
-          <t>soft, cozy, calm, warm</t>
+          <t>cozy, soft, calm, warm, sensual</t>
         </is>
       </c>
       <c r="N212" s="5" t="n"/>
@@ -28622,6 +30732,16 @@
           <t>보통 (앱에 표시)</t>
         </is>
       </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>cozy:2,soft:2,calm:1,warm:1,sensual:1</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>soft, cozy, calm, warm</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -28678,7 +30798,7 @@
       </c>
       <c r="M213" s="5" t="inlineStr">
         <is>
-          <t>clean, fresh, soft, calm</t>
+          <t>clean, soft, calm, fresh</t>
         </is>
       </c>
       <c r="N213" s="5" t="n"/>
@@ -28741,6 +30861,16 @@
       <c r="AE213" s="6" t="inlineStr">
         <is>
           <t>보통 (앱에 표시)</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>clean:2,soft:2,calm:1,fresh:1</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>clean, fresh, soft, calm</t>
         </is>
       </c>
     </row>
